--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO12" headerRowCount="1">
-  <autoFilter ref="A1:CO12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO24" headerRowCount="1">
+  <autoFilter ref="A1:CO24"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$12)</f>
+        <f>COUNTA('Picks'!$A$2:$A$24)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$24,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")+COUNTIFS('Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$24,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")/(COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"win")+COUNTIFS('Picks'!$BX$2:$BX$24,"&gt;0",'Picks'!$V$2:$V$24,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$24)/SUM('Picks'!$BX$2:$BX$24),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$12)</f>
+        <f>SUM('Picks'!$BY$2:$BY$24)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$24,"&lt;&gt;",'Picks'!$AB$2:$AB$24),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$24,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$24,'Picks'!$AM$2:$AM$24,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A14,'Picks'!$U$2:$U$24,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A15,'Picks'!$U$2:$U$24,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled",'Picks'!$V$2:$V$24,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$24,'Picks'!$H$2:$H$24,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$24,'Picks'!$H$2:$H$24,$A16,'Picks'!$U$2:$U$24,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO12"/>
+  <dimension ref="A1:CO24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3874,18 +3874,32 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T05:00:27.320959Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Elvina Kalieva p=0.574 vs Katherine Sebov. Executable ask 0.6700 (aec-wta-katseb-elvkal-2026-07-27).</t>
@@ -4320,22 +4334,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>373a488acf324fa9</t>
+          <t>8dda84772591491a</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:58:09.459721Z</t>
+          <t>2026-07-28T05:03:44.224309Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T15:00Z</t>
+          <t>2026-07-28T08:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>1067-2026:179450</t>
+          <t>1073-2026:179584</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4345,12 +4359,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Alesia Breaz</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Zeynep Sonmez</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4370,22 +4384,22 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-614</v>
+        <v>-1900</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.162866</v>
+        <v>1.052632</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.859944</v>
+        <v>0.95</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.772271</v>
+        <v>0.539316</v>
       </c>
       <c r="P12" s="28" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>-0.087673</v>
+        <v>-0.410684</v>
       </c>
       <c r="R12" s="26" t="n">
         <v>0</v>
@@ -4400,21 +4414,35 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:39.258308Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Cadence Brace p=0.228 vs Zeynep Sonmez. Executable ask 0.8600 (aec-wta-zeyson-cadbra-2026-07-26).</t>
+          <t>Surface-blended Elo on Hard: Alesia Breaz p=0.461 vs Laura Samson. Executable ask 0.9500 (aec-wta-lausam-alebre-2026-07-27).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4455,32 +4483,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Alesia Breaz</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Alesia Breaz</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Alesia Breaz</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Zeynep Sonmez</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Zeynep Sonmez</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Zeynep Sonmez</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4533,7 +4561,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T15:05:28.059607Z</t>
+          <t>2026-07-28T05:01:29.400703Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4543,13 +4571,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-614</v>
+        <v>-1900</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.162866</v>
+        <v>1.052632</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.859944</v>
+        <v>0.95</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4580,6 +4608,3260 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
     </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>30d29ce7fa0d4fdb</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T05:03:44.224309Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:179580</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Dalila Spiteri</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Yelyzaveta Kotliar</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.629597</v>
+      </c>
+      <c r="P13" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q13" s="28" t="n">
+        <v>0.07012599999999999</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:39.363889Z</t>
+        </is>
+      </c>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Dalila Spiteri p=0.370 vs Yelyzaveta Kotliar. Executable ask 0.5600 (aec-wta-yelkot-dalspi-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Dalila Spiteri</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Dalila Spiteri</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Dalila Spiteri</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Yelyzaveta Kotliar</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Yelyzaveta Kotliar</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Yelyzaveta Kotliar</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T05:01:29.353293Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>cc74bd5c56de4e4f</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T05:03:44.224309Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:183171</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Darja Semenistaja</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Mia Ristic</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.553512</v>
+      </c>
+      <c r="P14" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q14" s="28" t="n">
+        <v>0.022996</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:39.467765Z</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Darja Semenistaja p=0.554 vs Mia Ristic. Executable ask 0.5300 (aec-wta-miaris-darsem-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Darja Semenistaja</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Darja Semenistaja</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Darja Semenistaja</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Mia Ristic</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Mia Ristic</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Mia Ristic</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T05:01:29.436773Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>c468caf1f2da4603</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:09:48.374429Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T09:30Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:183172</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Lucia Bronzetti</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Miriana Tona</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-1011</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.098912</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.909991</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.671191</v>
+      </c>
+      <c r="P15" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q15" s="28" t="n">
+        <v>-0.2388</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:43.901317Z</t>
+        </is>
+      </c>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Lucia Bronzetti p=0.671 vs Miriana Tona. Executable ask 0.9100 (aec-wta-mirton-lucbro-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Lucia Bronzetti</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Lucia Bronzetti</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Lucia Bronzetti</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Miriana Tona</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Miriana Tona</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Miriana Tona</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:07:29.222890Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-1011</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.098912</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.909991</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>da48ac67863741c5</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:09:48.374429Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T10:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:183177</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Lola Radivojevic</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Margaux Rouvroy</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.549053</v>
+      </c>
+      <c r="P16" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q16" s="28" t="n">
+        <v>0.349053</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:44.017439Z</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Lola Radivojevic p=0.451 vs Margaux Rouvroy. Executable ask 0.2000 (aec-wta-marrou-lolrad-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Lola Radivojevic</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Lola Radivojevic</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Lola Radivojevic</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Margaux Rouvroy</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Margaux Rouvroy</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Margaux Rouvroy</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:07:29.251635Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>fdfd679380374cf5</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:09:48.374429Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:179593</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Chloe Paquet</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Francesca Jones</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.742329</v>
+      </c>
+      <c r="P17" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q17" s="28" t="n">
+        <v>-0.047587</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:44.134104Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Chloe Paquet p=0.258 vs Francesca Jones. Executable ask 0.7900 (aec-wta-frajon-chlpaq-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Chloe Paquet</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Chloe Paquet</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Chloe Paquet</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Francesca Jones</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Francesca Jones</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Francesca Jones</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:07:29.757214Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>4ef8462ffb1f4f65</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:09:48.374429Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:179585</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Maia Ilinca Burcescu</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Alevtina Ibragimova</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-456</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.219298</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.820144</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.597506</v>
+      </c>
+      <c r="P18" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q18" s="28" t="n">
+        <v>-0.222638</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:59:03.420461Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Maia Ilinca Burcescu p=0.402 vs Alevtina Ibragimova. Executable ask 0.8200 (aec-wta-aleibr-maibur-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Maia Ilinca Burcescu</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Maia Ilinca Burcescu</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Maia Ilinca Burcescu</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Alevtina Ibragimova</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Alevtina Ibragimova</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Alevtina Ibragimova</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:07:29.244295Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-456</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.219298</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.820144</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>4892baa973e74093</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:09:48.374429Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:179582</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Anastasiia Sobolieva</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Selena Janicijevic</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>376</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.210084</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.506887</v>
+      </c>
+      <c r="P19" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q19" s="28" t="n">
+        <v>0.296803</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:44.280191Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Anastasiia Sobolieva p=0.493 vs Selena Janicijevic. Executable ask 0.2100 (aec-wta-seljan-anasob-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Anastasiia Sobolieva</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Anastasiia Sobolieva</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Anastasiia Sobolieva</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Selena Janicijevic</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Selena Janicijevic</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Selena Janicijevic</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:07:29.943296Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>376</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.210084</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>b348a92598374228</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:15:58.367390Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:179597</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Carole Monnet</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Miriam Bulgaru</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.604046</v>
+      </c>
+      <c r="P20" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q20" s="28" t="n">
+        <v>0.033231</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Carole Monnet p=0.604 vs Miriam Bulgaru. Executable ask 0.5700 (aec-wta-mirbul-carmon-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Carole Monnet</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Carole Monnet</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Carole Monnet</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Miriam Bulgaru</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Miriam Bulgaru</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Miriam Bulgaru</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:13:41.297840Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>b6f4a3e099bb472a</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:22:03.423136Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>888-2026:179000</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Polina Kudermetova</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.512221</v>
+      </c>
+      <c r="P21" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q21" s="28" t="n">
+        <v>-0.058594</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Polina Kudermetova p=0.512 vs Cristina Bucsa. Executable ask 0.5700 (aec-wta-cribuc-polkud-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Polina Kudermetova</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Polina Kudermetova</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Polina Kudermetova</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:19:47.442380Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>6a97ad946c334512</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:22:03.423136Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>888-2026:179017</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xinyu</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Julieta Pareja</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.624023</v>
+      </c>
+      <c r="P22" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q22" s="28" t="n">
+        <v>0.044191</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Wang Xinyu p=0.624 vs Julieta Pareja. Executable ask 0.5800 (aec-wta-julpar-xinwan-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xinyu</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xinyu</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xinyu</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Julieta Pareja</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Julieta Pareja</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Julieta Pareja</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:19:49.037022Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>ba633ac72b564928</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:22:03.423136Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>1067-2026:179443</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.695466</v>
+      </c>
+      <c r="P23" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q23" s="28" t="n">
+        <v>0.025499</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Kristina Liutova p=0.305 vs Ekaterina Alexandrova. Executable ask 0.6700 (aec-wta-ekaale-kriliu-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:19:54.883376Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>1bd4b44fe1704333</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:22:03.423136Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>1067-2026:179450</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Cadence Brace</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Zeynep Sonmez</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-614</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.162866</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.859944</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.772271</v>
+      </c>
+      <c r="P24" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q24" s="28" t="n">
+        <v>-0.087673</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Cadence Brace p=0.228 vs Zeynep Sonmez. Executable ask 0.8600 (aec-wta-zeyson-cadbra-2026-07-26).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Cadence Brace</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Cadence Brace</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Cadence Brace</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Zeynep Sonmez</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Zeynep Sonmez</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Zeynep Sonmez</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>73429bd71f12304106b9ffb751bd50617d5109d487f00de7ae2732f60e779590</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:19:52.688752Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-614</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.162866</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.859944</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -17630,7 +17630,7 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>85646fa025124695</t>
+          <t>6d53fafea44848d1</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
@@ -17640,12 +17640,12 @@
       </c>
       <c r="C60" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T18:30Z</t>
+          <t>2026-07-30T17:00Z</t>
         </is>
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>875-2026:179558</t>
+          <t>888-2026:179021</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
@@ -17655,12 +17655,12 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>Himeno Sakatsume</t>
+          <t>Anna Kalinskaya</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>Mai Hontama</t>
+          <t>Janice Tjen</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
@@ -17680,25 +17680,25 @@
         </is>
       </c>
       <c r="L60" s="26" t="n">
-        <v>113</v>
+        <v>-257</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>2.13</v>
+        <v>1.389105</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.719888</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.5652740000000001</v>
+        <v>0.711749</v>
       </c>
       <c r="P60" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q60" s="28" t="n">
-        <v>0.09579</v>
+        <v>-0.008139</v>
       </c>
       <c r="R60" s="26" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="S60" s="29" t="n">
         <v>0</v>
@@ -17724,7 +17724,7 @@
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Himeno Sakatsume p=0.565 vs Mai Hontama. Executable ask 0.4700 (aec-wta-maihon-himsak-2026-07-31).</t>
+          <t>Surface-blended Elo on Hard: Anna Kalinskaya p=0.712 vs Janice Tjen. Executable ask 0.7200 (aec-wta-jantje-annkal-2026-07-29).</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -17765,32 +17765,32 @@
       </c>
       <c r="AP60" s="24" t="inlineStr">
         <is>
-          <t>Himeno Sakatsume</t>
+          <t>Anna Kalinskaya</t>
         </is>
       </c>
       <c r="AQ60" s="24" t="inlineStr">
         <is>
-          <t>Himeno Sakatsume</t>
+          <t>Anna Kalinskaya</t>
         </is>
       </c>
       <c r="AR60" s="24" t="inlineStr">
         <is>
-          <t>Himeno Sakatsume</t>
+          <t>Anna Kalinskaya</t>
         </is>
       </c>
       <c r="AS60" s="24" t="inlineStr">
         <is>
-          <t>Mai Hontama</t>
+          <t>Janice Tjen</t>
         </is>
       </c>
       <c r="AT60" s="24" t="inlineStr">
         <is>
-          <t>Mai Hontama</t>
+          <t>Janice Tjen</t>
         </is>
       </c>
       <c r="AU60" s="24" t="inlineStr">
         <is>
-          <t>Mai Hontama</t>
+          <t>Janice Tjen</t>
         </is>
       </c>
       <c r="AV60" s="24" t="n"/>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:54.156495Z</t>
+          <t>2026-07-30T16:50:51.570342Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -17853,13 +17853,13 @@
       </c>
       <c r="BJ60" s="25" t="n"/>
       <c r="BK60" s="26" t="n">
-        <v>113</v>
+        <v>-257</v>
       </c>
       <c r="BL60" s="27" t="n">
-        <v>2.13</v>
+        <v>1.389105</v>
       </c>
       <c r="BM60" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.719888</v>
       </c>
       <c r="BN60" s="28" t="n"/>
       <c r="BO60" s="28" t="n"/>
@@ -17893,12 +17893,12 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>f3d1314d7d5a47c0</t>
+          <t>a83cffe8daa44cf6</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:53:01.133141Z</t>
+          <t>2026-07-30T17:20:01.182496Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -17908,7 +17908,7 @@
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>875-2026:179559</t>
+          <t>875-2026:179558</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
@@ -17918,12 +17918,12 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>Maddison Inglis</t>
+          <t>Himeno Sakatsume</t>
         </is>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Mai Hontama</t>
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="I61" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J61" s="25" t="n"/>
@@ -17943,25 +17943,25 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-138</v>
+        <v>113</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.13</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.469484</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.555657</v>
+        <v>0.5652740000000001</v>
       </c>
       <c r="P61" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q61" s="28" t="n">
-        <v>-0.024175</v>
+        <v>0.09579</v>
       </c>
       <c r="R61" s="26" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="S61" s="29" t="n">
         <v>0</v>
@@ -17987,7 +17987,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Maddison Inglis p=0.444 vs Moyuka Uchijima. Executable ask 0.5800 (aec-wta-moyuch-mading-2026-07-30).</t>
+          <t>Surface-blended Elo on Hard: Himeno Sakatsume p=0.565 vs Mai Hontama. Executable ask 0.4700 (aec-wta-maihon-himsak-2026-07-31).</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -18028,32 +18028,32 @@
       </c>
       <c r="AP61" s="24" t="inlineStr">
         <is>
-          <t>Maddison Inglis</t>
+          <t>Himeno Sakatsume</t>
         </is>
       </c>
       <c r="AQ61" s="24" t="inlineStr">
         <is>
-          <t>Maddison Inglis</t>
+          <t>Himeno Sakatsume</t>
         </is>
       </c>
       <c r="AR61" s="24" t="inlineStr">
         <is>
-          <t>Maddison Inglis</t>
+          <t>Himeno Sakatsume</t>
         </is>
       </c>
       <c r="AS61" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Mai Hontama</t>
         </is>
       </c>
       <c r="AT61" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Mai Hontama</t>
         </is>
       </c>
       <c r="AU61" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Mai Hontama</t>
         </is>
       </c>
       <c r="AV61" s="24" t="n"/>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:54.280361Z</t>
+          <t>2026-07-30T17:17:54.938784Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -18116,13 +18116,13 @@
       </c>
       <c r="BJ61" s="25" t="n"/>
       <c r="BK61" s="26" t="n">
-        <v>-138</v>
+        <v>113</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.13</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.469484</v>
       </c>
       <c r="BN61" s="28" t="n"/>
       <c r="BO61" s="28" t="n"/>
@@ -18156,22 +18156,22 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>f35e3073d6c842fd</t>
+          <t>d76b851d49ea4089</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:53:01.133141Z</t>
+          <t>2026-07-30T17:20:01.182496Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T19:30Z</t>
+          <t>2026-07-30T18:30Z</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>875-2026:179557</t>
+          <t>875-2026:179559</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -18181,12 +18181,12 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Taylah Preston</t>
+          <t>Maddison Inglis</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>Harriet Dart</t>
+          <t>Moyuka Uchijima</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J62" s="25" t="n"/>
@@ -18206,25 +18206,25 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>-117</v>
+        <v>-138</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.724638</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.579832</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.532721</v>
+        <v>0.555657</v>
       </c>
       <c r="P62" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q62" s="28" t="n">
-        <v>-0.00645</v>
+        <v>-0.024175</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S62" s="29" t="n">
         <v>0</v>
@@ -18250,7 +18250,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Taylah Preston p=0.533 vs Harriet Dart. Executable ask 0.5400 (aec-wta-hardar-taypre-2026-07-31).</t>
+          <t>Surface-blended Elo on Hard: Maddison Inglis p=0.444 vs Moyuka Uchijima. Executable ask 0.5800 (aec-wta-moyuch-mading-2026-07-30).</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -18291,32 +18291,32 @@
       </c>
       <c r="AP62" s="24" t="inlineStr">
         <is>
-          <t>Taylah Preston</t>
+          <t>Maddison Inglis</t>
         </is>
       </c>
       <c r="AQ62" s="24" t="inlineStr">
         <is>
-          <t>Taylah Preston</t>
+          <t>Maddison Inglis</t>
         </is>
       </c>
       <c r="AR62" s="24" t="inlineStr">
         <is>
-          <t>Taylah Preston</t>
+          <t>Maddison Inglis</t>
         </is>
       </c>
       <c r="AS62" s="24" t="inlineStr">
         <is>
-          <t>Harriet Dart</t>
+          <t>Moyuka Uchijima</t>
         </is>
       </c>
       <c r="AT62" s="24" t="inlineStr">
         <is>
-          <t>Harriet Dart</t>
+          <t>Moyuka Uchijima</t>
         </is>
       </c>
       <c r="AU62" s="24" t="inlineStr">
         <is>
-          <t>Harriet Dart</t>
+          <t>Moyuka Uchijima</t>
         </is>
       </c>
       <c r="AV62" s="24" t="n"/>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:57.860934Z</t>
+          <t>2026-07-30T17:17:54.997326Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -18379,13 +18379,13 @@
       </c>
       <c r="BJ62" s="25" t="n"/>
       <c r="BK62" s="26" t="n">
-        <v>-117</v>
+        <v>-138</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.724638</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.579832</v>
       </c>
       <c r="BN62" s="28" t="n"/>
       <c r="BO62" s="28" t="n"/>
@@ -18419,22 +18419,22 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>6d53fafea44848d1</t>
+          <t>1a576638a4ac430f</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:53:01.133141Z</t>
+          <t>2026-07-30T17:20:01.182496Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:00Z</t>
+          <t>2026-07-30T19:30Z</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>888-2026:179021</t>
+          <t>875-2026:179557</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
@@ -18444,12 +18444,12 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>Anna Kalinskaya</t>
+          <t>Taylah Preston</t>
         </is>
       </c>
       <c r="G63" s="24" t="inlineStr">
         <is>
-          <t>Janice Tjen</t>
+          <t>Harriet Dart</t>
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr">
@@ -18469,25 +18469,25 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>-257</v>
+        <v>-117</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.854701</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.539171</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.711749</v>
+        <v>0.532721</v>
       </c>
       <c r="P63" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q63" s="28" t="n">
-        <v>-0.008139</v>
+        <v>-0.00645</v>
       </c>
       <c r="R63" s="26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S63" s="29" t="n">
         <v>0</v>
@@ -18513,7 +18513,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Anna Kalinskaya p=0.712 vs Janice Tjen. Executable ask 0.7200 (aec-wta-jantje-annkal-2026-07-29).</t>
+          <t>Surface-blended Elo on Hard: Taylah Preston p=0.533 vs Harriet Dart. Executable ask 0.5400 (aec-wta-hardar-taypre-2026-07-31).</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -18554,32 +18554,32 @@
       </c>
       <c r="AP63" s="24" t="inlineStr">
         <is>
-          <t>Anna Kalinskaya</t>
+          <t>Taylah Preston</t>
         </is>
       </c>
       <c r="AQ63" s="24" t="inlineStr">
         <is>
-          <t>Anna Kalinskaya</t>
+          <t>Taylah Preston</t>
         </is>
       </c>
       <c r="AR63" s="24" t="inlineStr">
         <is>
-          <t>Anna Kalinskaya</t>
+          <t>Taylah Preston</t>
         </is>
       </c>
       <c r="AS63" s="24" t="inlineStr">
         <is>
-          <t>Janice Tjen</t>
+          <t>Harriet Dart</t>
         </is>
       </c>
       <c r="AT63" s="24" t="inlineStr">
         <is>
-          <t>Janice Tjen</t>
+          <t>Harriet Dart</t>
         </is>
       </c>
       <c r="AU63" s="24" t="inlineStr">
         <is>
-          <t>Janice Tjen</t>
+          <t>Harriet Dart</t>
         </is>
       </c>
       <c r="AV63" s="24" t="n"/>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:51.570342Z</t>
+          <t>2026-07-30T17:17:58.851659Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -18642,13 +18642,13 @@
       </c>
       <c r="BJ63" s="25" t="n"/>
       <c r="BK63" s="26" t="n">
-        <v>-257</v>
+        <v>-117</v>
       </c>
       <c r="BL63" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.854701</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.539171</v>
       </c>
       <c r="BN63" s="28" t="n"/>
       <c r="BO63" s="28" t="n"/>
@@ -18682,12 +18682,12 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>b5387a45b35b4e37</t>
+          <t>86ac38977bd34407</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:53:01.133141Z</t>
+          <t>2026-07-30T17:20:01.182496Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:57.307878Z</t>
+          <t>2026-07-30T17:17:57.813995Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -18945,12 +18945,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>af2b4842e42d4fad</t>
+          <t>94098b44e1f544b9</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:53:01.133141Z</t>
+          <t>2026-07-30T17:20:01.182496Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:59.004241Z</t>
+          <t>2026-07-30T17:17:59.424416Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19208,12 +19208,12 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>c99c72b897134bb4</t>
+          <t>cd3c6788cca84289</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:53:01.133141Z</t>
+          <t>2026-07-30T17:20:01.182496Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19421,7 +19421,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:51:02.877395Z</t>
+          <t>2026-07-30T17:18:03.684187Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19471,12 +19471,12 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>a93b466b52d2440c</t>
+          <t>494e50bcd2bb4f02</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:53:01.133141Z</t>
+          <t>2026-07-30T17:20:01.182496Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -19521,13 +19521,13 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.613497</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.619772</v>
       </c>
       <c r="O67" s="28" t="n">
         <v>0.519871</v>
@@ -19536,7 +19536,7 @@
         <v>0.05</v>
       </c>
       <c r="Q67" s="28" t="n">
-        <v>-0.089504</v>
+        <v>-0.099901</v>
       </c>
       <c r="R67" s="26" t="n">
         <v>0</v>
@@ -19565,7 +19565,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Peyton Stearns p=0.520 vs Tatiana Prozorova. Executable ask 0.6100 (aec-wta-tatpro-peyste-2026-07-30).</t>
+          <t>Surface-blended Elo on Hard: Peyton Stearns p=0.520 vs Tatiana Prozorova. Executable ask 0.6200 (aec-wta-tatpro-peyste-2026-07-30).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:55.780992Z</t>
+          <t>2026-07-30T17:17:56.374384Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -19694,13 +19694,13 @@
       </c>
       <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.613497</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.619772</v>
       </c>
       <c r="BN67" s="28" t="n"/>
       <c r="BO67" s="28" t="n"/>
@@ -19734,12 +19734,12 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>acb27a67504e4849</t>
+          <t>16c0c563ecfc49c4</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:53:01.133141Z</t>
+          <t>2026-07-30T17:20:01.182496Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:51:01.079825Z</t>
+          <t>2026-07-30T17:18:02.129419Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -17893,12 +17893,12 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>a83cffe8daa44cf6</t>
+          <t>7c0cf703c2d9484e</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:20:01.182496Z</t>
+          <t>2026-07-30T17:37:43.528029Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:54.938784Z</t>
+          <t>2026-07-30T17:35:52.310964Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -18156,12 +18156,12 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>d76b851d49ea4089</t>
+          <t>f437f6de19cd4aed</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:20:01.182496Z</t>
+          <t>2026-07-30T17:37:43.528029Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:54.997326Z</t>
+          <t>2026-07-30T17:35:52.319608Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -18419,12 +18419,12 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>1a576638a4ac430f</t>
+          <t>c7d10b6b4dac4a9a</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:20:01.182496Z</t>
+          <t>2026-07-30T17:37:43.528029Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:58.851659Z</t>
+          <t>2026-07-30T17:35:56.111877Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -18682,12 +18682,12 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>86ac38977bd34407</t>
+          <t>c5ea892809844fc3</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:20:01.182496Z</t>
+          <t>2026-07-30T17:37:43.528029Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:57.813995Z</t>
+          <t>2026-07-30T17:35:52.888748Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -18945,12 +18945,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>94098b44e1f544b9</t>
+          <t>a5c6d08e438f42c4</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:20:01.182496Z</t>
+          <t>2026-07-30T17:37:43.528029Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:59.424416Z</t>
+          <t>2026-07-30T17:35:56.334866Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19208,12 +19208,12 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>cd3c6788cca84289</t>
+          <t>8d7b4698b06b484f</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:20:01.182496Z</t>
+          <t>2026-07-30T17:37:43.528029Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19421,7 +19421,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:18:03.684187Z</t>
+          <t>2026-07-30T17:36:00.484154Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19471,17 +19471,17 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>494e50bcd2bb4f02</t>
+          <t>f0a46e785b174dc0</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:20:01.182496Z</t>
+          <t>2026-07-30T17:37:43.528029Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T19:00Z</t>
+          <t>2026-07-30T19:15Z</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:56.374384Z</t>
+          <t>2026-07-30T17:35:55.334191Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -19734,12 +19734,12 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>16c0c563ecfc49c4</t>
+          <t>885f2c657bf548f5</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:20:01.182496Z</t>
+          <t>2026-07-30T17:37:43.528029Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -19784,13 +19784,13 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="M68" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="O68" s="28" t="n">
         <v>0.715942</v>
@@ -19799,10 +19799,10 @@
         <v>0.05</v>
       </c>
       <c r="Q68" s="28" t="n">
-        <v>0.106567</v>
+        <v>0.115942</v>
       </c>
       <c r="R68" s="26" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="S68" s="29" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.716 vs Sloane Stephens. Executable ask 0.6100 (aec-wta-sloste-darvid-2026-07-30).</t>
+          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.716 vs Sloane Stephens. Executable ask 0.6000 (aec-wta-sloste-darvid-2026-07-30).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:18:02.129419Z</t>
+          <t>2026-07-30T17:35:59.148966Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -19957,13 +19957,13 @@
       </c>
       <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="BL68" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="BN68" s="28" t="n"/>
       <c r="BO68" s="28" t="n"/>

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO99" headerRowCount="1">
-  <autoFilter ref="A1:CO99"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO114" headerRowCount="1">
+  <autoFilter ref="A1:CO114"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$99)</f>
+        <f>COUNTA('Picks'!$A$2:$A$114)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$99,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$114,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$99,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$114,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$99,"settled",'Picks'!$V$2:$V$99,"win")+COUNTIFS('Picks'!$U$2:$U$99,"settled",'Picks'!$V$2:$V$99,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"win")+COUNTIFS('Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$99,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$114,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$99,"&gt;0",'Picks'!$V$2:$V$99,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$99,"&gt;0",'Picks'!$V$2:$V$99,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$99,"&gt;0",'Picks'!$V$2:$V$99,"win")/(COUNTIFS('Picks'!$BX$2:$BX$99,"&gt;0",'Picks'!$V$2:$V$99,"win")+COUNTIFS('Picks'!$BX$2:$BX$99,"&gt;0",'Picks'!$V$2:$V$99,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"win")/(COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"win")+COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$99)/SUM('Picks'!$BX$2:$BX$99),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$114)/SUM('Picks'!$BX$2:$BX$114),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$99)</f>
+        <f>SUM('Picks'!$BY$2:$BY$114)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$99,"&lt;&gt;",'Picks'!$AB$2:$AB$99),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$114,"&lt;&gt;",'Picks'!$AB$2:$AB$114),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$99,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$99,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$114,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$114,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$99,'Picks'!$AM$2:$AM$99,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$114,'Picks'!$AM$2:$AM$114,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A14,'Picks'!$U$2:$U$99,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A14,'Picks'!$U$2:$U$114,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A14,'Picks'!$U$2:$U$99,"settled",'Picks'!$V$2:$V$99,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A14,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A14,'Picks'!$U$2:$U$99,"settled",'Picks'!$V$2:$V$99,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A14,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$99,'Picks'!$H$2:$H$99,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$114,'Picks'!$H$2:$H$114,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$99,'Picks'!$H$2:$H$99,$A14,'Picks'!$U$2:$U$99,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$114,'Picks'!$H$2:$H$114,$A14,'Picks'!$U$2:$U$114,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A15,'Picks'!$U$2:$U$99,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A15,'Picks'!$U$2:$U$114,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A15,'Picks'!$U$2:$U$99,"settled",'Picks'!$V$2:$V$99,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A15,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A15,'Picks'!$U$2:$U$99,"settled",'Picks'!$V$2:$V$99,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A15,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$99,'Picks'!$H$2:$H$99,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$114,'Picks'!$H$2:$H$114,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$99,'Picks'!$H$2:$H$99,$A15,'Picks'!$U$2:$U$99,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$114,'Picks'!$H$2:$H$114,$A15,'Picks'!$U$2:$U$114,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A16,'Picks'!$U$2:$U$99,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A16,'Picks'!$U$2:$U$114,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A16,'Picks'!$U$2:$U$99,"settled",'Picks'!$V$2:$V$99,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A16,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$99,$A16,'Picks'!$U$2:$U$99,"settled",'Picks'!$V$2:$V$99,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$114,$A16,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$99,'Picks'!$H$2:$H$99,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$114,'Picks'!$H$2:$H$114,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$99,'Picks'!$H$2:$H$99,$A16,'Picks'!$U$2:$U$99,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$114,'Picks'!$H$2:$H$114,$A16,'Picks'!$U$2:$U$114,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO99"/>
+  <dimension ref="A1:CO114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -27966,18 +27966,38 @@
       </c>
       <c r="U96" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V96" s="24" t="n"/>
-      <c r="W96" s="26" t="n"/>
-      <c r="X96" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V96" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W96" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y96" s="25" t="n"/>
-      <c r="Z96" s="26" t="n"/>
-      <c r="AA96" s="28" t="n"/>
-      <c r="AB96" s="28" t="n"/>
-      <c r="AC96" s="30" t="n"/>
-      <c r="AD96" s="24" t="n"/>
+      <c r="Z96" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA96" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB96" s="28" t="n">
+        <v>-0.000815</v>
+      </c>
+      <c r="AC96" s="30" t="n">
+        <v>1.1278</v>
+      </c>
+      <c r="AD96" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-01T23:51:12.440117Z</t>
+        </is>
+      </c>
       <c r="AE96" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Renata Zarazua p=0.357 vs Darja Vidmanova. Executable ask 0.5700 (aec-wta-darvid-renzar-2026-08-01).</t>
@@ -28120,8 +28140,12 @@
       <c r="BN96" s="28" t="n"/>
       <c r="BO96" s="28" t="n"/>
       <c r="BP96" s="25" t="n"/>
-      <c r="BQ96" s="27" t="n"/>
-      <c r="BR96" s="28" t="n"/>
+      <c r="BQ96" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR96" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS96" s="28" t="n"/>
       <c r="BT96" s="28" t="n"/>
       <c r="BU96" s="25" t="n"/>
@@ -28229,18 +28253,38 @@
       </c>
       <c r="U97" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V97" s="24" t="n"/>
-      <c r="W97" s="26" t="n"/>
-      <c r="X97" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V97" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W97" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X97" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y97" s="25" t="n"/>
-      <c r="Z97" s="26" t="n"/>
-      <c r="AA97" s="28" t="n"/>
-      <c r="AB97" s="28" t="n"/>
-      <c r="AC97" s="30" t="n"/>
-      <c r="AD97" s="24" t="n"/>
+      <c r="Z97" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA97" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB97" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC97" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD97" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-01T23:51:12.837368Z</t>
+        </is>
+      </c>
       <c r="AE97" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Sloane Stephens p=0.457 vs Harriet Dart. Executable ask 0.5100 (aec-wta-hardar-sloste-2026-08-01).</t>
@@ -28253,7 +28297,7 @@
       </c>
       <c r="AG97" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH97" s="24" t="n"/>
@@ -28383,8 +28427,12 @@
       <c r="BN97" s="28" t="n"/>
       <c r="BO97" s="28" t="n"/>
       <c r="BP97" s="25" t="n"/>
-      <c r="BQ97" s="27" t="n"/>
-      <c r="BR97" s="28" t="n"/>
+      <c r="BQ97" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR97" s="28" t="n">
+        <v>0.51</v>
+      </c>
       <c r="BS97" s="28" t="n"/>
       <c r="BT97" s="28" t="n"/>
       <c r="BU97" s="25" t="n"/>
@@ -28492,18 +28540,38 @@
       </c>
       <c r="U98" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V98" s="24" t="n"/>
-      <c r="W98" s="26" t="n"/>
-      <c r="X98" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V98" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W98" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X98" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y98" s="25" t="n"/>
-      <c r="Z98" s="26" t="n"/>
-      <c r="AA98" s="28" t="n"/>
-      <c r="AB98" s="28" t="n"/>
-      <c r="AC98" s="30" t="n"/>
-      <c r="AD98" s="24" t="n"/>
+      <c r="Z98" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA98" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB98" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC98" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD98" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-01T23:51:13.253347Z</t>
+        </is>
+      </c>
       <c r="AE98" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Rebecca Sramkova p=0.409 vs Mananchaya Sawangkaew. Executable ask 0.5600 (aec-wta-mansaw-rebsra-2026-08-01).</t>
@@ -28516,7 +28584,7 @@
       </c>
       <c r="AG98" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH98" s="24" t="n"/>
@@ -28646,8 +28714,12 @@
       <c r="BN98" s="28" t="n"/>
       <c r="BO98" s="28" t="n"/>
       <c r="BP98" s="25" t="n"/>
-      <c r="BQ98" s="27" t="n"/>
-      <c r="BR98" s="28" t="n"/>
+      <c r="BQ98" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR98" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS98" s="28" t="n"/>
       <c r="BT98" s="28" t="n"/>
       <c r="BU98" s="25" t="n"/>
@@ -28675,22 +28747,22 @@
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>23137b824b764b3e</t>
+          <t>c4929eec2cb843fd</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:45.565672Z</t>
+          <t>2026-08-02T07:14:33.942118Z</t>
         </is>
       </c>
       <c r="C99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00Z</t>
+          <t>2026-08-02T16:00Z</t>
         </is>
       </c>
       <c r="D99" s="24" t="inlineStr">
         <is>
-          <t>1073-2026:179603</t>
+          <t>888-2026:179014</t>
         </is>
       </c>
       <c r="E99" s="24" t="inlineStr">
@@ -28700,12 +28772,12 @@
       </c>
       <c r="F99" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="G99" s="24" t="inlineStr">
         <is>
-          <t>Kaitlin Quevedo</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="H99" s="24" t="inlineStr">
@@ -28725,28 +28797,28 @@
         </is>
       </c>
       <c r="L99" s="26" t="n">
-        <v>-4900</v>
+        <v>-144</v>
       </c>
       <c r="M99" s="27" t="n">
-        <v>1.020408</v>
+        <v>1.694444</v>
       </c>
       <c r="N99" s="28" t="n">
-        <v>0.98</v>
+        <v>0.590164</v>
       </c>
       <c r="O99" s="28" t="n">
-        <v>0.608004</v>
+        <v>0.821797</v>
       </c>
       <c r="P99" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q99" s="28" t="n">
-        <v>-0.371996</v>
+        <v>0.231633</v>
       </c>
       <c r="R99" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S99" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T99" s="24" t="inlineStr">
         <is>
@@ -28769,7 +28841,7 @@
       <c r="AD99" s="24" t="n"/>
       <c r="AE99" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Laura Samson p=0.392 vs Kaitlin Quevedo. Executable ask 0.9800 (aec-wta-kaique-lausam-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Alexandra Eala p=0.178 vs Jessica Pegula. Executable ask 0.5900 (aec-wta-jespeg-aleeal-2026-08-02).</t>
         </is>
       </c>
       <c r="AF99" s="31" t="inlineStr">
@@ -28810,32 +28882,32 @@
       </c>
       <c r="AP99" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AQ99" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AR99" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AS99" s="24" t="inlineStr">
         <is>
-          <t>Kaitlin Quevedo</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AT99" s="24" t="inlineStr">
         <is>
-          <t>Kaitlin Quevedo</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AU99" s="24" t="inlineStr">
         <is>
-          <t>Kaitlin Quevedo</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AV99" s="24" t="n"/>
@@ -28888,7 +28960,7 @@
       </c>
       <c r="BH99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:33.986747Z</t>
+          <t>2026-08-02T07:11:40.150606Z</t>
         </is>
       </c>
       <c r="BI99" s="24" t="inlineStr">
@@ -28898,13 +28970,13 @@
       </c>
       <c r="BJ99" s="25" t="n"/>
       <c r="BK99" s="26" t="n">
-        <v>-4900</v>
+        <v>-144</v>
       </c>
       <c r="BL99" s="27" t="n">
-        <v>1.020408</v>
+        <v>1.694444</v>
       </c>
       <c r="BM99" s="28" t="n">
-        <v>0.98</v>
+        <v>0.590164</v>
       </c>
       <c r="BN99" s="28" t="n"/>
       <c r="BO99" s="28" t="n"/>
@@ -28935,6 +29007,3951 @@
       <c r="CN99" s="24" t="n"/>
       <c r="CO99" s="24" t="n"/>
     </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="24" t="inlineStr">
+        <is>
+          <t>e5310e100d614eca</t>
+        </is>
+      </c>
+      <c r="B100" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C100" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="D100" s="24" t="inlineStr">
+        <is>
+          <t>1067-2026:179469</t>
+        </is>
+      </c>
+      <c r="E100" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F100" s="24" t="inlineStr">
+        <is>
+          <t>Darja Vidmanova</t>
+        </is>
+      </c>
+      <c r="G100" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="H100" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I100" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J100" s="25" t="n"/>
+      <c r="K100" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L100" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M100" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N100" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O100" s="28" t="n">
+        <v>0.639939</v>
+      </c>
+      <c r="P100" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q100" s="28" t="n">
+        <v>0.109423</v>
+      </c>
+      <c r="R100" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S100" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T100" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U100" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V100" s="24" t="n"/>
+      <c r="W100" s="26" t="n"/>
+      <c r="X100" s="26" t="n"/>
+      <c r="Y100" s="25" t="n"/>
+      <c r="Z100" s="26" t="n"/>
+      <c r="AA100" s="28" t="n"/>
+      <c r="AB100" s="28" t="n"/>
+      <c r="AC100" s="30" t="n"/>
+      <c r="AD100" s="24" t="n"/>
+      <c r="AE100" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.5300 (aec-wta-kriliu-darvid-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF100" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG100" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH100" s="24" t="n"/>
+      <c r="AI100" s="31" t="n"/>
+      <c r="AJ100" s="31" t="n"/>
+      <c r="AK100" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL100" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM100" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN100" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO100" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP100" s="24" t="inlineStr">
+        <is>
+          <t>Darja Vidmanova</t>
+        </is>
+      </c>
+      <c r="AQ100" s="24" t="inlineStr">
+        <is>
+          <t>Darja Vidmanova</t>
+        </is>
+      </c>
+      <c r="AR100" s="24" t="inlineStr">
+        <is>
+          <t>Darja Vidmanova</t>
+        </is>
+      </c>
+      <c r="AS100" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AT100" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AU100" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AV100" s="24" t="n"/>
+      <c r="AW100" s="24" t="n"/>
+      <c r="AX100" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY100" s="24" t="n"/>
+      <c r="AZ100" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA100" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB100" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC100" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD100" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE100" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF100" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG100" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH100" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:33.217270Z</t>
+        </is>
+      </c>
+      <c r="BI100" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ100" s="25" t="n"/>
+      <c r="BK100" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL100" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM100" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN100" s="28" t="n"/>
+      <c r="BO100" s="28" t="n"/>
+      <c r="BP100" s="25" t="n"/>
+      <c r="BQ100" s="27" t="n"/>
+      <c r="BR100" s="28" t="n"/>
+      <c r="BS100" s="28" t="n"/>
+      <c r="BT100" s="28" t="n"/>
+      <c r="BU100" s="25" t="n"/>
+      <c r="BV100" s="29" t="n"/>
+      <c r="BW100" s="24" t="n"/>
+      <c r="BX100" s="30" t="n"/>
+      <c r="BY100" s="27" t="n"/>
+      <c r="BZ100" s="24" t="n"/>
+      <c r="CA100" s="31" t="n"/>
+      <c r="CB100" s="24" t="n"/>
+      <c r="CC100" s="24" t="n"/>
+      <c r="CD100" s="24" t="n"/>
+      <c r="CE100" s="24" t="n"/>
+      <c r="CF100" s="24" t="n"/>
+      <c r="CG100" s="24" t="n"/>
+      <c r="CH100" s="24" t="n"/>
+      <c r="CI100" s="24" t="n"/>
+      <c r="CJ100" s="24" t="n"/>
+      <c r="CK100" s="24" t="n"/>
+      <c r="CL100" s="24" t="n"/>
+      <c r="CM100" s="24" t="n"/>
+      <c r="CN100" s="24" t="n"/>
+      <c r="CO100" s="24" t="n"/>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="24" t="inlineStr">
+        <is>
+          <t>4154cdee02b44038</t>
+        </is>
+      </c>
+      <c r="B101" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C101" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00Z</t>
+        </is>
+      </c>
+      <c r="D101" s="24" t="inlineStr">
+        <is>
+          <t>1073-2026:179603</t>
+        </is>
+      </c>
+      <c r="E101" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F101" s="24" t="inlineStr">
+        <is>
+          <t>Laura Samson</t>
+        </is>
+      </c>
+      <c r="G101" s="24" t="inlineStr">
+        <is>
+          <t>Kaitlin Quevedo</t>
+        </is>
+      </c>
+      <c r="H101" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I101" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J101" s="25" t="n"/>
+      <c r="K101" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L101" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M101" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N101" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O101" s="28" t="n">
+        <v>0.608004</v>
+      </c>
+      <c r="P101" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q101" s="28" t="n">
+        <v>0.037189</v>
+      </c>
+      <c r="R101" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="S101" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T101" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U101" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V101" s="24" t="n"/>
+      <c r="W101" s="26" t="n"/>
+      <c r="X101" s="26" t="n"/>
+      <c r="Y101" s="25" t="n"/>
+      <c r="Z101" s="26" t="n"/>
+      <c r="AA101" s="28" t="n"/>
+      <c r="AB101" s="28" t="n"/>
+      <c r="AC101" s="30" t="n"/>
+      <c r="AD101" s="24" t="n"/>
+      <c r="AE101" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Laura Samson p=0.392 vs Kaitlin Quevedo. Executable ask 0.5700 (aec-wta-kaique-lausam-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF101" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG101" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH101" s="24" t="n"/>
+      <c r="AI101" s="31" t="n"/>
+      <c r="AJ101" s="31" t="n"/>
+      <c r="AK101" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL101" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM101" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN101" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO101" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP101" s="24" t="inlineStr">
+        <is>
+          <t>Laura Samson</t>
+        </is>
+      </c>
+      <c r="AQ101" s="24" t="inlineStr">
+        <is>
+          <t>Laura Samson</t>
+        </is>
+      </c>
+      <c r="AR101" s="24" t="inlineStr">
+        <is>
+          <t>Laura Samson</t>
+        </is>
+      </c>
+      <c r="AS101" s="24" t="inlineStr">
+        <is>
+          <t>Kaitlin Quevedo</t>
+        </is>
+      </c>
+      <c r="AT101" s="24" t="inlineStr">
+        <is>
+          <t>Kaitlin Quevedo</t>
+        </is>
+      </c>
+      <c r="AU101" s="24" t="inlineStr">
+        <is>
+          <t>Kaitlin Quevedo</t>
+        </is>
+      </c>
+      <c r="AV101" s="24" t="n"/>
+      <c r="AW101" s="24" t="n"/>
+      <c r="AX101" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY101" s="24" t="n"/>
+      <c r="AZ101" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA101" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB101" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC101" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD101" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE101" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF101" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG101" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH101" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:31.826745Z</t>
+        </is>
+      </c>
+      <c r="BI101" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ101" s="25" t="n"/>
+      <c r="BK101" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL101" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM101" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN101" s="28" t="n"/>
+      <c r="BO101" s="28" t="n"/>
+      <c r="BP101" s="25" t="n"/>
+      <c r="BQ101" s="27" t="n"/>
+      <c r="BR101" s="28" t="n"/>
+      <c r="BS101" s="28" t="n"/>
+      <c r="BT101" s="28" t="n"/>
+      <c r="BU101" s="25" t="n"/>
+      <c r="BV101" s="29" t="n"/>
+      <c r="BW101" s="24" t="n"/>
+      <c r="BX101" s="30" t="n"/>
+      <c r="BY101" s="27" t="n"/>
+      <c r="BZ101" s="24" t="n"/>
+      <c r="CA101" s="31" t="n"/>
+      <c r="CB101" s="24" t="n"/>
+      <c r="CC101" s="24" t="n"/>
+      <c r="CD101" s="24" t="n"/>
+      <c r="CE101" s="24" t="n"/>
+      <c r="CF101" s="24" t="n"/>
+      <c r="CG101" s="24" t="n"/>
+      <c r="CH101" s="24" t="n"/>
+      <c r="CI101" s="24" t="n"/>
+      <c r="CJ101" s="24" t="n"/>
+      <c r="CK101" s="24" t="n"/>
+      <c r="CL101" s="24" t="n"/>
+      <c r="CM101" s="24" t="n"/>
+      <c r="CN101" s="24" t="n"/>
+      <c r="CO101" s="24" t="n"/>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="24" t="inlineStr">
+        <is>
+          <t>c81c82bfba664c2f</t>
+        </is>
+      </c>
+      <c r="B102" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:30Z</t>
+        </is>
+      </c>
+      <c r="D102" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182259</t>
+        </is>
+      </c>
+      <c r="E102" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F102" s="24" t="inlineStr">
+        <is>
+          <t>Viktorija Golubic</t>
+        </is>
+      </c>
+      <c r="G102" s="24" t="inlineStr">
+        <is>
+          <t>Kimberly Birrell</t>
+        </is>
+      </c>
+      <c r="H102" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I102" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J102" s="25" t="n"/>
+      <c r="K102" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L102" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M102" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N102" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O102" s="28" t="n">
+        <v>0.530496</v>
+      </c>
+      <c r="P102" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q102" s="28" t="n">
+        <v>0.020692</v>
+      </c>
+      <c r="R102" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S102" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U102" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V102" s="24" t="n"/>
+      <c r="W102" s="26" t="n"/>
+      <c r="X102" s="26" t="n"/>
+      <c r="Y102" s="25" t="n"/>
+      <c r="Z102" s="26" t="n"/>
+      <c r="AA102" s="28" t="n"/>
+      <c r="AB102" s="28" t="n"/>
+      <c r="AC102" s="30" t="n"/>
+      <c r="AD102" s="24" t="n"/>
+      <c r="AE102" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Viktorija Golubic p=0.470 vs Kimberly Birrell. Executable ask 0.5100 (aec-wta-kimbir-vikgol-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF102" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG102" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH102" s="24" t="n"/>
+      <c r="AI102" s="31" t="n"/>
+      <c r="AJ102" s="31" t="n"/>
+      <c r="AK102" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL102" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM102" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN102" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO102" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP102" s="24" t="inlineStr">
+        <is>
+          <t>Viktorija Golubic</t>
+        </is>
+      </c>
+      <c r="AQ102" s="24" t="inlineStr">
+        <is>
+          <t>Viktorija Golubic</t>
+        </is>
+      </c>
+      <c r="AR102" s="24" t="inlineStr">
+        <is>
+          <t>Viktorija Golubic</t>
+        </is>
+      </c>
+      <c r="AS102" s="24" t="inlineStr">
+        <is>
+          <t>Kimberly Birrell</t>
+        </is>
+      </c>
+      <c r="AT102" s="24" t="inlineStr">
+        <is>
+          <t>Kimberly Birrell</t>
+        </is>
+      </c>
+      <c r="AU102" s="24" t="inlineStr">
+        <is>
+          <t>Kimberly Birrell</t>
+        </is>
+      </c>
+      <c r="AV102" s="24" t="n"/>
+      <c r="AW102" s="24" t="n"/>
+      <c r="AX102" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY102" s="24" t="n"/>
+      <c r="AZ102" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA102" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB102" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC102" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD102" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE102" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF102" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG102" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH102" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:32.750457Z</t>
+        </is>
+      </c>
+      <c r="BI102" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ102" s="25" t="n"/>
+      <c r="BK102" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL102" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM102" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN102" s="28" t="n"/>
+      <c r="BO102" s="28" t="n"/>
+      <c r="BP102" s="25" t="n"/>
+      <c r="BQ102" s="27" t="n"/>
+      <c r="BR102" s="28" t="n"/>
+      <c r="BS102" s="28" t="n"/>
+      <c r="BT102" s="28" t="n"/>
+      <c r="BU102" s="25" t="n"/>
+      <c r="BV102" s="29" t="n"/>
+      <c r="BW102" s="24" t="n"/>
+      <c r="BX102" s="30" t="n"/>
+      <c r="BY102" s="27" t="n"/>
+      <c r="BZ102" s="24" t="n"/>
+      <c r="CA102" s="31" t="n"/>
+      <c r="CB102" s="24" t="n"/>
+      <c r="CC102" s="24" t="n"/>
+      <c r="CD102" s="24" t="n"/>
+      <c r="CE102" s="24" t="n"/>
+      <c r="CF102" s="24" t="n"/>
+      <c r="CG102" s="24" t="n"/>
+      <c r="CH102" s="24" t="n"/>
+      <c r="CI102" s="24" t="n"/>
+      <c r="CJ102" s="24" t="n"/>
+      <c r="CK102" s="24" t="n"/>
+      <c r="CL102" s="24" t="n"/>
+      <c r="CM102" s="24" t="n"/>
+      <c r="CN102" s="24" t="n"/>
+      <c r="CO102" s="24" t="n"/>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="A103" s="24" t="inlineStr">
+        <is>
+          <t>10d15853ccd14c44</t>
+        </is>
+      </c>
+      <c r="B103" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:30Z</t>
+        </is>
+      </c>
+      <c r="D103" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182279</t>
+        </is>
+      </c>
+      <c r="E103" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F103" s="24" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="G103" s="24" t="inlineStr">
+        <is>
+          <t>Moyuka Uchijima</t>
+        </is>
+      </c>
+      <c r="H103" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I103" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J103" s="25" t="n"/>
+      <c r="K103" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L103" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M103" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N103" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O103" s="28" t="n">
+        <v>0.548768</v>
+      </c>
+      <c r="P103" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q103" s="28" t="n">
+        <v>-0.071004</v>
+      </c>
+      <c r="R103" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U103" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V103" s="24" t="n"/>
+      <c r="W103" s="26" t="n"/>
+      <c r="X103" s="26" t="n"/>
+      <c r="Y103" s="25" t="n"/>
+      <c r="Z103" s="26" t="n"/>
+      <c r="AA103" s="28" t="n"/>
+      <c r="AB103" s="28" t="n"/>
+      <c r="AC103" s="30" t="n"/>
+      <c r="AD103" s="24" t="n"/>
+      <c r="AE103" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Cristina Bucsa p=0.549 vs Moyuka Uchijima. Executable ask 0.6200 (aec-wta-moyuch-cribuc-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF103" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG103" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH103" s="24" t="n"/>
+      <c r="AI103" s="31" t="n"/>
+      <c r="AJ103" s="31" t="n"/>
+      <c r="AK103" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL103" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM103" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN103" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO103" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP103" s="24" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="AQ103" s="24" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="AR103" s="24" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="AS103" s="24" t="inlineStr">
+        <is>
+          <t>Moyuka Uchijima</t>
+        </is>
+      </c>
+      <c r="AT103" s="24" t="inlineStr">
+        <is>
+          <t>Moyuka Uchijima</t>
+        </is>
+      </c>
+      <c r="AU103" s="24" t="inlineStr">
+        <is>
+          <t>Moyuka Uchijima</t>
+        </is>
+      </c>
+      <c r="AV103" s="24" t="n"/>
+      <c r="AW103" s="24" t="n"/>
+      <c r="AX103" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY103" s="24" t="n"/>
+      <c r="AZ103" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA103" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB103" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC103" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD103" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE103" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF103" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG103" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH103" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:31.808862Z</t>
+        </is>
+      </c>
+      <c r="BI103" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ103" s="25" t="n"/>
+      <c r="BK103" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL103" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM103" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN103" s="28" t="n"/>
+      <c r="BO103" s="28" t="n"/>
+      <c r="BP103" s="25" t="n"/>
+      <c r="BQ103" s="27" t="n"/>
+      <c r="BR103" s="28" t="n"/>
+      <c r="BS103" s="28" t="n"/>
+      <c r="BT103" s="28" t="n"/>
+      <c r="BU103" s="25" t="n"/>
+      <c r="BV103" s="29" t="n"/>
+      <c r="BW103" s="24" t="n"/>
+      <c r="BX103" s="30" t="n"/>
+      <c r="BY103" s="27" t="n"/>
+      <c r="BZ103" s="24" t="n"/>
+      <c r="CA103" s="31" t="n"/>
+      <c r="CB103" s="24" t="n"/>
+      <c r="CC103" s="24" t="n"/>
+      <c r="CD103" s="24" t="n"/>
+      <c r="CE103" s="24" t="n"/>
+      <c r="CF103" s="24" t="n"/>
+      <c r="CG103" s="24" t="n"/>
+      <c r="CH103" s="24" t="n"/>
+      <c r="CI103" s="24" t="n"/>
+      <c r="CJ103" s="24" t="n"/>
+      <c r="CK103" s="24" t="n"/>
+      <c r="CL103" s="24" t="n"/>
+      <c r="CM103" s="24" t="n"/>
+      <c r="CN103" s="24" t="n"/>
+      <c r="CO103" s="24" t="n"/>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="24" t="inlineStr">
+        <is>
+          <t>aadb962e8e0249ca</t>
+        </is>
+      </c>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:30Z</t>
+        </is>
+      </c>
+      <c r="D104" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182280</t>
+        </is>
+      </c>
+      <c r="E104" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F104" s="24" t="inlineStr">
+        <is>
+          <t>Sara Bejlek</t>
+        </is>
+      </c>
+      <c r="G104" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xiyu</t>
+        </is>
+      </c>
+      <c r="H104" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I104" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J104" s="25" t="n"/>
+      <c r="K104" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L104" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M104" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N104" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O104" s="28" t="n">
+        <v>0.597848</v>
+      </c>
+      <c r="P104" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q104" s="28" t="n">
+        <v>-0.002152</v>
+      </c>
+      <c r="R104" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="S104" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T104" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U104" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V104" s="24" t="n"/>
+      <c r="W104" s="26" t="n"/>
+      <c r="X104" s="26" t="n"/>
+      <c r="Y104" s="25" t="n"/>
+      <c r="Z104" s="26" t="n"/>
+      <c r="AA104" s="28" t="n"/>
+      <c r="AB104" s="28" t="n"/>
+      <c r="AC104" s="30" t="n"/>
+      <c r="AD104" s="24" t="n"/>
+      <c r="AE104" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.6000 (aec-wta-xiywan-sarbej-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF104" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG104" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH104" s="24" t="n"/>
+      <c r="AI104" s="31" t="n"/>
+      <c r="AJ104" s="31" t="n"/>
+      <c r="AK104" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL104" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM104" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN104" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO104" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP104" s="24" t="inlineStr">
+        <is>
+          <t>Sara Bejlek</t>
+        </is>
+      </c>
+      <c r="AQ104" s="24" t="inlineStr">
+        <is>
+          <t>Sara Bejlek</t>
+        </is>
+      </c>
+      <c r="AR104" s="24" t="inlineStr">
+        <is>
+          <t>Sara Bejlek</t>
+        </is>
+      </c>
+      <c r="AS104" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xiyu</t>
+        </is>
+      </c>
+      <c r="AT104" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xiyu</t>
+        </is>
+      </c>
+      <c r="AU104" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xiyu</t>
+        </is>
+      </c>
+      <c r="AV104" s="24" t="n"/>
+      <c r="AW104" s="24" t="n"/>
+      <c r="AX104" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY104" s="24" t="n"/>
+      <c r="AZ104" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA104" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB104" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC104" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD104" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE104" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF104" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG104" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH104" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:31.845281Z</t>
+        </is>
+      </c>
+      <c r="BI104" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ104" s="25" t="n"/>
+      <c r="BK104" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL104" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM104" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN104" s="28" t="n"/>
+      <c r="BO104" s="28" t="n"/>
+      <c r="BP104" s="25" t="n"/>
+      <c r="BQ104" s="27" t="n"/>
+      <c r="BR104" s="28" t="n"/>
+      <c r="BS104" s="28" t="n"/>
+      <c r="BT104" s="28" t="n"/>
+      <c r="BU104" s="25" t="n"/>
+      <c r="BV104" s="29" t="n"/>
+      <c r="BW104" s="24" t="n"/>
+      <c r="BX104" s="30" t="n"/>
+      <c r="BY104" s="27" t="n"/>
+      <c r="BZ104" s="24" t="n"/>
+      <c r="CA104" s="31" t="n"/>
+      <c r="CB104" s="24" t="n"/>
+      <c r="CC104" s="24" t="n"/>
+      <c r="CD104" s="24" t="n"/>
+      <c r="CE104" s="24" t="n"/>
+      <c r="CF104" s="24" t="n"/>
+      <c r="CG104" s="24" t="n"/>
+      <c r="CH104" s="24" t="n"/>
+      <c r="CI104" s="24" t="n"/>
+      <c r="CJ104" s="24" t="n"/>
+      <c r="CK104" s="24" t="n"/>
+      <c r="CL104" s="24" t="n"/>
+      <c r="CM104" s="24" t="n"/>
+      <c r="CN104" s="24" t="n"/>
+      <c r="CO104" s="24" t="n"/>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="24" t="inlineStr">
+        <is>
+          <t>f5c1adcfc0d34ca0</t>
+        </is>
+      </c>
+      <c r="B105" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C105" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D105" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182236</t>
+        </is>
+      </c>
+      <c r="E105" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F105" s="24" t="inlineStr">
+        <is>
+          <t>Leolia Jeanjean</t>
+        </is>
+      </c>
+      <c r="G105" s="24" t="inlineStr">
+        <is>
+          <t>Magdalena Frech</t>
+        </is>
+      </c>
+      <c r="H105" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I105" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J105" s="25" t="n"/>
+      <c r="K105" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L105" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M105" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N105" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O105" s="28" t="n">
+        <v>0.504343</v>
+      </c>
+      <c r="P105" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q105" s="28" t="n">
+        <v>0.104343</v>
+      </c>
+      <c r="R105" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="S105" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U105" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V105" s="24" t="n"/>
+      <c r="W105" s="26" t="n"/>
+      <c r="X105" s="26" t="n"/>
+      <c r="Y105" s="25" t="n"/>
+      <c r="Z105" s="26" t="n"/>
+      <c r="AA105" s="28" t="n"/>
+      <c r="AB105" s="28" t="n"/>
+      <c r="AC105" s="30" t="n"/>
+      <c r="AD105" s="24" t="n"/>
+      <c r="AE105" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Leolia Jeanjean p=0.504 vs Magdalena Frech. Executable ask 0.4000 (aec-wta-magfre-leojea-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF105" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG105" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH105" s="24" t="n"/>
+      <c r="AI105" s="31" t="n"/>
+      <c r="AJ105" s="31" t="n"/>
+      <c r="AK105" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL105" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM105" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN105" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO105" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP105" s="24" t="inlineStr">
+        <is>
+          <t>Leolia Jeanjean</t>
+        </is>
+      </c>
+      <c r="AQ105" s="24" t="inlineStr">
+        <is>
+          <t>Leolia Jeanjean</t>
+        </is>
+      </c>
+      <c r="AR105" s="24" t="inlineStr">
+        <is>
+          <t>Leolia Jeanjean</t>
+        </is>
+      </c>
+      <c r="AS105" s="24" t="inlineStr">
+        <is>
+          <t>Magdalena Frech</t>
+        </is>
+      </c>
+      <c r="AT105" s="24" t="inlineStr">
+        <is>
+          <t>Magdalena Frech</t>
+        </is>
+      </c>
+      <c r="AU105" s="24" t="inlineStr">
+        <is>
+          <t>Magdalena Frech</t>
+        </is>
+      </c>
+      <c r="AV105" s="24" t="n"/>
+      <c r="AW105" s="24" t="n"/>
+      <c r="AX105" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY105" s="24" t="n"/>
+      <c r="AZ105" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA105" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB105" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC105" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD105" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE105" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF105" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG105" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH105" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:35.341815Z</t>
+        </is>
+      </c>
+      <c r="BI105" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ105" s="25" t="n"/>
+      <c r="BK105" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL105" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM105" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN105" s="28" t="n"/>
+      <c r="BO105" s="28" t="n"/>
+      <c r="BP105" s="25" t="n"/>
+      <c r="BQ105" s="27" t="n"/>
+      <c r="BR105" s="28" t="n"/>
+      <c r="BS105" s="28" t="n"/>
+      <c r="BT105" s="28" t="n"/>
+      <c r="BU105" s="25" t="n"/>
+      <c r="BV105" s="29" t="n"/>
+      <c r="BW105" s="24" t="n"/>
+      <c r="BX105" s="30" t="n"/>
+      <c r="BY105" s="27" t="n"/>
+      <c r="BZ105" s="24" t="n"/>
+      <c r="CA105" s="31" t="n"/>
+      <c r="CB105" s="24" t="n"/>
+      <c r="CC105" s="24" t="n"/>
+      <c r="CD105" s="24" t="n"/>
+      <c r="CE105" s="24" t="n"/>
+      <c r="CF105" s="24" t="n"/>
+      <c r="CG105" s="24" t="n"/>
+      <c r="CH105" s="24" t="n"/>
+      <c r="CI105" s="24" t="n"/>
+      <c r="CJ105" s="24" t="n"/>
+      <c r="CK105" s="24" t="n"/>
+      <c r="CL105" s="24" t="n"/>
+      <c r="CM105" s="24" t="n"/>
+      <c r="CN105" s="24" t="n"/>
+      <c r="CO105" s="24" t="n"/>
+    </row>
+    <row r="106" ht="36" customHeight="1">
+      <c r="A106" s="24" t="inlineStr">
+        <is>
+          <t>84d2748d860a452d</t>
+        </is>
+      </c>
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182257</t>
+        </is>
+      </c>
+      <c r="E106" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F106" s="24" t="inlineStr">
+        <is>
+          <t>Antonia Ruzic</t>
+        </is>
+      </c>
+      <c r="G106" s="24" t="inlineStr">
+        <is>
+          <t>Lois Boisson</t>
+        </is>
+      </c>
+      <c r="H106" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I106" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J106" s="25" t="n"/>
+      <c r="K106" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L106" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M106" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N106" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O106" s="28" t="n">
+        <v>0.549832</v>
+      </c>
+      <c r="P106" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q106" s="28" t="n">
+        <v>-0.009639</v>
+      </c>
+      <c r="R106" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="S106" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U106" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V106" s="24" t="n"/>
+      <c r="W106" s="26" t="n"/>
+      <c r="X106" s="26" t="n"/>
+      <c r="Y106" s="25" t="n"/>
+      <c r="Z106" s="26" t="n"/>
+      <c r="AA106" s="28" t="n"/>
+      <c r="AB106" s="28" t="n"/>
+      <c r="AC106" s="30" t="n"/>
+      <c r="AD106" s="24" t="n"/>
+      <c r="AE106" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Antonia Ruzic p=0.550 vs Lois Boisson. Executable ask 0.5600 (aec-wta-loiboi-antruz-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF106" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG106" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH106" s="24" t="n"/>
+      <c r="AI106" s="31" t="n"/>
+      <c r="AJ106" s="31" t="n"/>
+      <c r="AK106" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL106" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM106" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN106" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO106" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP106" s="24" t="inlineStr">
+        <is>
+          <t>Antonia Ruzic</t>
+        </is>
+      </c>
+      <c r="AQ106" s="24" t="inlineStr">
+        <is>
+          <t>Antonia Ruzic</t>
+        </is>
+      </c>
+      <c r="AR106" s="24" t="inlineStr">
+        <is>
+          <t>Antonia Ruzic</t>
+        </is>
+      </c>
+      <c r="AS106" s="24" t="inlineStr">
+        <is>
+          <t>Lois Boisson</t>
+        </is>
+      </c>
+      <c r="AT106" s="24" t="inlineStr">
+        <is>
+          <t>Lois Boisson</t>
+        </is>
+      </c>
+      <c r="AU106" s="24" t="inlineStr">
+        <is>
+          <t>Lois Boisson</t>
+        </is>
+      </c>
+      <c r="AV106" s="24" t="n"/>
+      <c r="AW106" s="24" t="n"/>
+      <c r="AX106" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY106" s="24" t="n"/>
+      <c r="AZ106" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA106" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB106" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC106" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD106" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE106" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF106" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG106" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH106" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:35.998974Z</t>
+        </is>
+      </c>
+      <c r="BI106" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ106" s="25" t="n"/>
+      <c r="BK106" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL106" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM106" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN106" s="28" t="n"/>
+      <c r="BO106" s="28" t="n"/>
+      <c r="BP106" s="25" t="n"/>
+      <c r="BQ106" s="27" t="n"/>
+      <c r="BR106" s="28" t="n"/>
+      <c r="BS106" s="28" t="n"/>
+      <c r="BT106" s="28" t="n"/>
+      <c r="BU106" s="25" t="n"/>
+      <c r="BV106" s="29" t="n"/>
+      <c r="BW106" s="24" t="n"/>
+      <c r="BX106" s="30" t="n"/>
+      <c r="BY106" s="27" t="n"/>
+      <c r="BZ106" s="24" t="n"/>
+      <c r="CA106" s="31" t="n"/>
+      <c r="CB106" s="24" t="n"/>
+      <c r="CC106" s="24" t="n"/>
+      <c r="CD106" s="24" t="n"/>
+      <c r="CE106" s="24" t="n"/>
+      <c r="CF106" s="24" t="n"/>
+      <c r="CG106" s="24" t="n"/>
+      <c r="CH106" s="24" t="n"/>
+      <c r="CI106" s="24" t="n"/>
+      <c r="CJ106" s="24" t="n"/>
+      <c r="CK106" s="24" t="n"/>
+      <c r="CL106" s="24" t="n"/>
+      <c r="CM106" s="24" t="n"/>
+      <c r="CN106" s="24" t="n"/>
+      <c r="CO106" s="24" t="n"/>
+    </row>
+    <row r="107" ht="36" customHeight="1">
+      <c r="A107" s="24" t="inlineStr">
+        <is>
+          <t>64ef379ab18349f7</t>
+        </is>
+      </c>
+      <c r="B107" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C107" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D107" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182268</t>
+        </is>
+      </c>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F107" s="24" t="inlineStr">
+        <is>
+          <t>Katherine Sebov</t>
+        </is>
+      </c>
+      <c r="G107" s="24" t="inlineStr">
+        <is>
+          <t>Aoi Ito</t>
+        </is>
+      </c>
+      <c r="H107" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I107" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J107" s="25" t="n"/>
+      <c r="K107" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L107" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M107" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N107" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O107" s="28" t="n">
+        <v>0.52927</v>
+      </c>
+      <c r="P107" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q107" s="28" t="n">
+        <v>-0.07073</v>
+      </c>
+      <c r="R107" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U107" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V107" s="24" t="n"/>
+      <c r="W107" s="26" t="n"/>
+      <c r="X107" s="26" t="n"/>
+      <c r="Y107" s="25" t="n"/>
+      <c r="Z107" s="26" t="n"/>
+      <c r="AA107" s="28" t="n"/>
+      <c r="AB107" s="28" t="n"/>
+      <c r="AC107" s="30" t="n"/>
+      <c r="AD107" s="24" t="n"/>
+      <c r="AE107" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Katherine Sebov p=0.471 vs Aoi Ito. Executable ask 0.6000 (aec-wta-aoiito-katseb-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF107" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG107" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH107" s="24" t="n"/>
+      <c r="AI107" s="31" t="n"/>
+      <c r="AJ107" s="31" t="n"/>
+      <c r="AK107" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL107" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM107" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN107" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO107" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP107" s="24" t="inlineStr">
+        <is>
+          <t>Katherine Sebov</t>
+        </is>
+      </c>
+      <c r="AQ107" s="24" t="inlineStr">
+        <is>
+          <t>Katherine Sebov</t>
+        </is>
+      </c>
+      <c r="AR107" s="24" t="inlineStr">
+        <is>
+          <t>Katherine Sebov</t>
+        </is>
+      </c>
+      <c r="AS107" s="24" t="inlineStr">
+        <is>
+          <t>Aoi Ito</t>
+        </is>
+      </c>
+      <c r="AT107" s="24" t="inlineStr">
+        <is>
+          <t>Aoi Ito</t>
+        </is>
+      </c>
+      <c r="AU107" s="24" t="inlineStr">
+        <is>
+          <t>Aoi Ito</t>
+        </is>
+      </c>
+      <c r="AV107" s="24" t="n"/>
+      <c r="AW107" s="24" t="n"/>
+      <c r="AX107" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY107" s="24" t="n"/>
+      <c r="AZ107" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA107" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB107" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC107" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD107" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE107" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF107" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG107" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH107" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:37.008588Z</t>
+        </is>
+      </c>
+      <c r="BI107" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ107" s="25" t="n"/>
+      <c r="BK107" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL107" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM107" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN107" s="28" t="n"/>
+      <c r="BO107" s="28" t="n"/>
+      <c r="BP107" s="25" t="n"/>
+      <c r="BQ107" s="27" t="n"/>
+      <c r="BR107" s="28" t="n"/>
+      <c r="BS107" s="28" t="n"/>
+      <c r="BT107" s="28" t="n"/>
+      <c r="BU107" s="25" t="n"/>
+      <c r="BV107" s="29" t="n"/>
+      <c r="BW107" s="24" t="n"/>
+      <c r="BX107" s="30" t="n"/>
+      <c r="BY107" s="27" t="n"/>
+      <c r="BZ107" s="24" t="n"/>
+      <c r="CA107" s="31" t="n"/>
+      <c r="CB107" s="24" t="n"/>
+      <c r="CC107" s="24" t="n"/>
+      <c r="CD107" s="24" t="n"/>
+      <c r="CE107" s="24" t="n"/>
+      <c r="CF107" s="24" t="n"/>
+      <c r="CG107" s="24" t="n"/>
+      <c r="CH107" s="24" t="n"/>
+      <c r="CI107" s="24" t="n"/>
+      <c r="CJ107" s="24" t="n"/>
+      <c r="CK107" s="24" t="n"/>
+      <c r="CL107" s="24" t="n"/>
+      <c r="CM107" s="24" t="n"/>
+      <c r="CN107" s="24" t="n"/>
+      <c r="CO107" s="24" t="n"/>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="A108" s="24" t="inlineStr">
+        <is>
+          <t>99be0b0015e5439d</t>
+        </is>
+      </c>
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D108" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182284</t>
+        </is>
+      </c>
+      <c r="E108" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F108" s="24" t="inlineStr">
+        <is>
+          <t>Camila Osorio</t>
+        </is>
+      </c>
+      <c r="G108" s="24" t="inlineStr">
+        <is>
+          <t>Lucrezia Stefanini</t>
+        </is>
+      </c>
+      <c r="H108" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I108" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J108" s="25" t="n"/>
+      <c r="K108" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L108" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M108" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N108" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O108" s="28" t="n">
+        <v>0.736958</v>
+      </c>
+      <c r="P108" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q108" s="28" t="n">
+        <v>0.086608</v>
+      </c>
+      <c r="R108" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="S108" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U108" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V108" s="24" t="n"/>
+      <c r="W108" s="26" t="n"/>
+      <c r="X108" s="26" t="n"/>
+      <c r="Y108" s="25" t="n"/>
+      <c r="Z108" s="26" t="n"/>
+      <c r="AA108" s="28" t="n"/>
+      <c r="AB108" s="28" t="n"/>
+      <c r="AC108" s="30" t="n"/>
+      <c r="AD108" s="24" t="n"/>
+      <c r="AE108" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Camila Osorio p=0.737 vs Lucrezia Stefanini. Executable ask 0.6500 (aec-wta-lucste-camoso-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF108" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG108" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH108" s="24" t="n"/>
+      <c r="AI108" s="31" t="n"/>
+      <c r="AJ108" s="31" t="n"/>
+      <c r="AK108" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL108" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM108" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN108" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO108" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP108" s="24" t="inlineStr">
+        <is>
+          <t>Camila Osorio</t>
+        </is>
+      </c>
+      <c r="AQ108" s="24" t="inlineStr">
+        <is>
+          <t>Camila Osorio</t>
+        </is>
+      </c>
+      <c r="AR108" s="24" t="inlineStr">
+        <is>
+          <t>Camila Osorio</t>
+        </is>
+      </c>
+      <c r="AS108" s="24" t="inlineStr">
+        <is>
+          <t>Lucrezia Stefanini</t>
+        </is>
+      </c>
+      <c r="AT108" s="24" t="inlineStr">
+        <is>
+          <t>Lucrezia Stefanini</t>
+        </is>
+      </c>
+      <c r="AU108" s="24" t="inlineStr">
+        <is>
+          <t>Lucrezia Stefanini</t>
+        </is>
+      </c>
+      <c r="AV108" s="24" t="n"/>
+      <c r="AW108" s="24" t="n"/>
+      <c r="AX108" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY108" s="24" t="n"/>
+      <c r="AZ108" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA108" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB108" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC108" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD108" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE108" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF108" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG108" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH108" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:34.504805Z</t>
+        </is>
+      </c>
+      <c r="BI108" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ108" s="25" t="n"/>
+      <c r="BK108" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL108" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM108" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN108" s="28" t="n"/>
+      <c r="BO108" s="28" t="n"/>
+      <c r="BP108" s="25" t="n"/>
+      <c r="BQ108" s="27" t="n"/>
+      <c r="BR108" s="28" t="n"/>
+      <c r="BS108" s="28" t="n"/>
+      <c r="BT108" s="28" t="n"/>
+      <c r="BU108" s="25" t="n"/>
+      <c r="BV108" s="29" t="n"/>
+      <c r="BW108" s="24" t="n"/>
+      <c r="BX108" s="30" t="n"/>
+      <c r="BY108" s="27" t="n"/>
+      <c r="BZ108" s="24" t="n"/>
+      <c r="CA108" s="31" t="n"/>
+      <c r="CB108" s="24" t="n"/>
+      <c r="CC108" s="24" t="n"/>
+      <c r="CD108" s="24" t="n"/>
+      <c r="CE108" s="24" t="n"/>
+      <c r="CF108" s="24" t="n"/>
+      <c r="CG108" s="24" t="n"/>
+      <c r="CH108" s="24" t="n"/>
+      <c r="CI108" s="24" t="n"/>
+      <c r="CJ108" s="24" t="n"/>
+      <c r="CK108" s="24" t="n"/>
+      <c r="CL108" s="24" t="n"/>
+      <c r="CM108" s="24" t="n"/>
+      <c r="CN108" s="24" t="n"/>
+      <c r="CO108" s="24" t="n"/>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="A109" s="24" t="inlineStr">
+        <is>
+          <t>e7256f4701794fd3</t>
+        </is>
+      </c>
+      <c r="B109" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C109" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="D109" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182241</t>
+        </is>
+      </c>
+      <c r="E109" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F109" s="24" t="inlineStr">
+        <is>
+          <t>Anna Blinkova</t>
+        </is>
+      </c>
+      <c r="G109" s="24" t="inlineStr">
+        <is>
+          <t>Rebecca Sramkova</t>
+        </is>
+      </c>
+      <c r="H109" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I109" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J109" s="25" t="n"/>
+      <c r="K109" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L109" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M109" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N109" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O109" s="28" t="n">
+        <v>0.53051</v>
+      </c>
+      <c r="P109" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q109" s="28" t="n">
+        <v>0.011279</v>
+      </c>
+      <c r="R109" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S109" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U109" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V109" s="24" t="n"/>
+      <c r="W109" s="26" t="n"/>
+      <c r="X109" s="26" t="n"/>
+      <c r="Y109" s="25" t="n"/>
+      <c r="Z109" s="26" t="n"/>
+      <c r="AA109" s="28" t="n"/>
+      <c r="AB109" s="28" t="n"/>
+      <c r="AC109" s="30" t="n"/>
+      <c r="AD109" s="24" t="n"/>
+      <c r="AE109" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Anna Blinkova p=0.469 vs Rebecca Sramkova. Executable ask 0.5200 (aec-wta-rebsra-annbli-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF109" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG109" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH109" s="24" t="n"/>
+      <c r="AI109" s="31" t="n"/>
+      <c r="AJ109" s="31" t="n"/>
+      <c r="AK109" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL109" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM109" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN109" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO109" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP109" s="24" t="inlineStr">
+        <is>
+          <t>Anna Blinkova</t>
+        </is>
+      </c>
+      <c r="AQ109" s="24" t="inlineStr">
+        <is>
+          <t>Anna Blinkova</t>
+        </is>
+      </c>
+      <c r="AR109" s="24" t="inlineStr">
+        <is>
+          <t>Anna Blinkova</t>
+        </is>
+      </c>
+      <c r="AS109" s="24" t="inlineStr">
+        <is>
+          <t>Rebecca Sramkova</t>
+        </is>
+      </c>
+      <c r="AT109" s="24" t="inlineStr">
+        <is>
+          <t>Rebecca Sramkova</t>
+        </is>
+      </c>
+      <c r="AU109" s="24" t="inlineStr">
+        <is>
+          <t>Rebecca Sramkova</t>
+        </is>
+      </c>
+      <c r="AV109" s="24" t="n"/>
+      <c r="AW109" s="24" t="n"/>
+      <c r="AX109" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY109" s="24" t="n"/>
+      <c r="AZ109" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA109" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB109" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC109" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD109" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE109" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF109" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG109" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH109" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:37.841935Z</t>
+        </is>
+      </c>
+      <c r="BI109" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ109" s="25" t="n"/>
+      <c r="BK109" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL109" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM109" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN109" s="28" t="n"/>
+      <c r="BO109" s="28" t="n"/>
+      <c r="BP109" s="25" t="n"/>
+      <c r="BQ109" s="27" t="n"/>
+      <c r="BR109" s="28" t="n"/>
+      <c r="BS109" s="28" t="n"/>
+      <c r="BT109" s="28" t="n"/>
+      <c r="BU109" s="25" t="n"/>
+      <c r="BV109" s="29" t="n"/>
+      <c r="BW109" s="24" t="n"/>
+      <c r="BX109" s="30" t="n"/>
+      <c r="BY109" s="27" t="n"/>
+      <c r="BZ109" s="24" t="n"/>
+      <c r="CA109" s="31" t="n"/>
+      <c r="CB109" s="24" t="n"/>
+      <c r="CC109" s="24" t="n"/>
+      <c r="CD109" s="24" t="n"/>
+      <c r="CE109" s="24" t="n"/>
+      <c r="CF109" s="24" t="n"/>
+      <c r="CG109" s="24" t="n"/>
+      <c r="CH109" s="24" t="n"/>
+      <c r="CI109" s="24" t="n"/>
+      <c r="CJ109" s="24" t="n"/>
+      <c r="CK109" s="24" t="n"/>
+      <c r="CL109" s="24" t="n"/>
+      <c r="CM109" s="24" t="n"/>
+      <c r="CN109" s="24" t="n"/>
+      <c r="CO109" s="24" t="n"/>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="A110" s="24" t="inlineStr">
+        <is>
+          <t>1a8764981c564053</t>
+        </is>
+      </c>
+      <c r="B110" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F110" s="24" t="inlineStr">
+        <is>
+          <t>Lanlana Tararudee</t>
+        </is>
+      </c>
+      <c r="G110" s="24" t="inlineStr">
+        <is>
+          <t>Emerson Jones</t>
+        </is>
+      </c>
+      <c r="H110" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I110" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J110" s="25" t="n"/>
+      <c r="K110" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L110" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M110" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N110" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O110" s="28" t="n">
+        <v>0.756798</v>
+      </c>
+      <c r="P110" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q110" s="28" t="n">
+        <v>0.147423</v>
+      </c>
+      <c r="R110" s="26" t="n">
+        <v>94</v>
+      </c>
+      <c r="S110" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T110" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U110" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V110" s="24" t="n"/>
+      <c r="W110" s="26" t="n"/>
+      <c r="X110" s="26" t="n"/>
+      <c r="Y110" s="25" t="n"/>
+      <c r="Z110" s="26" t="n"/>
+      <c r="AA110" s="28" t="n"/>
+      <c r="AB110" s="28" t="n"/>
+      <c r="AC110" s="30" t="n"/>
+      <c r="AD110" s="24" t="n"/>
+      <c r="AE110" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6100 (aec-wta-emejon-lantar-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF110" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG110" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH110" s="24" t="n"/>
+      <c r="AI110" s="31" t="n"/>
+      <c r="AJ110" s="31" t="n"/>
+      <c r="AK110" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL110" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM110" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN110" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO110" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP110" s="24" t="inlineStr">
+        <is>
+          <t>Lanlana Tararudee</t>
+        </is>
+      </c>
+      <c r="AQ110" s="24" t="inlineStr">
+        <is>
+          <t>Lanlana Tararudee</t>
+        </is>
+      </c>
+      <c r="AR110" s="24" t="inlineStr">
+        <is>
+          <t>Lanlana Tararudee</t>
+        </is>
+      </c>
+      <c r="AS110" s="24" t="inlineStr">
+        <is>
+          <t>Emerson Jones</t>
+        </is>
+      </c>
+      <c r="AT110" s="24" t="inlineStr">
+        <is>
+          <t>Emerson Jones</t>
+        </is>
+      </c>
+      <c r="AU110" s="24" t="inlineStr">
+        <is>
+          <t>Emerson Jones</t>
+        </is>
+      </c>
+      <c r="AV110" s="24" t="n"/>
+      <c r="AW110" s="24" t="n"/>
+      <c r="AX110" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY110" s="24" t="n"/>
+      <c r="AZ110" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA110" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB110" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC110" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD110" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE110" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF110" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG110" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH110" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:38.720666Z</t>
+        </is>
+      </c>
+      <c r="BI110" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ110" s="25" t="n"/>
+      <c r="BK110" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL110" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM110" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN110" s="28" t="n"/>
+      <c r="BO110" s="28" t="n"/>
+      <c r="BP110" s="25" t="n"/>
+      <c r="BQ110" s="27" t="n"/>
+      <c r="BR110" s="28" t="n"/>
+      <c r="BS110" s="28" t="n"/>
+      <c r="BT110" s="28" t="n"/>
+      <c r="BU110" s="25" t="n"/>
+      <c r="BV110" s="29" t="n"/>
+      <c r="BW110" s="24" t="n"/>
+      <c r="BX110" s="30" t="n"/>
+      <c r="BY110" s="27" t="n"/>
+      <c r="BZ110" s="24" t="n"/>
+      <c r="CA110" s="31" t="n"/>
+      <c r="CB110" s="24" t="n"/>
+      <c r="CC110" s="24" t="n"/>
+      <c r="CD110" s="24" t="n"/>
+      <c r="CE110" s="24" t="n"/>
+      <c r="CF110" s="24" t="n"/>
+      <c r="CG110" s="24" t="n"/>
+      <c r="CH110" s="24" t="n"/>
+      <c r="CI110" s="24" t="n"/>
+      <c r="CJ110" s="24" t="n"/>
+      <c r="CK110" s="24" t="n"/>
+      <c r="CL110" s="24" t="n"/>
+      <c r="CM110" s="24" t="n"/>
+      <c r="CN110" s="24" t="n"/>
+      <c r="CO110" s="24" t="n"/>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="A111" s="24" t="inlineStr">
+        <is>
+          <t>93efa735c8214ad7</t>
+        </is>
+      </c>
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C111" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00Z</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182240</t>
+        </is>
+      </c>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="inlineStr">
+        <is>
+          <t>Cadence Brace</t>
+        </is>
+      </c>
+      <c r="G111" s="24" t="inlineStr">
+        <is>
+          <t>McCartney Kessler</t>
+        </is>
+      </c>
+      <c r="H111" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I111" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J111" s="25" t="n"/>
+      <c r="K111" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L111" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="M111" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="N111" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="O111" s="28" t="n">
+        <v>0.7637620000000001</v>
+      </c>
+      <c r="P111" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q111" s="28" t="n">
+        <v>-0.11619</v>
+      </c>
+      <c r="R111" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T111" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U111" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V111" s="24" t="n"/>
+      <c r="W111" s="26" t="n"/>
+      <c r="X111" s="26" t="n"/>
+      <c r="Y111" s="25" t="n"/>
+      <c r="Z111" s="26" t="n"/>
+      <c r="AA111" s="28" t="n"/>
+      <c r="AB111" s="28" t="n"/>
+      <c r="AC111" s="30" t="n"/>
+      <c r="AD111" s="24" t="n"/>
+      <c r="AE111" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Cadence Brace p=0.236 vs McCartney Kessler. Executable ask 0.8800 (aec-wta-mcckes-cadbra-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF111" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG111" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH111" s="24" t="n"/>
+      <c r="AI111" s="31" t="n"/>
+      <c r="AJ111" s="31" t="n"/>
+      <c r="AK111" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL111" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM111" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN111" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO111" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP111" s="24" t="inlineStr">
+        <is>
+          <t>Cadence Brace</t>
+        </is>
+      </c>
+      <c r="AQ111" s="24" t="inlineStr">
+        <is>
+          <t>Cadence Brace</t>
+        </is>
+      </c>
+      <c r="AR111" s="24" t="inlineStr">
+        <is>
+          <t>Cadence Brace</t>
+        </is>
+      </c>
+      <c r="AS111" s="24" t="inlineStr">
+        <is>
+          <t>McCartney Kessler</t>
+        </is>
+      </c>
+      <c r="AT111" s="24" t="inlineStr">
+        <is>
+          <t>McCartney Kessler</t>
+        </is>
+      </c>
+      <c r="AU111" s="24" t="inlineStr">
+        <is>
+          <t>McCartney Kessler</t>
+        </is>
+      </c>
+      <c r="AV111" s="24" t="n"/>
+      <c r="AW111" s="24" t="n"/>
+      <c r="AX111" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY111" s="24" t="n"/>
+      <c r="AZ111" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA111" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB111" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC111" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD111" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE111" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF111" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG111" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH111" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:39.630632Z</t>
+        </is>
+      </c>
+      <c r="BI111" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ111" s="25" t="n"/>
+      <c r="BK111" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="BL111" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="BM111" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="BN111" s="28" t="n"/>
+      <c r="BO111" s="28" t="n"/>
+      <c r="BP111" s="25" t="n"/>
+      <c r="BQ111" s="27" t="n"/>
+      <c r="BR111" s="28" t="n"/>
+      <c r="BS111" s="28" t="n"/>
+      <c r="BT111" s="28" t="n"/>
+      <c r="BU111" s="25" t="n"/>
+      <c r="BV111" s="29" t="n"/>
+      <c r="BW111" s="24" t="n"/>
+      <c r="BX111" s="30" t="n"/>
+      <c r="BY111" s="27" t="n"/>
+      <c r="BZ111" s="24" t="n"/>
+      <c r="CA111" s="31" t="n"/>
+      <c r="CB111" s="24" t="n"/>
+      <c r="CC111" s="24" t="n"/>
+      <c r="CD111" s="24" t="n"/>
+      <c r="CE111" s="24" t="n"/>
+      <c r="CF111" s="24" t="n"/>
+      <c r="CG111" s="24" t="n"/>
+      <c r="CH111" s="24" t="n"/>
+      <c r="CI111" s="24" t="n"/>
+      <c r="CJ111" s="24" t="n"/>
+      <c r="CK111" s="24" t="n"/>
+      <c r="CL111" s="24" t="n"/>
+      <c r="CM111" s="24" t="n"/>
+      <c r="CN111" s="24" t="n"/>
+      <c r="CO111" s="24" t="n"/>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="A112" s="24" t="inlineStr">
+        <is>
+          <t>b3faa8afac844eba</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="D112" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182283</t>
+        </is>
+      </c>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
+        <is>
+          <t>Elisabetta Cocciaretto</t>
+        </is>
+      </c>
+      <c r="G112" s="24" t="inlineStr">
+        <is>
+          <t>Talia Gibson</t>
+        </is>
+      </c>
+      <c r="H112" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I112" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J112" s="25" t="n"/>
+      <c r="K112" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L112" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M112" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N112" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O112" s="28" t="n">
+        <v>0.578226</v>
+      </c>
+      <c r="P112" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q112" s="28" t="n">
+        <v>-0.011938</v>
+      </c>
+      <c r="R112" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="S112" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T112" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U112" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V112" s="24" t="n"/>
+      <c r="W112" s="26" t="n"/>
+      <c r="X112" s="26" t="n"/>
+      <c r="Y112" s="25" t="n"/>
+      <c r="Z112" s="26" t="n"/>
+      <c r="AA112" s="28" t="n"/>
+      <c r="AB112" s="28" t="n"/>
+      <c r="AC112" s="30" t="n"/>
+      <c r="AD112" s="24" t="n"/>
+      <c r="AE112" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Elisabetta Cocciaretto p=0.578 vs Talia Gibson. Executable ask 0.5900 (aec-wta-talgib-elicoc-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF112" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG112" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH112" s="24" t="n"/>
+      <c r="AI112" s="31" t="n"/>
+      <c r="AJ112" s="31" t="n"/>
+      <c r="AK112" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL112" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM112" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN112" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO112" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP112" s="24" t="inlineStr">
+        <is>
+          <t>Elisabetta Cocciaretto</t>
+        </is>
+      </c>
+      <c r="AQ112" s="24" t="inlineStr">
+        <is>
+          <t>Elisabetta Cocciaretto</t>
+        </is>
+      </c>
+      <c r="AR112" s="24" t="inlineStr">
+        <is>
+          <t>Elisabetta Cocciaretto</t>
+        </is>
+      </c>
+      <c r="AS112" s="24" t="inlineStr">
+        <is>
+          <t>Talia Gibson</t>
+        </is>
+      </c>
+      <c r="AT112" s="24" t="inlineStr">
+        <is>
+          <t>Talia Gibson</t>
+        </is>
+      </c>
+      <c r="AU112" s="24" t="inlineStr">
+        <is>
+          <t>Talia Gibson</t>
+        </is>
+      </c>
+      <c r="AV112" s="24" t="n"/>
+      <c r="AW112" s="24" t="n"/>
+      <c r="AX112" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY112" s="24" t="n"/>
+      <c r="AZ112" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA112" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB112" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC112" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD112" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE112" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF112" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG112" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH112" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:41.712269Z</t>
+        </is>
+      </c>
+      <c r="BI112" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ112" s="25" t="n"/>
+      <c r="BK112" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL112" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM112" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN112" s="28" t="n"/>
+      <c r="BO112" s="28" t="n"/>
+      <c r="BP112" s="25" t="n"/>
+      <c r="BQ112" s="27" t="n"/>
+      <c r="BR112" s="28" t="n"/>
+      <c r="BS112" s="28" t="n"/>
+      <c r="BT112" s="28" t="n"/>
+      <c r="BU112" s="25" t="n"/>
+      <c r="BV112" s="29" t="n"/>
+      <c r="BW112" s="24" t="n"/>
+      <c r="BX112" s="30" t="n"/>
+      <c r="BY112" s="27" t="n"/>
+      <c r="BZ112" s="24" t="n"/>
+      <c r="CA112" s="31" t="n"/>
+      <c r="CB112" s="24" t="n"/>
+      <c r="CC112" s="24" t="n"/>
+      <c r="CD112" s="24" t="n"/>
+      <c r="CE112" s="24" t="n"/>
+      <c r="CF112" s="24" t="n"/>
+      <c r="CG112" s="24" t="n"/>
+      <c r="CH112" s="24" t="n"/>
+      <c r="CI112" s="24" t="n"/>
+      <c r="CJ112" s="24" t="n"/>
+      <c r="CK112" s="24" t="n"/>
+      <c r="CL112" s="24" t="n"/>
+      <c r="CM112" s="24" t="n"/>
+      <c r="CN112" s="24" t="n"/>
+      <c r="CO112" s="24" t="n"/>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="A113" s="24" t="inlineStr">
+        <is>
+          <t>aa38aa54aad441df</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C113" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182274</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>Bianca Andreescu</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>Nikola Bartunkova</t>
+        </is>
+      </c>
+      <c r="H113" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I113" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J113" s="25" t="n"/>
+      <c r="K113" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L113" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M113" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N113" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O113" s="28" t="n">
+        <v>0.617346</v>
+      </c>
+      <c r="P113" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q113" s="28" t="n">
+        <v>0.017346</v>
+      </c>
+      <c r="R113" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S113" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T113" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U113" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V113" s="24" t="n"/>
+      <c r="W113" s="26" t="n"/>
+      <c r="X113" s="26" t="n"/>
+      <c r="Y113" s="25" t="n"/>
+      <c r="Z113" s="26" t="n"/>
+      <c r="AA113" s="28" t="n"/>
+      <c r="AB113" s="28" t="n"/>
+      <c r="AC113" s="30" t="n"/>
+      <c r="AD113" s="24" t="n"/>
+      <c r="AE113" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Bianca Andreescu p=0.383 vs Nikola Bartunkova. Executable ask 0.6000 (aec-wta-nikbar-biaand-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF113" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG113" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH113" s="24" t="n"/>
+      <c r="AI113" s="31" t="n"/>
+      <c r="AJ113" s="31" t="n"/>
+      <c r="AK113" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL113" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM113" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN113" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO113" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP113" s="24" t="inlineStr">
+        <is>
+          <t>Bianca Andreescu</t>
+        </is>
+      </c>
+      <c r="AQ113" s="24" t="inlineStr">
+        <is>
+          <t>Bianca Andreescu</t>
+        </is>
+      </c>
+      <c r="AR113" s="24" t="inlineStr">
+        <is>
+          <t>Bianca Andreescu</t>
+        </is>
+      </c>
+      <c r="AS113" s="24" t="inlineStr">
+        <is>
+          <t>Nikola Bartunkova</t>
+        </is>
+      </c>
+      <c r="AT113" s="24" t="inlineStr">
+        <is>
+          <t>Nikola Bartunkova</t>
+        </is>
+      </c>
+      <c r="AU113" s="24" t="inlineStr">
+        <is>
+          <t>Nikola Bartunkova</t>
+        </is>
+      </c>
+      <c r="AV113" s="24" t="n"/>
+      <c r="AW113" s="24" t="n"/>
+      <c r="AX113" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY113" s="24" t="n"/>
+      <c r="AZ113" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA113" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB113" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC113" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD113" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE113" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF113" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG113" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH113" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:41.762741Z</t>
+        </is>
+      </c>
+      <c r="BI113" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ113" s="25" t="n"/>
+      <c r="BK113" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL113" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM113" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN113" s="28" t="n"/>
+      <c r="BO113" s="28" t="n"/>
+      <c r="BP113" s="25" t="n"/>
+      <c r="BQ113" s="27" t="n"/>
+      <c r="BR113" s="28" t="n"/>
+      <c r="BS113" s="28" t="n"/>
+      <c r="BT113" s="28" t="n"/>
+      <c r="BU113" s="25" t="n"/>
+      <c r="BV113" s="29" t="n"/>
+      <c r="BW113" s="24" t="n"/>
+      <c r="BX113" s="30" t="n"/>
+      <c r="BY113" s="27" t="n"/>
+      <c r="BZ113" s="24" t="n"/>
+      <c r="CA113" s="31" t="n"/>
+      <c r="CB113" s="24" t="n"/>
+      <c r="CC113" s="24" t="n"/>
+      <c r="CD113" s="24" t="n"/>
+      <c r="CE113" s="24" t="n"/>
+      <c r="CF113" s="24" t="n"/>
+      <c r="CG113" s="24" t="n"/>
+      <c r="CH113" s="24" t="n"/>
+      <c r="CI113" s="24" t="n"/>
+      <c r="CJ113" s="24" t="n"/>
+      <c r="CK113" s="24" t="n"/>
+      <c r="CL113" s="24" t="n"/>
+      <c r="CM113" s="24" t="n"/>
+      <c r="CN113" s="24" t="n"/>
+      <c r="CO113" s="24" t="n"/>
+    </row>
+    <row r="114" ht="36" customHeight="1">
+      <c r="A114" s="24" t="inlineStr">
+        <is>
+          <t>6ff28fd485c748f5</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:33.942118Z</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182281</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>Zhang Shuai</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="inlineStr">
+        <is>
+          <t>Yulia Putintseva</t>
+        </is>
+      </c>
+      <c r="H114" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I114" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J114" s="25" t="n"/>
+      <c r="K114" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L114" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M114" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N114" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O114" s="28" t="n">
+        <v>0.630736</v>
+      </c>
+      <c r="P114" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q114" s="28" t="n">
+        <v>-0.019614</v>
+      </c>
+      <c r="R114" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S114" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T114" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U114" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V114" s="24" t="n"/>
+      <c r="W114" s="26" t="n"/>
+      <c r="X114" s="26" t="n"/>
+      <c r="Y114" s="25" t="n"/>
+      <c r="Z114" s="26" t="n"/>
+      <c r="AA114" s="28" t="n"/>
+      <c r="AB114" s="28" t="n"/>
+      <c r="AC114" s="30" t="n"/>
+      <c r="AD114" s="24" t="n"/>
+      <c r="AE114" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Zhang Shuai p=0.369 vs Yulia Putintseva. Executable ask 0.6500 (aec-wta-yulput-shuzha-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF114" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG114" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH114" s="24" t="n"/>
+      <c r="AI114" s="31" t="n"/>
+      <c r="AJ114" s="31" t="n"/>
+      <c r="AK114" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL114" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM114" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN114" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO114" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP114" s="24" t="inlineStr">
+        <is>
+          <t>Zhang Shuai</t>
+        </is>
+      </c>
+      <c r="AQ114" s="24" t="inlineStr">
+        <is>
+          <t>Zhang Shuai</t>
+        </is>
+      </c>
+      <c r="AR114" s="24" t="inlineStr">
+        <is>
+          <t>Zhang Shuai</t>
+        </is>
+      </c>
+      <c r="AS114" s="24" t="inlineStr">
+        <is>
+          <t>Yulia Putintseva</t>
+        </is>
+      </c>
+      <c r="AT114" s="24" t="inlineStr">
+        <is>
+          <t>Yulia Putintseva</t>
+        </is>
+      </c>
+      <c r="AU114" s="24" t="inlineStr">
+        <is>
+          <t>Yulia Putintseva</t>
+        </is>
+      </c>
+      <c r="AV114" s="24" t="n"/>
+      <c r="AW114" s="24" t="n"/>
+      <c r="AX114" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY114" s="24" t="n"/>
+      <c r="AZ114" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA114" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB114" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC114" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD114" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE114" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF114" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG114" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH114" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:41.780045Z</t>
+        </is>
+      </c>
+      <c r="BI114" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ114" s="25" t="n"/>
+      <c r="BK114" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL114" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM114" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN114" s="28" t="n"/>
+      <c r="BO114" s="28" t="n"/>
+      <c r="BP114" s="25" t="n"/>
+      <c r="BQ114" s="27" t="n"/>
+      <c r="BR114" s="28" t="n"/>
+      <c r="BS114" s="28" t="n"/>
+      <c r="BT114" s="28" t="n"/>
+      <c r="BU114" s="25" t="n"/>
+      <c r="BV114" s="29" t="n"/>
+      <c r="BW114" s="24" t="n"/>
+      <c r="BX114" s="30" t="n"/>
+      <c r="BY114" s="27" t="n"/>
+      <c r="BZ114" s="24" t="n"/>
+      <c r="CA114" s="31" t="n"/>
+      <c r="CB114" s="24" t="n"/>
+      <c r="CC114" s="24" t="n"/>
+      <c r="CD114" s="24" t="n"/>
+      <c r="CE114" s="24" t="n"/>
+      <c r="CF114" s="24" t="n"/>
+      <c r="CG114" s="24" t="n"/>
+      <c r="CH114" s="24" t="n"/>
+      <c r="CI114" s="24" t="n"/>
+      <c r="CJ114" s="24" t="n"/>
+      <c r="CK114" s="24" t="n"/>
+      <c r="CL114" s="24" t="n"/>
+      <c r="CM114" s="24" t="n"/>
+      <c r="CN114" s="24" t="n"/>
+      <c r="CO114" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -28747,12 +28747,12 @@
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>c4929eec2cb843fd</t>
+          <t>db680842cfb54539</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C99" s="24" t="inlineStr">
@@ -28960,7 +28960,7 @@
       </c>
       <c r="BH99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:40.150606Z</t>
+          <t>2026-08-02T08:13:45.527180Z</t>
         </is>
       </c>
       <c r="BI99" s="24" t="inlineStr">
@@ -29010,12 +29010,12 @@
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
         <is>
-          <t>e5310e100d614eca</t>
+          <t>cd72fa05b014431f</t>
         </is>
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="BH100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:33.217270Z</t>
+          <t>2026-08-02T08:13:36.597767Z</t>
         </is>
       </c>
       <c r="BI100" s="24" t="inlineStr">
@@ -29273,12 +29273,12 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>4154cdee02b44038</t>
+          <t>908eca11251b4f63</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:31.826745Z</t>
+          <t>2026-08-02T08:13:35.148255Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -29536,12 +29536,12 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>c81c82bfba664c2f</t>
+          <t>957db24736fa4a29</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -29749,7 +29749,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:32.750457Z</t>
+          <t>2026-08-02T08:13:36.108286Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -29799,12 +29799,12 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>10d15853ccd14c44</t>
+          <t>2611f34636684052</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -29849,13 +29849,13 @@
         </is>
       </c>
       <c r="L103" s="26" t="n">
-        <v>-163</v>
+        <v>-150</v>
       </c>
       <c r="M103" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.666667</v>
       </c>
       <c r="N103" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.6</v>
       </c>
       <c r="O103" s="28" t="n">
         <v>0.548768</v>
@@ -29864,7 +29864,7 @@
         <v>0.05</v>
       </c>
       <c r="Q103" s="28" t="n">
-        <v>-0.071004</v>
+        <v>-0.051232</v>
       </c>
       <c r="R103" s="26" t="n">
         <v>0</v>
@@ -29893,7 +29893,7 @@
       <c r="AD103" s="24" t="n"/>
       <c r="AE103" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Cristina Bucsa p=0.549 vs Moyuka Uchijima. Executable ask 0.6200 (aec-wta-moyuch-cribuc-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Cristina Bucsa p=0.549 vs Moyuka Uchijima. Executable ask 0.6000 (aec-wta-moyuch-cribuc-2026-08-02).</t>
         </is>
       </c>
       <c r="AF103" s="31" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:31.808862Z</t>
+          <t>2026-08-02T08:13:35.093685Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -30022,13 +30022,13 @@
       </c>
       <c r="BJ103" s="25" t="n"/>
       <c r="BK103" s="26" t="n">
-        <v>-163</v>
+        <v>-150</v>
       </c>
       <c r="BL103" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.666667</v>
       </c>
       <c r="BM103" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.6</v>
       </c>
       <c r="BN103" s="28" t="n"/>
       <c r="BO103" s="28" t="n"/>
@@ -30062,12 +30062,12 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>aadb962e8e0249ca</t>
+          <t>a7f07d70258641a2</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -30112,13 +30112,13 @@
         </is>
       </c>
       <c r="L104" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="M104" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="N104" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="O104" s="28" t="n">
         <v>0.597848</v>
@@ -30127,10 +30127,10 @@
         <v>0.05</v>
       </c>
       <c r="Q104" s="28" t="n">
-        <v>-0.002152</v>
+        <v>0.007684</v>
       </c>
       <c r="R104" s="26" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="S104" s="29" t="n">
         <v>1.25</v>
@@ -30156,7 +30156,7 @@
       <c r="AD104" s="24" t="n"/>
       <c r="AE104" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.6000 (aec-wta-xiywan-sarbej-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.5900 (aec-wta-xiywan-sarbej-2026-08-02).</t>
         </is>
       </c>
       <c r="AF104" s="31" t="inlineStr">
@@ -30275,7 +30275,7 @@
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:31.845281Z</t>
+          <t>2026-08-02T08:13:35.171707Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -30285,13 +30285,13 @@
       </c>
       <c r="BJ104" s="25" t="n"/>
       <c r="BK104" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="BL104" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="BM104" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="BN104" s="28" t="n"/>
       <c r="BO104" s="28" t="n"/>
@@ -30325,12 +30325,12 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>f5c1adcfc0d34ca0</t>
+          <t>1e5223eab24d4288</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:35.341815Z</t>
+          <t>2026-08-02T08:13:38.726922Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -30588,12 +30588,12 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>84d2748d860a452d</t>
+          <t>8bdd181148754e7a</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
@@ -30801,7 +30801,7 @@
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:35.998974Z</t>
+          <t>2026-08-02T08:13:40.169422Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -30851,12 +30851,12 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>64ef379ab18349f7</t>
+          <t>c982ad904ec6402f</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:37.008588Z</t>
+          <t>2026-08-02T08:13:41.403395Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -31114,12 +31114,12 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>99be0b0015e5439d</t>
+          <t>45fc2f47b40b4865</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
@@ -31327,7 +31327,7 @@
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:34.504805Z</t>
+          <t>2026-08-02T08:13:37.821288Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -31377,12 +31377,12 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>e7256f4701794fd3</t>
+          <t>7ee60621a71e475f</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
@@ -31590,7 +31590,7 @@
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:37.841935Z</t>
+          <t>2026-08-02T08:13:42.785061Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -31640,12 +31640,12 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>1a8764981c564053</t>
+          <t>cd8e0bae7b284cbd</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
@@ -31853,7 +31853,7 @@
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:38.720666Z</t>
+          <t>2026-08-02T08:13:43.671992Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -31903,12 +31903,12 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>93efa735c8214ad7</t>
+          <t>5fca9cf5fcc7440f</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
@@ -32116,7 +32116,7 @@
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:39.630632Z</t>
+          <t>2026-08-02T08:13:45.005805Z</t>
         </is>
       </c>
       <c r="BI111" s="24" t="inlineStr">
@@ -32166,12 +32166,12 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>b3faa8afac844eba</t>
+          <t>fbea84407b0f4ba8</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
@@ -32379,7 +32379,7 @@
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:41.712269Z</t>
+          <t>2026-08-02T08:13:47.211871Z</t>
         </is>
       </c>
       <c r="BI112" s="24" t="inlineStr">
@@ -32429,12 +32429,12 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>aa38aa54aad441df</t>
+          <t>27064a9cecbd4d36</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
@@ -32642,7 +32642,7 @@
       </c>
       <c r="BH113" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:41.762741Z</t>
+          <t>2026-08-02T08:13:47.475586Z</t>
         </is>
       </c>
       <c r="BI113" s="24" t="inlineStr">
@@ -32692,12 +32692,12 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>6ff28fd485c748f5</t>
+          <t>25e732f82f3244b8</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:33.942118Z</t>
+          <t>2026-08-02T08:17:29.872422Z</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
@@ -32905,7 +32905,7 @@
       </c>
       <c r="BH114" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:41.780045Z</t>
+          <t>2026-08-02T08:13:47.520549Z</t>
         </is>
       </c>
       <c r="BI114" s="24" t="inlineStr">

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -28747,12 +28747,12 @@
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>db680842cfb54539</t>
+          <t>f6133e3ec2714216</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C99" s="24" t="inlineStr">
@@ -28960,7 +28960,7 @@
       </c>
       <c r="BH99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:45.527180Z</t>
+          <t>2026-08-02T09:54:59.234279Z</t>
         </is>
       </c>
       <c r="BI99" s="24" t="inlineStr">
@@ -29010,12 +29010,12 @@
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
         <is>
-          <t>cd72fa05b014431f</t>
+          <t>78ec2df0e70a44cc</t>
         </is>
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
@@ -29060,13 +29060,13 @@
         </is>
       </c>
       <c r="L100" s="26" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="M100" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.925926</v>
       </c>
       <c r="N100" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.519231</v>
       </c>
       <c r="O100" s="28" t="n">
         <v>0.639939</v>
@@ -29075,10 +29075,10 @@
         <v>0.05</v>
       </c>
       <c r="Q100" s="28" t="n">
-        <v>0.109423</v>
+        <v>0.120708</v>
       </c>
       <c r="R100" s="26" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S100" s="29" t="n">
         <v>1.5</v>
@@ -29104,7 +29104,7 @@
       <c r="AD100" s="24" t="n"/>
       <c r="AE100" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.5300 (aec-wta-kriliu-darvid-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.5200 (aec-wta-kriliu-darvid-2026-08-02).</t>
         </is>
       </c>
       <c r="AF100" s="31" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="BH100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:36.597767Z</t>
+          <t>2026-08-02T09:54:49.276365Z</t>
         </is>
       </c>
       <c r="BI100" s="24" t="inlineStr">
@@ -29233,13 +29233,13 @@
       </c>
       <c r="BJ100" s="25" t="n"/>
       <c r="BK100" s="26" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="BL100" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.925926</v>
       </c>
       <c r="BM100" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.519231</v>
       </c>
       <c r="BN100" s="28" t="n"/>
       <c r="BO100" s="28" t="n"/>
@@ -29273,12 +29273,12 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>908eca11251b4f63</t>
+          <t>da9d6d1b27154233</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="L101" s="26" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="M101" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.724638</v>
       </c>
       <c r="N101" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.579832</v>
       </c>
       <c r="O101" s="28" t="n">
         <v>0.608004</v>
@@ -29338,10 +29338,10 @@
         <v>0.05</v>
       </c>
       <c r="Q101" s="28" t="n">
-        <v>0.037189</v>
+        <v>0.028172</v>
       </c>
       <c r="R101" s="26" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="S101" s="29" t="n">
         <v>1.5</v>
@@ -29367,7 +29367,7 @@
       <c r="AD101" s="24" t="n"/>
       <c r="AE101" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Laura Samson p=0.392 vs Kaitlin Quevedo. Executable ask 0.5700 (aec-wta-kaique-lausam-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Laura Samson p=0.392 vs Kaitlin Quevedo. Executable ask 0.5800 (aec-wta-kaique-lausam-2026-08-02).</t>
         </is>
       </c>
       <c r="AF101" s="31" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:35.148255Z</t>
+          <t>2026-08-02T09:54:47.814266Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -29496,13 +29496,13 @@
       </c>
       <c r="BJ101" s="25" t="n"/>
       <c r="BK101" s="26" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="BL101" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.724638</v>
       </c>
       <c r="BM101" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.579832</v>
       </c>
       <c r="BN101" s="28" t="n"/>
       <c r="BO101" s="28" t="n"/>
@@ -29536,12 +29536,12 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>957db24736fa4a29</t>
+          <t>624f45d41cca4fad</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -29749,7 +29749,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:36.108286Z</t>
+          <t>2026-08-02T09:54:48.787189Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -29799,12 +29799,12 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>2611f34636684052</t>
+          <t>64c699a375f4400a</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:35.093685Z</t>
+          <t>2026-08-02T09:54:47.754501Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -30062,12 +30062,12 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>a7f07d70258641a2</t>
+          <t>c8fc8717e2734e88</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -30275,7 +30275,7 @@
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:35.171707Z</t>
+          <t>2026-08-02T09:54:47.739233Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -30325,12 +30325,12 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>1e5223eab24d4288</t>
+          <t>56444c2c506641fe</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:38.726922Z</t>
+          <t>2026-08-02T09:54:51.971588Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -30588,12 +30588,12 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>8bdd181148754e7a</t>
+          <t>6c0b5bf65dc84348</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
@@ -30801,7 +30801,7 @@
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:40.169422Z</t>
+          <t>2026-08-02T09:54:53.441330Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -30851,12 +30851,12 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>c982ad904ec6402f</t>
+          <t>91db2bf60c5d4e85</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:41.403395Z</t>
+          <t>2026-08-02T09:54:54.664274Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -31114,12 +31114,12 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>45fc2f47b40b4865</t>
+          <t>c0183b77a2ac45e8</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
@@ -31327,7 +31327,7 @@
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:37.821288Z</t>
+          <t>2026-08-02T09:54:50.773487Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -31377,12 +31377,12 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>7ee60621a71e475f</t>
+          <t>8af8b4a297a34ce3</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
@@ -31590,7 +31590,7 @@
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:42.785061Z</t>
+          <t>2026-08-02T09:54:56.021809Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -31640,12 +31640,12 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>cd8e0bae7b284cbd</t>
+          <t>0ace72a6c9964cf8</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
@@ -31853,7 +31853,7 @@
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:43.671992Z</t>
+          <t>2026-08-02T09:54:57.197277Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -31903,12 +31903,12 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>5fca9cf5fcc7440f</t>
+          <t>f49ff5b0d84e40e8</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
@@ -32116,7 +32116,7 @@
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:45.005805Z</t>
+          <t>2026-08-02T09:54:58.597855Z</t>
         </is>
       </c>
       <c r="BI111" s="24" t="inlineStr">
@@ -32166,12 +32166,12 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>fbea84407b0f4ba8</t>
+          <t>5466db52b99548f5</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
@@ -32379,7 +32379,7 @@
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:47.211871Z</t>
+          <t>2026-08-02T09:55:00.882635Z</t>
         </is>
       </c>
       <c r="BI112" s="24" t="inlineStr">
@@ -32429,12 +32429,12 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>27064a9cecbd4d36</t>
+          <t>bf3daa1ac89a4b1a</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
@@ -32642,7 +32642,7 @@
       </c>
       <c r="BH113" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:47.475586Z</t>
+          <t>2026-08-02T09:55:00.982396Z</t>
         </is>
       </c>
       <c r="BI113" s="24" t="inlineStr">
@@ -32692,12 +32692,12 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>25e732f82f3244b8</t>
+          <t>6566991c6bb04ce0</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:17:29.872422Z</t>
+          <t>2026-08-02T09:58:14.597238Z</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
@@ -32905,7 +32905,7 @@
       </c>
       <c r="BH114" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:47.520549Z</t>
+          <t>2026-08-02T09:55:01.453864Z</t>
         </is>
       </c>
       <c r="BI114" s="24" t="inlineStr">

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO114" headerRowCount="1">
-  <autoFilter ref="A1:CO114"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP114" headerRowCount="1">
+  <autoFilter ref="A1:CP114"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO114"/>
+  <dimension ref="A1:CP114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1851,6 +1858,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2128,6 +2136,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2405,6 +2414,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2682,6 +2692,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2959,6 +2970,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3236,6 +3248,7 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3513,6 +3526,7 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3790,6 +3804,7 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4067,6 +4082,7 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4344,6 +4360,7 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4621,6 +4638,7 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4898,6 +4916,7 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5175,6 +5194,7 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5452,6 +5472,7 @@
       <c r="CM15" s="24" t="n"/>
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5729,6 +5750,7 @@
       <c r="CM16" s="24" t="n"/>
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6006,6 +6028,7 @@
       <c r="CM17" s="24" t="n"/>
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6283,6 +6306,7 @@
       <c r="CM18" s="24" t="n"/>
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6560,6 +6584,7 @@
       <c r="CM19" s="24" t="n"/>
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6837,6 +6862,7 @@
       <c r="CM20" s="24" t="n"/>
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7114,6 +7140,7 @@
       <c r="CM21" s="24" t="n"/>
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7391,6 +7418,7 @@
       <c r="CM22" s="24" t="n"/>
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7668,6 +7696,7 @@
       <c r="CM23" s="24" t="n"/>
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -7945,6 +7974,7 @@
       <c r="CM24" s="24" t="n"/>
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8222,6 +8252,7 @@
       <c r="CM25" s="24" t="n"/>
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8499,6 +8530,7 @@
       <c r="CM26" s="24" t="n"/>
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -8776,6 +8808,7 @@
       <c r="CM27" s="24" t="n"/>
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9053,6 +9086,7 @@
       <c r="CM28" s="24" t="n"/>
       <c r="CN28" s="24" t="n"/>
       <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9330,6 +9364,7 @@
       <c r="CM29" s="24" t="n"/>
       <c r="CN29" s="24" t="n"/>
       <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9607,6 +9642,7 @@
       <c r="CM30" s="24" t="n"/>
       <c r="CN30" s="24" t="n"/>
       <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -9884,6 +9920,7 @@
       <c r="CM31" s="24" t="n"/>
       <c r="CN31" s="24" t="n"/>
       <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10161,6 +10198,7 @@
       <c r="CM32" s="24" t="n"/>
       <c r="CN32" s="24" t="n"/>
       <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10438,6 +10476,7 @@
       <c r="CM33" s="24" t="n"/>
       <c r="CN33" s="24" t="n"/>
       <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -10715,6 +10754,7 @@
       <c r="CM34" s="24" t="n"/>
       <c r="CN34" s="24" t="n"/>
       <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -10992,6 +11032,7 @@
       <c r="CM35" s="24" t="n"/>
       <c r="CN35" s="24" t="n"/>
       <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11269,6 +11310,7 @@
       <c r="CM36" s="24" t="n"/>
       <c r="CN36" s="24" t="n"/>
       <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11546,6 +11588,7 @@
       <c r="CM37" s="24" t="n"/>
       <c r="CN37" s="24" t="n"/>
       <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -11823,6 +11866,7 @@
       <c r="CM38" s="24" t="n"/>
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
@@ -12100,6 +12144,7 @@
       <c r="CM39" s="24" t="n"/>
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
@@ -12377,6 +12422,7 @@
       <c r="CM40" s="24" t="n"/>
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
@@ -12654,6 +12700,7 @@
       <c r="CM41" s="24" t="n"/>
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
@@ -12931,6 +12978,7 @@
       <c r="CM42" s="24" t="n"/>
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
@@ -13208,6 +13256,7 @@
       <c r="CM43" s="24" t="n"/>
       <c r="CN43" s="24" t="n"/>
       <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
@@ -13485,6 +13534,7 @@
       <c r="CM44" s="24" t="n"/>
       <c r="CN44" s="24" t="n"/>
       <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
@@ -13762,6 +13812,7 @@
       <c r="CM45" s="24" t="n"/>
       <c r="CN45" s="24" t="n"/>
       <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
@@ -14039,6 +14090,7 @@
       <c r="CM46" s="24" t="n"/>
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
@@ -14316,6 +14368,7 @@
       <c r="CM47" s="24" t="n"/>
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
@@ -14593,6 +14646,7 @@
       <c r="CM48" s="24" t="n"/>
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
@@ -14870,6 +14924,7 @@
       <c r="CM49" s="24" t="n"/>
       <c r="CN49" s="24" t="n"/>
       <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
@@ -15147,6 +15202,7 @@
       <c r="CM50" s="24" t="n"/>
       <c r="CN50" s="24" t="n"/>
       <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
@@ -15424,6 +15480,7 @@
       <c r="CM51" s="24" t="n"/>
       <c r="CN51" s="24" t="n"/>
       <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
@@ -15701,6 +15758,7 @@
       <c r="CM52" s="24" t="n"/>
       <c r="CN52" s="24" t="n"/>
       <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
@@ -15978,6 +16036,7 @@
       <c r="CM53" s="24" t="n"/>
       <c r="CN53" s="24" t="n"/>
       <c r="CO53" s="24" t="n"/>
+      <c r="CP53" s="24" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
@@ -16255,6 +16314,7 @@
       <c r="CM54" s="24" t="n"/>
       <c r="CN54" s="24" t="n"/>
       <c r="CO54" s="24" t="n"/>
+      <c r="CP54" s="24" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
@@ -16532,6 +16592,7 @@
       <c r="CM55" s="24" t="n"/>
       <c r="CN55" s="24" t="n"/>
       <c r="CO55" s="24" t="n"/>
+      <c r="CP55" s="24" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
@@ -16809,6 +16870,7 @@
       <c r="CM56" s="24" t="n"/>
       <c r="CN56" s="24" t="n"/>
       <c r="CO56" s="24" t="n"/>
+      <c r="CP56" s="24" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
@@ -17086,6 +17148,7 @@
       <c r="CM57" s="24" t="n"/>
       <c r="CN57" s="24" t="n"/>
       <c r="CO57" s="24" t="n"/>
+      <c r="CP57" s="24" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
@@ -17363,6 +17426,7 @@
       <c r="CM58" s="24" t="n"/>
       <c r="CN58" s="24" t="n"/>
       <c r="CO58" s="24" t="n"/>
+      <c r="CP58" s="24" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
@@ -17640,6 +17704,7 @@
       <c r="CM59" s="24" t="n"/>
       <c r="CN59" s="24" t="n"/>
       <c r="CO59" s="24" t="n"/>
+      <c r="CP59" s="24" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
@@ -17917,6 +17982,7 @@
       <c r="CM60" s="24" t="n"/>
       <c r="CN60" s="24" t="n"/>
       <c r="CO60" s="24" t="n"/>
+      <c r="CP60" s="24" t="n"/>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
@@ -18194,6 +18260,7 @@
       <c r="CM61" s="24" t="n"/>
       <c r="CN61" s="24" t="n"/>
       <c r="CO61" s="24" t="n"/>
+      <c r="CP61" s="24" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
@@ -18471,6 +18538,7 @@
       <c r="CM62" s="24" t="n"/>
       <c r="CN62" s="24" t="n"/>
       <c r="CO62" s="24" t="n"/>
+      <c r="CP62" s="24" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
@@ -18748,6 +18816,7 @@
       <c r="CM63" s="24" t="n"/>
       <c r="CN63" s="24" t="n"/>
       <c r="CO63" s="24" t="n"/>
+      <c r="CP63" s="24" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
@@ -19025,6 +19094,7 @@
       <c r="CM64" s="24" t="n"/>
       <c r="CN64" s="24" t="n"/>
       <c r="CO64" s="24" t="n"/>
+      <c r="CP64" s="24" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
@@ -19302,6 +19372,7 @@
       <c r="CM65" s="24" t="n"/>
       <c r="CN65" s="24" t="n"/>
       <c r="CO65" s="24" t="n"/>
+      <c r="CP65" s="24" t="n"/>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
@@ -19579,6 +19650,7 @@
       <c r="CM66" s="24" t="n"/>
       <c r="CN66" s="24" t="n"/>
       <c r="CO66" s="24" t="n"/>
+      <c r="CP66" s="24" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
@@ -19856,6 +19928,7 @@
       <c r="CM67" s="24" t="n"/>
       <c r="CN67" s="24" t="n"/>
       <c r="CO67" s="24" t="n"/>
+      <c r="CP67" s="24" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
@@ -20143,6 +20216,7 @@
       <c r="CM68" s="24" t="n"/>
       <c r="CN68" s="24" t="n"/>
       <c r="CO68" s="24" t="n"/>
+      <c r="CP68" s="24" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
@@ -20430,6 +20504,7 @@
       <c r="CM69" s="24" t="n"/>
       <c r="CN69" s="24" t="n"/>
       <c r="CO69" s="24" t="n"/>
+      <c r="CP69" s="24" t="n"/>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
@@ -20717,6 +20792,7 @@
       <c r="CM70" s="24" t="n"/>
       <c r="CN70" s="24" t="n"/>
       <c r="CO70" s="24" t="n"/>
+      <c r="CP70" s="24" t="n"/>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
@@ -21004,6 +21080,7 @@
       <c r="CM71" s="24" t="n"/>
       <c r="CN71" s="24" t="n"/>
       <c r="CO71" s="24" t="n"/>
+      <c r="CP71" s="24" t="n"/>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
@@ -21291,6 +21368,7 @@
       <c r="CM72" s="24" t="n"/>
       <c r="CN72" s="24" t="n"/>
       <c r="CO72" s="24" t="n"/>
+      <c r="CP72" s="24" t="n"/>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
@@ -21578,6 +21656,7 @@
       <c r="CM73" s="24" t="n"/>
       <c r="CN73" s="24" t="n"/>
       <c r="CO73" s="24" t="n"/>
+      <c r="CP73" s="24" t="n"/>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
@@ -21865,6 +21944,7 @@
       <c r="CM74" s="24" t="n"/>
       <c r="CN74" s="24" t="n"/>
       <c r="CO74" s="24" t="n"/>
+      <c r="CP74" s="24" t="n"/>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
@@ -22152,6 +22232,7 @@
       <c r="CM75" s="24" t="n"/>
       <c r="CN75" s="24" t="n"/>
       <c r="CO75" s="24" t="n"/>
+      <c r="CP75" s="24" t="n"/>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
@@ -22439,6 +22520,7 @@
       <c r="CM76" s="24" t="n"/>
       <c r="CN76" s="24" t="n"/>
       <c r="CO76" s="24" t="n"/>
+      <c r="CP76" s="24" t="n"/>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
@@ -22726,6 +22808,7 @@
       <c r="CM77" s="24" t="n"/>
       <c r="CN77" s="24" t="n"/>
       <c r="CO77" s="24" t="n"/>
+      <c r="CP77" s="24" t="n"/>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
@@ -23013,6 +23096,7 @@
       <c r="CM78" s="24" t="n"/>
       <c r="CN78" s="24" t="n"/>
       <c r="CO78" s="24" t="n"/>
+      <c r="CP78" s="24" t="n"/>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
@@ -23300,6 +23384,7 @@
       <c r="CM79" s="24" t="n"/>
       <c r="CN79" s="24" t="n"/>
       <c r="CO79" s="24" t="n"/>
+      <c r="CP79" s="24" t="n"/>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
@@ -23587,6 +23672,7 @@
       <c r="CM80" s="24" t="n"/>
       <c r="CN80" s="24" t="n"/>
       <c r="CO80" s="24" t="n"/>
+      <c r="CP80" s="24" t="n"/>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
@@ -23874,6 +23960,7 @@
       <c r="CM81" s="24" t="n"/>
       <c r="CN81" s="24" t="n"/>
       <c r="CO81" s="24" t="n"/>
+      <c r="CP81" s="24" t="n"/>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
@@ -24161,6 +24248,7 @@
       <c r="CM82" s="24" t="n"/>
       <c r="CN82" s="24" t="n"/>
       <c r="CO82" s="24" t="n"/>
+      <c r="CP82" s="24" t="n"/>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
@@ -24448,6 +24536,7 @@
       <c r="CM83" s="24" t="n"/>
       <c r="CN83" s="24" t="n"/>
       <c r="CO83" s="24" t="n"/>
+      <c r="CP83" s="24" t="n"/>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
@@ -24735,6 +24824,7 @@
       <c r="CM84" s="24" t="n"/>
       <c r="CN84" s="24" t="n"/>
       <c r="CO84" s="24" t="n"/>
+      <c r="CP84" s="24" t="n"/>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
@@ -25022,6 +25112,7 @@
       <c r="CM85" s="24" t="n"/>
       <c r="CN85" s="24" t="n"/>
       <c r="CO85" s="24" t="n"/>
+      <c r="CP85" s="24" t="n"/>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
@@ -25309,6 +25400,7 @@
       <c r="CM86" s="24" t="n"/>
       <c r="CN86" s="24" t="n"/>
       <c r="CO86" s="24" t="n"/>
+      <c r="CP86" s="24" t="n"/>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
@@ -25586,6 +25678,7 @@
       <c r="CM87" s="24" t="n"/>
       <c r="CN87" s="24" t="n"/>
       <c r="CO87" s="24" t="n"/>
+      <c r="CP87" s="24" t="n"/>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
@@ -25873,6 +25966,7 @@
       <c r="CM88" s="24" t="n"/>
       <c r="CN88" s="24" t="n"/>
       <c r="CO88" s="24" t="n"/>
+      <c r="CP88" s="24" t="n"/>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="24" t="inlineStr">
@@ -26160,6 +26254,7 @@
       <c r="CM89" s="24" t="n"/>
       <c r="CN89" s="24" t="n"/>
       <c r="CO89" s="24" t="n"/>
+      <c r="CP89" s="24" t="n"/>
     </row>
     <row r="90" ht="36" customHeight="1">
       <c r="A90" s="24" t="inlineStr">
@@ -26447,6 +26542,7 @@
       <c r="CM90" s="24" t="n"/>
       <c r="CN90" s="24" t="n"/>
       <c r="CO90" s="24" t="n"/>
+      <c r="CP90" s="24" t="n"/>
     </row>
     <row r="91" ht="36" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
@@ -26734,6 +26830,7 @@
       <c r="CM91" s="24" t="n"/>
       <c r="CN91" s="24" t="n"/>
       <c r="CO91" s="24" t="n"/>
+      <c r="CP91" s="24" t="n"/>
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="24" t="inlineStr">
@@ -27021,6 +27118,7 @@
       <c r="CM92" s="24" t="n"/>
       <c r="CN92" s="24" t="n"/>
       <c r="CO92" s="24" t="n"/>
+      <c r="CP92" s="24" t="n"/>
     </row>
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
@@ -27308,6 +27406,7 @@
       <c r="CM93" s="24" t="n"/>
       <c r="CN93" s="24" t="n"/>
       <c r="CO93" s="24" t="n"/>
+      <c r="CP93" s="24" t="n"/>
     </row>
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
@@ -27595,6 +27694,7 @@
       <c r="CM94" s="24" t="n"/>
       <c r="CN94" s="24" t="n"/>
       <c r="CO94" s="24" t="n"/>
+      <c r="CP94" s="24" t="n"/>
     </row>
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
@@ -27882,6 +27982,7 @@
       <c r="CM95" s="24" t="n"/>
       <c r="CN95" s="24" t="n"/>
       <c r="CO95" s="24" t="n"/>
+      <c r="CP95" s="24" t="n"/>
     </row>
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="24" t="inlineStr">
@@ -28169,6 +28270,7 @@
       <c r="CM96" s="24" t="n"/>
       <c r="CN96" s="24" t="n"/>
       <c r="CO96" s="24" t="n"/>
+      <c r="CP96" s="24" t="n"/>
     </row>
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="24" t="inlineStr">
@@ -28456,6 +28558,7 @@
       <c r="CM97" s="24" t="n"/>
       <c r="CN97" s="24" t="n"/>
       <c r="CO97" s="24" t="n"/>
+      <c r="CP97" s="24" t="n"/>
     </row>
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="24" t="inlineStr">
@@ -28743,26 +28846,27 @@
       <c r="CM98" s="24" t="n"/>
       <c r="CN98" s="24" t="n"/>
       <c r="CO98" s="24" t="n"/>
+      <c r="CP98" s="24" t="n"/>
     </row>
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>f6133e3ec2714216</t>
+          <t>2561c71be5564c8d</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T12:28:47.396277Z</t>
         </is>
       </c>
       <c r="C99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:00Z</t>
+          <t>2026-08-02T13:00Z</t>
         </is>
       </c>
       <c r="D99" s="24" t="inlineStr">
         <is>
-          <t>888-2026:179014</t>
+          <t>1073-2026:179603</t>
         </is>
       </c>
       <c r="E99" s="24" t="inlineStr">
@@ -28772,12 +28876,12 @@
       </c>
       <c r="F99" s="24" t="inlineStr">
         <is>
-          <t>Alexandra Eala</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="G99" s="24" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
+          <t>Kaitlin Quevedo</t>
         </is>
       </c>
       <c r="H99" s="24" t="inlineStr">
@@ -28797,28 +28901,28 @@
         </is>
       </c>
       <c r="L99" s="26" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="M99" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.724638</v>
       </c>
       <c r="N99" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.579832</v>
       </c>
       <c r="O99" s="28" t="n">
-        <v>0.821797</v>
+        <v>0.608004</v>
       </c>
       <c r="P99" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q99" s="28" t="n">
-        <v>0.231633</v>
+        <v>0.028172</v>
       </c>
       <c r="R99" s="26" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="S99" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T99" s="24" t="inlineStr">
         <is>
@@ -28841,7 +28945,7 @@
       <c r="AD99" s="24" t="n"/>
       <c r="AE99" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alexandra Eala p=0.178 vs Jessica Pegula. Executable ask 0.5900 (aec-wta-jespeg-aleeal-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Laura Samson p=0.392 vs Kaitlin Quevedo. Executable ask 0.5800 (aec-wta-kaique-lausam-2026-08-02).</t>
         </is>
       </c>
       <c r="AF99" s="31" t="inlineStr">
@@ -28882,32 +28986,32 @@
       </c>
       <c r="AP99" s="24" t="inlineStr">
         <is>
-          <t>Alexandra Eala</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AQ99" s="24" t="inlineStr">
         <is>
-          <t>Alexandra Eala</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AR99" s="24" t="inlineStr">
         <is>
-          <t>Alexandra Eala</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AS99" s="24" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
+          <t>Kaitlin Quevedo</t>
         </is>
       </c>
       <c r="AT99" s="24" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
+          <t>Kaitlin Quevedo</t>
         </is>
       </c>
       <c r="AU99" s="24" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
+          <t>Kaitlin Quevedo</t>
         </is>
       </c>
       <c r="AV99" s="24" t="n"/>
@@ -28960,7 +29064,7 @@
       </c>
       <c r="BH99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:59.234279Z</t>
+          <t>2026-08-02T12:25:29.223380Z</t>
         </is>
       </c>
       <c r="BI99" s="24" t="inlineStr">
@@ -28970,13 +29074,13 @@
       </c>
       <c r="BJ99" s="25" t="n"/>
       <c r="BK99" s="26" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="BL99" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.724638</v>
       </c>
       <c r="BM99" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.579832</v>
       </c>
       <c r="BN99" s="28" t="n"/>
       <c r="BO99" s="28" t="n"/>
@@ -29006,26 +29110,27 @@
       <c r="CM99" s="24" t="n"/>
       <c r="CN99" s="24" t="n"/>
       <c r="CO99" s="24" t="n"/>
+      <c r="CP99" s="24" t="n"/>
     </row>
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
         <is>
-          <t>78ec2df0e70a44cc</t>
+          <t>55bbf085e03f44e4</t>
         </is>
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:30Z</t>
+          <t>2026-08-02T16:00Z</t>
         </is>
       </c>
       <c r="D100" s="24" t="inlineStr">
         <is>
-          <t>1067-2026:179469</t>
+          <t>888-2026:179014</t>
         </is>
       </c>
       <c r="E100" s="24" t="inlineStr">
@@ -29035,12 +29140,12 @@
       </c>
       <c r="F100" s="24" t="inlineStr">
         <is>
-          <t>Darja Vidmanova</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="G100" s="24" t="inlineStr">
         <is>
-          <t>Kristina Liutova</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="H100" s="24" t="inlineStr">
@@ -29050,7 +29155,7 @@
       </c>
       <c r="I100" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J100" s="25" t="n"/>
@@ -29060,28 +29165,28 @@
         </is>
       </c>
       <c r="L100" s="26" t="n">
-        <v>-108</v>
+        <v>-150</v>
       </c>
       <c r="M100" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.666667</v>
       </c>
       <c r="N100" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.6</v>
       </c>
       <c r="O100" s="28" t="n">
-        <v>0.639939</v>
+        <v>0.821797</v>
       </c>
       <c r="P100" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q100" s="28" t="n">
-        <v>0.120708</v>
+        <v>0.221797</v>
       </c>
       <c r="R100" s="26" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="S100" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T100" s="24" t="inlineStr">
         <is>
@@ -29104,7 +29209,7 @@
       <c r="AD100" s="24" t="n"/>
       <c r="AE100" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.5200 (aec-wta-kriliu-darvid-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Alexandra Eala p=0.178 vs Jessica Pegula. Executable ask 0.6000 (aec-wta-jespeg-aleeal-2026-08-02).</t>
         </is>
       </c>
       <c r="AF100" s="31" t="inlineStr">
@@ -29145,32 +29250,32 @@
       </c>
       <c r="AP100" s="24" t="inlineStr">
         <is>
-          <t>Darja Vidmanova</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AQ100" s="24" t="inlineStr">
         <is>
-          <t>Darja Vidmanova</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AR100" s="24" t="inlineStr">
         <is>
-          <t>Darja Vidmanova</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AS100" s="24" t="inlineStr">
         <is>
-          <t>Kristina Liutova</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AT100" s="24" t="inlineStr">
         <is>
-          <t>Kristina Liutova</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AU100" s="24" t="inlineStr">
         <is>
-          <t>Kristina Liutova</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AV100" s="24" t="n"/>
@@ -29223,7 +29328,7 @@
       </c>
       <c r="BH100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:49.276365Z</t>
+          <t>2026-08-02T13:03:06.520346Z</t>
         </is>
       </c>
       <c r="BI100" s="24" t="inlineStr">
@@ -29233,13 +29338,13 @@
       </c>
       <c r="BJ100" s="25" t="n"/>
       <c r="BK100" s="26" t="n">
-        <v>-108</v>
+        <v>-150</v>
       </c>
       <c r="BL100" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.666667</v>
       </c>
       <c r="BM100" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.6</v>
       </c>
       <c r="BN100" s="28" t="n"/>
       <c r="BO100" s="28" t="n"/>
@@ -29269,26 +29374,27 @@
       <c r="CM100" s="24" t="n"/>
       <c r="CN100" s="24" t="n"/>
       <c r="CO100" s="24" t="n"/>
+      <c r="CP100" s="24" t="n"/>
     </row>
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>da9d6d1b27154233</t>
+          <t>7d464ad36d7c4d6c</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00Z</t>
+          <t>2026-08-02T17:30Z</t>
         </is>
       </c>
       <c r="D101" s="24" t="inlineStr">
         <is>
-          <t>1073-2026:179603</t>
+          <t>1067-2026:179469</t>
         </is>
       </c>
       <c r="E101" s="24" t="inlineStr">
@@ -29298,12 +29404,12 @@
       </c>
       <c r="F101" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Darja Vidmanova</t>
         </is>
       </c>
       <c r="G101" s="24" t="inlineStr">
         <is>
-          <t>Kaitlin Quevedo</t>
+          <t>Kristina Liutova</t>
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr">
@@ -29313,7 +29419,7 @@
       </c>
       <c r="I101" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J101" s="25" t="n"/>
@@ -29323,25 +29429,25 @@
         </is>
       </c>
       <c r="L101" s="26" t="n">
-        <v>-138</v>
+        <v>-108</v>
       </c>
       <c r="M101" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.925926</v>
       </c>
       <c r="N101" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.519231</v>
       </c>
       <c r="O101" s="28" t="n">
-        <v>0.608004</v>
+        <v>0.639939</v>
       </c>
       <c r="P101" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q101" s="28" t="n">
-        <v>0.028172</v>
+        <v>0.120708</v>
       </c>
       <c r="R101" s="26" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="S101" s="29" t="n">
         <v>1.5</v>
@@ -29367,7 +29473,7 @@
       <c r="AD101" s="24" t="n"/>
       <c r="AE101" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Laura Samson p=0.392 vs Kaitlin Quevedo. Executable ask 0.5800 (aec-wta-kaique-lausam-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.5200 (aec-wta-kriliu-darvid-2026-08-02).</t>
         </is>
       </c>
       <c r="AF101" s="31" t="inlineStr">
@@ -29408,32 +29514,32 @@
       </c>
       <c r="AP101" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Darja Vidmanova</t>
         </is>
       </c>
       <c r="AQ101" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Darja Vidmanova</t>
         </is>
       </c>
       <c r="AR101" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Darja Vidmanova</t>
         </is>
       </c>
       <c r="AS101" s="24" t="inlineStr">
         <is>
-          <t>Kaitlin Quevedo</t>
+          <t>Kristina Liutova</t>
         </is>
       </c>
       <c r="AT101" s="24" t="inlineStr">
         <is>
-          <t>Kaitlin Quevedo</t>
+          <t>Kristina Liutova</t>
         </is>
       </c>
       <c r="AU101" s="24" t="inlineStr">
         <is>
-          <t>Kaitlin Quevedo</t>
+          <t>Kristina Liutova</t>
         </is>
       </c>
       <c r="AV101" s="24" t="n"/>
@@ -29486,7 +29592,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:47.814266Z</t>
+          <t>2026-08-02T13:02:54.201124Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -29496,13 +29602,13 @@
       </c>
       <c r="BJ101" s="25" t="n"/>
       <c r="BK101" s="26" t="n">
-        <v>-138</v>
+        <v>-108</v>
       </c>
       <c r="BL101" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.925926</v>
       </c>
       <c r="BM101" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.519231</v>
       </c>
       <c r="BN101" s="28" t="n"/>
       <c r="BO101" s="28" t="n"/>
@@ -29532,16 +29638,17 @@
       <c r="CM101" s="24" t="n"/>
       <c r="CN101" s="24" t="n"/>
       <c r="CO101" s="24" t="n"/>
+      <c r="CP101" s="24" t="n"/>
     </row>
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>624f45d41cca4fad</t>
+          <t>29e6aff4398b4d37</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -29749,7 +29856,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:48.787189Z</t>
+          <t>2026-08-02T13:02:54.035256Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -29795,16 +29902,17 @@
       <c r="CM102" s="24" t="n"/>
       <c r="CN102" s="24" t="n"/>
       <c r="CO102" s="24" t="n"/>
+      <c r="CP102" s="24" t="n"/>
     </row>
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>64c699a375f4400a</t>
+          <t>d7f806886b994cbd</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -29849,13 +29957,13 @@
         </is>
       </c>
       <c r="L103" s="26" t="n">
-        <v>-150</v>
+        <v>-127</v>
       </c>
       <c r="M103" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.787402</v>
       </c>
       <c r="N103" s="28" t="n">
-        <v>0.6</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O103" s="28" t="n">
         <v>0.548768</v>
@@ -29864,10 +29972,10 @@
         <v>0.05</v>
       </c>
       <c r="Q103" s="28" t="n">
-        <v>-0.051232</v>
+        <v>-0.010703</v>
       </c>
       <c r="R103" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S103" s="29" t="n">
         <v>1</v>
@@ -29893,7 +30001,7 @@
       <c r="AD103" s="24" t="n"/>
       <c r="AE103" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Cristina Bucsa p=0.549 vs Moyuka Uchijima. Executable ask 0.6000 (aec-wta-moyuch-cribuc-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Cristina Bucsa p=0.549 vs Moyuka Uchijima. Executable ask 0.5600 (aec-wta-moyuch-cribuc-2026-08-02).</t>
         </is>
       </c>
       <c r="AF103" s="31" t="inlineStr">
@@ -30012,7 +30120,7 @@
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:47.754501Z</t>
+          <t>2026-08-02T13:02:52.534967Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -30022,13 +30130,13 @@
       </c>
       <c r="BJ103" s="25" t="n"/>
       <c r="BK103" s="26" t="n">
-        <v>-150</v>
+        <v>-127</v>
       </c>
       <c r="BL103" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.787402</v>
       </c>
       <c r="BM103" s="28" t="n">
-        <v>0.6</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN103" s="28" t="n"/>
       <c r="BO103" s="28" t="n"/>
@@ -30058,16 +30166,17 @@
       <c r="CM103" s="24" t="n"/>
       <c r="CN103" s="24" t="n"/>
       <c r="CO103" s="24" t="n"/>
+      <c r="CP103" s="24" t="n"/>
     </row>
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>c8fc8717e2734e88</t>
+          <t>1e896c6181374872</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -30112,13 +30221,13 @@
         </is>
       </c>
       <c r="L104" s="26" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="M104" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.724638</v>
       </c>
       <c r="N104" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.579832</v>
       </c>
       <c r="O104" s="28" t="n">
         <v>0.597848</v>
@@ -30127,10 +30236,10 @@
         <v>0.05</v>
       </c>
       <c r="Q104" s="28" t="n">
-        <v>0.007684</v>
+        <v>0.018016</v>
       </c>
       <c r="R104" s="26" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="S104" s="29" t="n">
         <v>1.25</v>
@@ -30156,7 +30265,7 @@
       <c r="AD104" s="24" t="n"/>
       <c r="AE104" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.5900 (aec-wta-xiywan-sarbej-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.5800 (aec-wta-xiywan-sarbej-2026-08-02).</t>
         </is>
       </c>
       <c r="AF104" s="31" t="inlineStr">
@@ -30275,7 +30384,7 @@
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:47.739233Z</t>
+          <t>2026-08-02T13:02:52.010592Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -30285,13 +30394,13 @@
       </c>
       <c r="BJ104" s="25" t="n"/>
       <c r="BK104" s="26" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="BL104" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.724638</v>
       </c>
       <c r="BM104" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.579832</v>
       </c>
       <c r="BN104" s="28" t="n"/>
       <c r="BO104" s="28" t="n"/>
@@ -30321,16 +30430,17 @@
       <c r="CM104" s="24" t="n"/>
       <c r="CN104" s="24" t="n"/>
       <c r="CO104" s="24" t="n"/>
+      <c r="CP104" s="24" t="n"/>
     </row>
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>56444c2c506641fe</t>
+          <t>8e7ed969290f4b2b</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -30538,7 +30648,7 @@
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:51.971588Z</t>
+          <t>2026-08-02T13:02:57.273126Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -30584,16 +30694,17 @@
       <c r="CM105" s="24" t="n"/>
       <c r="CN105" s="24" t="n"/>
       <c r="CO105" s="24" t="n"/>
+      <c r="CP105" s="24" t="n"/>
     </row>
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>6c0b5bf65dc84348</t>
+          <t>c38d58a0356a465c</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
@@ -30638,13 +30749,13 @@
         </is>
       </c>
       <c r="L106" s="26" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="M106" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.925926</v>
       </c>
       <c r="N106" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.519231</v>
       </c>
       <c r="O106" s="28" t="n">
         <v>0.549832</v>
@@ -30653,10 +30764,10 @@
         <v>0.05</v>
       </c>
       <c r="Q106" s="28" t="n">
-        <v>-0.009639</v>
+        <v>0.030601</v>
       </c>
       <c r="R106" s="26" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="S106" s="29" t="n">
         <v>1</v>
@@ -30682,7 +30793,7 @@
       <c r="AD106" s="24" t="n"/>
       <c r="AE106" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Antonia Ruzic p=0.550 vs Lois Boisson. Executable ask 0.5600 (aec-wta-loiboi-antruz-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Antonia Ruzic p=0.550 vs Lois Boisson. Executable ask 0.5200 (aec-wta-loiboi-antruz-2026-08-02).</t>
         </is>
       </c>
       <c r="AF106" s="31" t="inlineStr">
@@ -30801,7 +30912,7 @@
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:53.441330Z</t>
+          <t>2026-08-02T13:02:59.101567Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -30811,13 +30922,13 @@
       </c>
       <c r="BJ106" s="25" t="n"/>
       <c r="BK106" s="26" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="BL106" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.925926</v>
       </c>
       <c r="BM106" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.519231</v>
       </c>
       <c r="BN106" s="28" t="n"/>
       <c r="BO106" s="28" t="n"/>
@@ -30847,16 +30958,17 @@
       <c r="CM106" s="24" t="n"/>
       <c r="CN106" s="24" t="n"/>
       <c r="CO106" s="24" t="n"/>
+      <c r="CP106" s="24" t="n"/>
     </row>
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>91db2bf60c5d4e85</t>
+          <t>ba8d1777216147f7</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
@@ -30901,13 +31013,13 @@
         </is>
       </c>
       <c r="L107" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="M107" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="N107" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="O107" s="28" t="n">
         <v>0.52927</v>
@@ -30916,7 +31028,7 @@
         <v>0.05</v>
       </c>
       <c r="Q107" s="28" t="n">
-        <v>-0.07073</v>
+        <v>-0.060894</v>
       </c>
       <c r="R107" s="26" t="n">
         <v>0</v>
@@ -30945,7 +31057,7 @@
       <c r="AD107" s="24" t="n"/>
       <c r="AE107" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Katherine Sebov p=0.471 vs Aoi Ito. Executable ask 0.6000 (aec-wta-aoiito-katseb-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Katherine Sebov p=0.471 vs Aoi Ito. Executable ask 0.5900 (aec-wta-aoiito-katseb-2026-08-02).</t>
         </is>
       </c>
       <c r="AF107" s="31" t="inlineStr">
@@ -31064,7 +31176,7 @@
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:54.664274Z</t>
+          <t>2026-08-02T13:03:00.691051Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -31074,13 +31186,13 @@
       </c>
       <c r="BJ107" s="25" t="n"/>
       <c r="BK107" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="BL107" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="BM107" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="BN107" s="28" t="n"/>
       <c r="BO107" s="28" t="n"/>
@@ -31110,16 +31222,17 @@
       <c r="CM107" s="24" t="n"/>
       <c r="CN107" s="24" t="n"/>
       <c r="CO107" s="24" t="n"/>
+      <c r="CP107" s="24" t="n"/>
     </row>
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>c0183b77a2ac45e8</t>
+          <t>8b27c3e5857049f5</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
@@ -31164,13 +31277,13 @@
         </is>
       </c>
       <c r="L108" s="26" t="n">
-        <v>-186</v>
+        <v>-213</v>
       </c>
       <c r="M108" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.469484</v>
       </c>
       <c r="N108" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.680511</v>
       </c>
       <c r="O108" s="28" t="n">
         <v>0.736958</v>
@@ -31179,10 +31292,10 @@
         <v>0.05</v>
       </c>
       <c r="Q108" s="28" t="n">
-        <v>0.086608</v>
+        <v>0.056447</v>
       </c>
       <c r="R108" s="26" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="S108" s="29" t="n">
         <v>2</v>
@@ -31208,7 +31321,7 @@
       <c r="AD108" s="24" t="n"/>
       <c r="AE108" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Camila Osorio p=0.737 vs Lucrezia Stefanini. Executable ask 0.6500 (aec-wta-lucste-camoso-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Camila Osorio p=0.737 vs Lucrezia Stefanini. Executable ask 0.6800 (aec-wta-lucste-camoso-2026-08-02).</t>
         </is>
       </c>
       <c r="AF108" s="31" t="inlineStr">
@@ -31327,7 +31440,7 @@
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:50.773487Z</t>
+          <t>2026-08-02T13:02:56.120241Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -31337,13 +31450,13 @@
       </c>
       <c r="BJ108" s="25" t="n"/>
       <c r="BK108" s="26" t="n">
-        <v>-186</v>
+        <v>-213</v>
       </c>
       <c r="BL108" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.469484</v>
       </c>
       <c r="BM108" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.680511</v>
       </c>
       <c r="BN108" s="28" t="n"/>
       <c r="BO108" s="28" t="n"/>
@@ -31373,16 +31486,17 @@
       <c r="CM108" s="24" t="n"/>
       <c r="CN108" s="24" t="n"/>
       <c r="CO108" s="24" t="n"/>
+      <c r="CP108" s="24" t="n"/>
     </row>
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>8af8b4a297a34ce3</t>
+          <t>da00bccb495b4f35</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
@@ -31427,13 +31541,13 @@
         </is>
       </c>
       <c r="L109" s="26" t="n">
-        <v>-108</v>
+        <v>117</v>
       </c>
       <c r="M109" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.17</v>
       </c>
       <c r="N109" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.460829</v>
       </c>
       <c r="O109" s="28" t="n">
         <v>0.53051</v>
@@ -31442,10 +31556,10 @@
         <v>0.05</v>
       </c>
       <c r="Q109" s="28" t="n">
-        <v>0.011279</v>
+        <v>0.06968100000000001</v>
       </c>
       <c r="R109" s="26" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="S109" s="29" t="n">
         <v>1</v>
@@ -31471,7 +31585,7 @@
       <c r="AD109" s="24" t="n"/>
       <c r="AE109" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Anna Blinkova p=0.469 vs Rebecca Sramkova. Executable ask 0.5200 (aec-wta-rebsra-annbli-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Anna Blinkova p=0.469 vs Rebecca Sramkova. Executable ask 0.4600 (aec-wta-rebsra-annbli-2026-08-02).</t>
         </is>
       </c>
       <c r="AF109" s="31" t="inlineStr">
@@ -31590,7 +31704,7 @@
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:56.021809Z</t>
+          <t>2026-08-02T13:03:02.249448Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -31600,13 +31714,13 @@
       </c>
       <c r="BJ109" s="25" t="n"/>
       <c r="BK109" s="26" t="n">
-        <v>-108</v>
+        <v>117</v>
       </c>
       <c r="BL109" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.17</v>
       </c>
       <c r="BM109" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.460829</v>
       </c>
       <c r="BN109" s="28" t="n"/>
       <c r="BO109" s="28" t="n"/>
@@ -31636,16 +31750,17 @@
       <c r="CM109" s="24" t="n"/>
       <c r="CN109" s="24" t="n"/>
       <c r="CO109" s="24" t="n"/>
+      <c r="CP109" s="24" t="n"/>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>0ace72a6c9964cf8</t>
+          <t>1753b525b0f44db0</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
@@ -31690,13 +31805,13 @@
         </is>
       </c>
       <c r="L110" s="26" t="n">
-        <v>-156</v>
+        <v>-186</v>
       </c>
       <c r="M110" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.537634</v>
       </c>
       <c r="N110" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.65035</v>
       </c>
       <c r="O110" s="28" t="n">
         <v>0.756798</v>
@@ -31705,10 +31820,10 @@
         <v>0.05</v>
       </c>
       <c r="Q110" s="28" t="n">
-        <v>0.147423</v>
+        <v>0.106448</v>
       </c>
       <c r="R110" s="26" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S110" s="29" t="n">
         <v>2</v>
@@ -31734,7 +31849,7 @@
       <c r="AD110" s="24" t="n"/>
       <c r="AE110" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6100 (aec-wta-emejon-lantar-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6500 (aec-wta-emejon-lantar-2026-08-02).</t>
         </is>
       </c>
       <c r="AF110" s="31" t="inlineStr">
@@ -31853,7 +31968,7 @@
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:57.197277Z</t>
+          <t>2026-08-02T13:03:03.966317Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -31863,13 +31978,13 @@
       </c>
       <c r="BJ110" s="25" t="n"/>
       <c r="BK110" s="26" t="n">
-        <v>-156</v>
+        <v>-186</v>
       </c>
       <c r="BL110" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.537634</v>
       </c>
       <c r="BM110" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.65035</v>
       </c>
       <c r="BN110" s="28" t="n"/>
       <c r="BO110" s="28" t="n"/>
@@ -31899,16 +32014,17 @@
       <c r="CM110" s="24" t="n"/>
       <c r="CN110" s="24" t="n"/>
       <c r="CO110" s="24" t="n"/>
+      <c r="CP110" s="24" t="n"/>
     </row>
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>f49ff5b0d84e40e8</t>
+          <t>4d7224f9b9324e14</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
@@ -31953,13 +32069,13 @@
         </is>
       </c>
       <c r="L111" s="26" t="n">
-        <v>-733</v>
+        <v>-669</v>
       </c>
       <c r="M111" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.149477</v>
       </c>
       <c r="N111" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.869961</v>
       </c>
       <c r="O111" s="28" t="n">
         <v>0.7637620000000001</v>
@@ -31968,7 +32084,7 @@
         <v>0.05</v>
       </c>
       <c r="Q111" s="28" t="n">
-        <v>-0.11619</v>
+        <v>-0.106199</v>
       </c>
       <c r="R111" s="26" t="n">
         <v>0</v>
@@ -31997,7 +32113,7 @@
       <c r="AD111" s="24" t="n"/>
       <c r="AE111" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Cadence Brace p=0.236 vs McCartney Kessler. Executable ask 0.8800 (aec-wta-mcckes-cadbra-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Cadence Brace p=0.236 vs McCartney Kessler. Executable ask 0.8700 (aec-wta-mcckes-cadbra-2026-08-02).</t>
         </is>
       </c>
       <c r="AF111" s="31" t="inlineStr">
@@ -32116,7 +32232,7 @@
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:58.597855Z</t>
+          <t>2026-08-02T13:03:05.518836Z</t>
         </is>
       </c>
       <c r="BI111" s="24" t="inlineStr">
@@ -32126,13 +32242,13 @@
       </c>
       <c r="BJ111" s="25" t="n"/>
       <c r="BK111" s="26" t="n">
-        <v>-733</v>
+        <v>-669</v>
       </c>
       <c r="BL111" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.149477</v>
       </c>
       <c r="BM111" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.869961</v>
       </c>
       <c r="BN111" s="28" t="n"/>
       <c r="BO111" s="28" t="n"/>
@@ -32162,16 +32278,17 @@
       <c r="CM111" s="24" t="n"/>
       <c r="CN111" s="24" t="n"/>
       <c r="CO111" s="24" t="n"/>
+      <c r="CP111" s="24" t="n"/>
     </row>
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>5466db52b99548f5</t>
+          <t>9051b14886ef491b</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
@@ -32379,7 +32496,7 @@
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:55:00.882635Z</t>
+          <t>2026-08-02T13:03:08.039049Z</t>
         </is>
       </c>
       <c r="BI112" s="24" t="inlineStr">
@@ -32425,16 +32542,17 @@
       <c r="CM112" s="24" t="n"/>
       <c r="CN112" s="24" t="n"/>
       <c r="CO112" s="24" t="n"/>
+      <c r="CP112" s="24" t="n"/>
     </row>
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>bf3daa1ac89a4b1a</t>
+          <t>052104783b3b428d</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
@@ -32642,7 +32760,7 @@
       </c>
       <c r="BH113" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:55:00.982396Z</t>
+          <t>2026-08-02T13:03:08.272891Z</t>
         </is>
       </c>
       <c r="BI113" s="24" t="inlineStr">
@@ -32688,16 +32806,17 @@
       <c r="CM113" s="24" t="n"/>
       <c r="CN113" s="24" t="n"/>
       <c r="CO113" s="24" t="n"/>
+      <c r="CP113" s="24" t="n"/>
     </row>
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>6566991c6bb04ce0</t>
+          <t>cedaf60a1a1b4b62</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:58:14.597238Z</t>
+          <t>2026-08-02T13:06:07.951791Z</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
@@ -32905,7 +33024,7 @@
       </c>
       <c r="BH114" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:55:01.453864Z</t>
+          <t>2026-08-02T13:03:08.587763Z</t>
         </is>
       </c>
       <c r="BI114" s="24" t="inlineStr">
@@ -32951,6 +33070,7 @@
       <c r="CM114" s="24" t="n"/>
       <c r="CN114" s="24" t="n"/>
       <c r="CO114" s="24" t="n"/>
+      <c r="CP114" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP114" headerRowCount="1">
-  <autoFilter ref="A1:CP114"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP112" headerRowCount="1">
+  <autoFilter ref="A1:CP112"/>
   <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -753,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$114)</f>
+        <f>COUNTA('Picks'!$A$2:$A$112)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$114,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$112,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$114,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$112,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"win")+COUNTIFS('Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"win")+COUNTIFS('Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$114,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$112,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"win")/(COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"win")+COUNTIFS('Picks'!$BX$2:$BX$114,"&gt;0",'Picks'!$V$2:$V$114,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"win")/(COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"win")+COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$114)/SUM('Picks'!$BX$2:$BX$114),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$112)/SUM('Picks'!$BX$2:$BX$112),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$114)</f>
+        <f>SUM('Picks'!$BY$2:$BY$112)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$114,"&lt;&gt;",'Picks'!$AB$2:$AB$114),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$112,"&lt;&gt;",'Picks'!$AB$2:$AB$112),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$114,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$114,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$112,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$112,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$114,'Picks'!$AM$2:$AM$114,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$112,'Picks'!$AM$2:$AM$112,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A14,'Picks'!$U$2:$U$114,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A14,'Picks'!$U$2:$U$112,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A14,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A14,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A14,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A14,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$114,'Picks'!$H$2:$H$114,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$112,'Picks'!$H$2:$H$112,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$114,'Picks'!$H$2:$H$114,$A14,'Picks'!$U$2:$U$114,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$112,'Picks'!$H$2:$H$112,$A14,'Picks'!$U$2:$U$112,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A15,'Picks'!$U$2:$U$114,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A15,'Picks'!$U$2:$U$112,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A15,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A15,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A15,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A15,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$114,'Picks'!$H$2:$H$114,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$112,'Picks'!$H$2:$H$112,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$114,'Picks'!$H$2:$H$114,$A15,'Picks'!$U$2:$U$114,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$112,'Picks'!$H$2:$H$112,$A15,'Picks'!$U$2:$U$112,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A16,'Picks'!$U$2:$U$114,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A16,'Picks'!$U$2:$U$112,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A16,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A16,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$114,$A16,'Picks'!$U$2:$U$114,"settled",'Picks'!$V$2:$V$114,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$112,$A16,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$114,'Picks'!$H$2:$H$114,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$112,'Picks'!$H$2:$H$112,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$114,'Picks'!$H$2:$H$114,$A16,'Picks'!$U$2:$U$114,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$112,'Picks'!$H$2:$H$112,$A16,'Picks'!$U$2:$U$112,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP114"/>
+  <dimension ref="A1:CP112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -28931,18 +28931,38 @@
       </c>
       <c r="U99" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V99" s="24" t="n"/>
-      <c r="W99" s="26" t="n"/>
-      <c r="X99" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V99" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W99" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X99" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y99" s="25" t="n"/>
-      <c r="Z99" s="26" t="n"/>
-      <c r="AA99" s="28" t="n"/>
-      <c r="AB99" s="28" t="n"/>
-      <c r="AC99" s="30" t="n"/>
-      <c r="AD99" s="24" t="n"/>
+      <c r="Z99" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA99" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB99" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC99" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD99" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:53:31.398063Z</t>
+        </is>
+      </c>
       <c r="AE99" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Laura Samson p=0.392 vs Kaitlin Quevedo. Executable ask 0.5800 (aec-wta-kaique-lausam-2026-08-02).</t>
@@ -28955,7 +28975,7 @@
       </c>
       <c r="AG99" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH99" s="24" t="n"/>
@@ -29085,8 +29105,12 @@
       <c r="BN99" s="28" t="n"/>
       <c r="BO99" s="28" t="n"/>
       <c r="BP99" s="25" t="n"/>
-      <c r="BQ99" s="27" t="n"/>
-      <c r="BR99" s="28" t="n"/>
+      <c r="BQ99" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR99" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS99" s="28" t="n"/>
       <c r="BT99" s="28" t="n"/>
       <c r="BU99" s="25" t="n"/>
@@ -29115,12 +29139,12 @@
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
         <is>
-          <t>55bbf085e03f44e4</t>
+          <t>2ccf46ab0ab040ed</t>
         </is>
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
@@ -29165,13 +29189,13 @@
         </is>
       </c>
       <c r="L100" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="M100" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="N100" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="O100" s="28" t="n">
         <v>0.821797</v>
@@ -29180,7 +29204,7 @@
         <v>0.05</v>
       </c>
       <c r="Q100" s="28" t="n">
-        <v>0.221797</v>
+        <v>0.231633</v>
       </c>
       <c r="R100" s="26" t="n">
         <v>100</v>
@@ -29209,7 +29233,7 @@
       <c r="AD100" s="24" t="n"/>
       <c r="AE100" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alexandra Eala p=0.178 vs Jessica Pegula. Executable ask 0.6000 (aec-wta-jespeg-aleeal-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Alexandra Eala p=0.178 vs Jessica Pegula. Executable ask 0.5900 (aec-wta-jespeg-aleeal-2026-08-02).</t>
         </is>
       </c>
       <c r="AF100" s="31" t="inlineStr">
@@ -29227,7 +29251,7 @@
       <c r="AJ100" s="31" t="n"/>
       <c r="AK100" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL100" s="26" t="n">
@@ -29235,17 +29259,17 @@
       </c>
       <c r="AM100" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN100" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO100" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP100" s="24" t="inlineStr">
@@ -29328,7 +29352,7 @@
       </c>
       <c r="BH100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:03:06.520346Z</t>
+          <t>2026-08-02T15:46:52.794231Z</t>
         </is>
       </c>
       <c r="BI100" s="24" t="inlineStr">
@@ -29338,13 +29362,13 @@
       </c>
       <c r="BJ100" s="25" t="n"/>
       <c r="BK100" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="BL100" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="BM100" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="BN100" s="28" t="n"/>
       <c r="BO100" s="28" t="n"/>
@@ -29374,17 +29398,21 @@
       <c r="CM100" s="24" t="n"/>
       <c r="CN100" s="24" t="n"/>
       <c r="CO100" s="24" t="n"/>
-      <c r="CP100" s="24" t="n"/>
+      <c r="CP100" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>7d464ad36d7c4d6c</t>
+          <t>a7f951016379499b</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -29429,13 +29457,13 @@
         </is>
       </c>
       <c r="L101" s="26" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="M101" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.04</v>
       </c>
       <c r="N101" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.490196</v>
       </c>
       <c r="O101" s="28" t="n">
         <v>0.639939</v>
@@ -29444,10 +29472,10 @@
         <v>0.05</v>
       </c>
       <c r="Q101" s="28" t="n">
-        <v>0.120708</v>
+        <v>0.149743</v>
       </c>
       <c r="R101" s="26" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="S101" s="29" t="n">
         <v>1.5</v>
@@ -29473,7 +29501,7 @@
       <c r="AD101" s="24" t="n"/>
       <c r="AE101" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.5200 (aec-wta-kriliu-darvid-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.4900 (aec-wta-kriliu-darvid-2026-08-02).</t>
         </is>
       </c>
       <c r="AF101" s="31" t="inlineStr">
@@ -29491,7 +29519,7 @@
       <c r="AJ101" s="31" t="n"/>
       <c r="AK101" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL101" s="26" t="n">
@@ -29499,17 +29527,17 @@
       </c>
       <c r="AM101" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN101" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO101" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP101" s="24" t="inlineStr">
@@ -29592,7 +29620,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:54.201124Z</t>
+          <t>2026-08-02T15:46:42.019193Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -29602,13 +29630,13 @@
       </c>
       <c r="BJ101" s="25" t="n"/>
       <c r="BK101" s="26" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="BL101" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.04</v>
       </c>
       <c r="BM101" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.490196</v>
       </c>
       <c r="BN101" s="28" t="n"/>
       <c r="BO101" s="28" t="n"/>
@@ -29638,17 +29666,21 @@
       <c r="CM101" s="24" t="n"/>
       <c r="CN101" s="24" t="n"/>
       <c r="CO101" s="24" t="n"/>
-      <c r="CP101" s="24" t="n"/>
+      <c r="CP101" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>29e6aff4398b4d37</t>
+          <t>c0cf59bfb705465c</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -29773,7 +29805,7 @@
       </c>
       <c r="AO102" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP102" s="24" t="inlineStr">
@@ -29856,7 +29888,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:54.035256Z</t>
+          <t>2026-08-02T15:46:40.733235Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -29902,17 +29934,21 @@
       <c r="CM102" s="24" t="n"/>
       <c r="CN102" s="24" t="n"/>
       <c r="CO102" s="24" t="n"/>
-      <c r="CP102" s="24" t="n"/>
+      <c r="CP102" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>d7f806886b994cbd</t>
+          <t>1631795568fd45da</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -29922,7 +29958,7 @@
       </c>
       <c r="D103" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182279</t>
+          <t>421-2026:182280</t>
         </is>
       </c>
       <c r="E103" s="24" t="inlineStr">
@@ -29932,12 +29968,12 @@
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>Cristina Bucsa</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="G103" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Wang Xiyu</t>
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr">
@@ -29957,28 +29993,28 @@
         </is>
       </c>
       <c r="L103" s="26" t="n">
-        <v>-127</v>
+        <v>-144</v>
       </c>
       <c r="M103" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.694444</v>
       </c>
       <c r="N103" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.590164</v>
       </c>
       <c r="O103" s="28" t="n">
-        <v>0.548768</v>
+        <v>0.597848</v>
       </c>
       <c r="P103" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q103" s="28" t="n">
-        <v>-0.010703</v>
+        <v>0.007684</v>
       </c>
       <c r="R103" s="26" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="S103" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T103" s="24" t="inlineStr">
         <is>
@@ -30001,7 +30037,7 @@
       <c r="AD103" s="24" t="n"/>
       <c r="AE103" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Cristina Bucsa p=0.549 vs Moyuka Uchijima. Executable ask 0.5600 (aec-wta-moyuch-cribuc-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.5900 (aec-wta-xiywan-sarbej-2026-08-02).</t>
         </is>
       </c>
       <c r="AF103" s="31" t="inlineStr">
@@ -30037,37 +30073,37 @@
       </c>
       <c r="AO103" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP103" s="24" t="inlineStr">
         <is>
-          <t>Cristina Bucsa</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AQ103" s="24" t="inlineStr">
         <is>
-          <t>Cristina Bucsa</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AR103" s="24" t="inlineStr">
         <is>
-          <t>Cristina Bucsa</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AS103" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Wang Xiyu</t>
         </is>
       </c>
       <c r="AT103" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Wang Xiyu</t>
         </is>
       </c>
       <c r="AU103" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Wang Xiyu</t>
         </is>
       </c>
       <c r="AV103" s="24" t="n"/>
@@ -30120,7 +30156,7 @@
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:52.534967Z</t>
+          <t>2026-08-02T15:46:41.086960Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -30130,13 +30166,13 @@
       </c>
       <c r="BJ103" s="25" t="n"/>
       <c r="BK103" s="26" t="n">
-        <v>-127</v>
+        <v>-144</v>
       </c>
       <c r="BL103" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.694444</v>
       </c>
       <c r="BM103" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.590164</v>
       </c>
       <c r="BN103" s="28" t="n"/>
       <c r="BO103" s="28" t="n"/>
@@ -30166,27 +30202,31 @@
       <c r="CM103" s="24" t="n"/>
       <c r="CN103" s="24" t="n"/>
       <c r="CO103" s="24" t="n"/>
-      <c r="CP103" s="24" t="n"/>
+      <c r="CP103" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>1e896c6181374872</t>
+          <t>aa80b38afdc44bf2</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:30Z</t>
+          <t>2026-08-02T18:00Z</t>
         </is>
       </c>
       <c r="D104" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182280</t>
+          <t>421-2026:182257</t>
         </is>
       </c>
       <c r="E104" s="24" t="inlineStr">
@@ -30196,12 +30236,12 @@
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Antonia Ruzic</t>
         </is>
       </c>
       <c r="G104" s="24" t="inlineStr">
         <is>
-          <t>Wang Xiyu</t>
+          <t>Lois Boisson</t>
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr">
@@ -30221,28 +30261,28 @@
         </is>
       </c>
       <c r="L104" s="26" t="n">
-        <v>-138</v>
+        <v>-104</v>
       </c>
       <c r="M104" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.961538</v>
       </c>
       <c r="N104" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.509804</v>
       </c>
       <c r="O104" s="28" t="n">
-        <v>0.597848</v>
+        <v>0.549832</v>
       </c>
       <c r="P104" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q104" s="28" t="n">
-        <v>0.018016</v>
+        <v>0.040028</v>
       </c>
       <c r="R104" s="26" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S104" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T104" s="24" t="inlineStr">
         <is>
@@ -30265,7 +30305,7 @@
       <c r="AD104" s="24" t="n"/>
       <c r="AE104" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.5800 (aec-wta-xiywan-sarbej-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Antonia Ruzic p=0.550 vs Lois Boisson. Executable ask 0.5100 (aec-wta-loiboi-antruz-2026-08-02).</t>
         </is>
       </c>
       <c r="AF104" s="31" t="inlineStr">
@@ -30301,37 +30341,37 @@
       </c>
       <c r="AO104" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP104" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Antonia Ruzic</t>
         </is>
       </c>
       <c r="AQ104" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Antonia Ruzic</t>
         </is>
       </c>
       <c r="AR104" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Antonia Ruzic</t>
         </is>
       </c>
       <c r="AS104" s="24" t="inlineStr">
         <is>
-          <t>Wang Xiyu</t>
+          <t>Lois Boisson</t>
         </is>
       </c>
       <c r="AT104" s="24" t="inlineStr">
         <is>
-          <t>Wang Xiyu</t>
+          <t>Lois Boisson</t>
         </is>
       </c>
       <c r="AU104" s="24" t="inlineStr">
         <is>
-          <t>Wang Xiyu</t>
+          <t>Lois Boisson</t>
         </is>
       </c>
       <c r="AV104" s="24" t="n"/>
@@ -30384,7 +30424,7 @@
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:52.010592Z</t>
+          <t>2026-08-02T15:46:48.248249Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -30394,13 +30434,13 @@
       </c>
       <c r="BJ104" s="25" t="n"/>
       <c r="BK104" s="26" t="n">
-        <v>-138</v>
+        <v>-104</v>
       </c>
       <c r="BL104" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.961538</v>
       </c>
       <c r="BM104" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.509804</v>
       </c>
       <c r="BN104" s="28" t="n"/>
       <c r="BO104" s="28" t="n"/>
@@ -30430,17 +30470,21 @@
       <c r="CM104" s="24" t="n"/>
       <c r="CN104" s="24" t="n"/>
       <c r="CO104" s="24" t="n"/>
-      <c r="CP104" s="24" t="n"/>
+      <c r="CP104" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>8e7ed969290f4b2b</t>
+          <t>d1fcb39b0d8f4e1a</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -30450,7 +30494,7 @@
       </c>
       <c r="D105" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182236</t>
+          <t>421-2026:182268</t>
         </is>
       </c>
       <c r="E105" s="24" t="inlineStr">
@@ -30460,12 +30504,12 @@
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
-          <t>Leolia Jeanjean</t>
+          <t>Katherine Sebov</t>
         </is>
       </c>
       <c r="G105" s="24" t="inlineStr">
         <is>
-          <t>Magdalena Frech</t>
+          <t>Aoi Ito</t>
         </is>
       </c>
       <c r="H105" s="24" t="inlineStr">
@@ -30475,7 +30519,7 @@
       </c>
       <c r="I105" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J105" s="25" t="n"/>
@@ -30485,25 +30529,25 @@
         </is>
       </c>
       <c r="L105" s="26" t="n">
-        <v>150</v>
+        <v>-150</v>
       </c>
       <c r="M105" s="27" t="n">
-        <v>2.5</v>
+        <v>1.666667</v>
       </c>
       <c r="N105" s="28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O105" s="28" t="n">
-        <v>0.504343</v>
+        <v>0.52927</v>
       </c>
       <c r="P105" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q105" s="28" t="n">
-        <v>0.104343</v>
+        <v>-0.07073</v>
       </c>
       <c r="R105" s="26" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="S105" s="29" t="n">
         <v>1</v>
@@ -30529,7 +30573,7 @@
       <c r="AD105" s="24" t="n"/>
       <c r="AE105" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Leolia Jeanjean p=0.504 vs Magdalena Frech. Executable ask 0.4000 (aec-wta-magfre-leojea-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Katherine Sebov p=0.471 vs Aoi Ito. Executable ask 0.6000 (aec-wta-aoiito-katseb-2026-08-02).</t>
         </is>
       </c>
       <c r="AF105" s="31" t="inlineStr">
@@ -30565,37 +30609,37 @@
       </c>
       <c r="AO105" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP105" s="24" t="inlineStr">
         <is>
-          <t>Leolia Jeanjean</t>
+          <t>Katherine Sebov</t>
         </is>
       </c>
       <c r="AQ105" s="24" t="inlineStr">
         <is>
-          <t>Leolia Jeanjean</t>
+          <t>Katherine Sebov</t>
         </is>
       </c>
       <c r="AR105" s="24" t="inlineStr">
         <is>
-          <t>Leolia Jeanjean</t>
+          <t>Katherine Sebov</t>
         </is>
       </c>
       <c r="AS105" s="24" t="inlineStr">
         <is>
-          <t>Magdalena Frech</t>
+          <t>Aoi Ito</t>
         </is>
       </c>
       <c r="AT105" s="24" t="inlineStr">
         <is>
-          <t>Magdalena Frech</t>
+          <t>Aoi Ito</t>
         </is>
       </c>
       <c r="AU105" s="24" t="inlineStr">
         <is>
-          <t>Magdalena Frech</t>
+          <t>Aoi Ito</t>
         </is>
       </c>
       <c r="AV105" s="24" t="n"/>
@@ -30648,7 +30692,7 @@
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:57.273126Z</t>
+          <t>2026-08-02T15:46:44.674546Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -30658,13 +30702,13 @@
       </c>
       <c r="BJ105" s="25" t="n"/>
       <c r="BK105" s="26" t="n">
-        <v>150</v>
+        <v>-150</v>
       </c>
       <c r="BL105" s="27" t="n">
-        <v>2.5</v>
+        <v>1.666667</v>
       </c>
       <c r="BM105" s="28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="BN105" s="28" t="n"/>
       <c r="BO105" s="28" t="n"/>
@@ -30694,17 +30738,21 @@
       <c r="CM105" s="24" t="n"/>
       <c r="CN105" s="24" t="n"/>
       <c r="CO105" s="24" t="n"/>
-      <c r="CP105" s="24" t="n"/>
+      <c r="CP105" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>c38d58a0356a465c</t>
+          <t>c061c5b94c184f35</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
@@ -30714,7 +30762,7 @@
       </c>
       <c r="D106" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182257</t>
+          <t>421-2026:182284</t>
         </is>
       </c>
       <c r="E106" s="24" t="inlineStr">
@@ -30724,12 +30772,12 @@
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
-          <t>Antonia Ruzic</t>
+          <t>Camila Osorio</t>
         </is>
       </c>
       <c r="G106" s="24" t="inlineStr">
         <is>
-          <t>Lois Boisson</t>
+          <t>Lucrezia Stefanini</t>
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr">
@@ -30749,28 +30797,28 @@
         </is>
       </c>
       <c r="L106" s="26" t="n">
-        <v>-108</v>
+        <v>-233</v>
       </c>
       <c r="M106" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.429185</v>
       </c>
       <c r="N106" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.6997</v>
       </c>
       <c r="O106" s="28" t="n">
-        <v>0.549832</v>
+        <v>0.736958</v>
       </c>
       <c r="P106" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q106" s="28" t="n">
-        <v>0.030601</v>
+        <v>0.037258</v>
       </c>
       <c r="R106" s="26" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S106" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T106" s="24" t="inlineStr">
         <is>
@@ -30793,7 +30841,7 @@
       <c r="AD106" s="24" t="n"/>
       <c r="AE106" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Antonia Ruzic p=0.550 vs Lois Boisson. Executable ask 0.5200 (aec-wta-loiboi-antruz-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Camila Osorio p=0.737 vs Lucrezia Stefanini. Executable ask 0.7000 (aec-wta-lucste-camoso-2026-08-02).</t>
         </is>
       </c>
       <c r="AF106" s="31" t="inlineStr">
@@ -30829,37 +30877,37 @@
       </c>
       <c r="AO106" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP106" s="24" t="inlineStr">
         <is>
-          <t>Antonia Ruzic</t>
+          <t>Camila Osorio</t>
         </is>
       </c>
       <c r="AQ106" s="24" t="inlineStr">
         <is>
-          <t>Antonia Ruzic</t>
+          <t>Camila Osorio</t>
         </is>
       </c>
       <c r="AR106" s="24" t="inlineStr">
         <is>
-          <t>Antonia Ruzic</t>
+          <t>Camila Osorio</t>
         </is>
       </c>
       <c r="AS106" s="24" t="inlineStr">
         <is>
-          <t>Lois Boisson</t>
+          <t>Lucrezia Stefanini</t>
         </is>
       </c>
       <c r="AT106" s="24" t="inlineStr">
         <is>
-          <t>Lois Boisson</t>
+          <t>Lucrezia Stefanini</t>
         </is>
       </c>
       <c r="AU106" s="24" t="inlineStr">
         <is>
-          <t>Lois Boisson</t>
+          <t>Lucrezia Stefanini</t>
         </is>
       </c>
       <c r="AV106" s="24" t="n"/>
@@ -30912,7 +30960,7 @@
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:59.101567Z</t>
+          <t>2026-08-02T15:46:43.798568Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -30922,13 +30970,13 @@
       </c>
       <c r="BJ106" s="25" t="n"/>
       <c r="BK106" s="26" t="n">
-        <v>-108</v>
+        <v>-233</v>
       </c>
       <c r="BL106" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.429185</v>
       </c>
       <c r="BM106" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.6997</v>
       </c>
       <c r="BN106" s="28" t="n"/>
       <c r="BO106" s="28" t="n"/>
@@ -30958,27 +31006,31 @@
       <c r="CM106" s="24" t="n"/>
       <c r="CN106" s="24" t="n"/>
       <c r="CO106" s="24" t="n"/>
-      <c r="CP106" s="24" t="n"/>
+      <c r="CP106" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>ba8d1777216147f7</t>
+          <t>68186bba3f2b4e2e</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T19:30Z</t>
         </is>
       </c>
       <c r="D107" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182268</t>
+          <t>421-2026:182241</t>
         </is>
       </c>
       <c r="E107" s="24" t="inlineStr">
@@ -30988,12 +31040,12 @@
       </c>
       <c r="F107" s="24" t="inlineStr">
         <is>
-          <t>Katherine Sebov</t>
+          <t>Anna Blinkova</t>
         </is>
       </c>
       <c r="G107" s="24" t="inlineStr">
         <is>
-          <t>Aoi Ito</t>
+          <t>Rebecca Sramkova</t>
         </is>
       </c>
       <c r="H107" s="24" t="inlineStr">
@@ -31013,25 +31065,25 @@
         </is>
       </c>
       <c r="L107" s="26" t="n">
-        <v>-144</v>
+        <v>117</v>
       </c>
       <c r="M107" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.17</v>
       </c>
       <c r="N107" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.460829</v>
       </c>
       <c r="O107" s="28" t="n">
-        <v>0.52927</v>
+        <v>0.53051</v>
       </c>
       <c r="P107" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q107" s="28" t="n">
-        <v>-0.060894</v>
+        <v>0.06968100000000001</v>
       </c>
       <c r="R107" s="26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="S107" s="29" t="n">
         <v>1</v>
@@ -31057,7 +31109,7 @@
       <c r="AD107" s="24" t="n"/>
       <c r="AE107" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Katherine Sebov p=0.471 vs Aoi Ito. Executable ask 0.5900 (aec-wta-aoiito-katseb-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Anna Blinkova p=0.469 vs Rebecca Sramkova. Executable ask 0.4600 (aec-wta-rebsra-annbli-2026-08-02).</t>
         </is>
       </c>
       <c r="AF107" s="31" t="inlineStr">
@@ -31075,7 +31127,7 @@
       <c r="AJ107" s="31" t="n"/>
       <c r="AK107" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL107" s="26" t="n">
@@ -31083,47 +31135,47 @@
       </c>
       <c r="AM107" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN107" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO107" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP107" s="24" t="inlineStr">
         <is>
-          <t>Katherine Sebov</t>
+          <t>Anna Blinkova</t>
         </is>
       </c>
       <c r="AQ107" s="24" t="inlineStr">
         <is>
-          <t>Katherine Sebov</t>
+          <t>Anna Blinkova</t>
         </is>
       </c>
       <c r="AR107" s="24" t="inlineStr">
         <is>
-          <t>Katherine Sebov</t>
+          <t>Anna Blinkova</t>
         </is>
       </c>
       <c r="AS107" s="24" t="inlineStr">
         <is>
-          <t>Aoi Ito</t>
+          <t>Rebecca Sramkova</t>
         </is>
       </c>
       <c r="AT107" s="24" t="inlineStr">
         <is>
-          <t>Aoi Ito</t>
+          <t>Rebecca Sramkova</t>
         </is>
       </c>
       <c r="AU107" s="24" t="inlineStr">
         <is>
-          <t>Aoi Ito</t>
+          <t>Rebecca Sramkova</t>
         </is>
       </c>
       <c r="AV107" s="24" t="n"/>
@@ -31176,7 +31228,7 @@
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:03:00.691051Z</t>
+          <t>2026-08-02T15:46:49.636292Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -31186,13 +31238,13 @@
       </c>
       <c r="BJ107" s="25" t="n"/>
       <c r="BK107" s="26" t="n">
-        <v>-144</v>
+        <v>117</v>
       </c>
       <c r="BL107" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.17</v>
       </c>
       <c r="BM107" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.460829</v>
       </c>
       <c r="BN107" s="28" t="n"/>
       <c r="BO107" s="28" t="n"/>
@@ -31222,27 +31274,31 @@
       <c r="CM107" s="24" t="n"/>
       <c r="CN107" s="24" t="n"/>
       <c r="CO107" s="24" t="n"/>
-      <c r="CP107" s="24" t="n"/>
+      <c r="CP107" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>8b27c3e5857049f5</t>
+          <t>e5a2586d0b754134</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T20:00Z</t>
         </is>
       </c>
       <c r="D108" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182284</t>
+          <t>421-2026:182273</t>
         </is>
       </c>
       <c r="E108" s="24" t="inlineStr">
@@ -31252,12 +31308,12 @@
       </c>
       <c r="F108" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="G108" s="24" t="inlineStr">
         <is>
-          <t>Lucrezia Stefanini</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr">
@@ -31277,25 +31333,25 @@
         </is>
       </c>
       <c r="L108" s="26" t="n">
-        <v>-213</v>
+        <v>-186</v>
       </c>
       <c r="M108" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.537634</v>
       </c>
       <c r="N108" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.65035</v>
       </c>
       <c r="O108" s="28" t="n">
-        <v>0.736958</v>
+        <v>0.756798</v>
       </c>
       <c r="P108" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q108" s="28" t="n">
-        <v>0.056447</v>
+        <v>0.106448</v>
       </c>
       <c r="R108" s="26" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="S108" s="29" t="n">
         <v>2</v>
@@ -31321,7 +31377,7 @@
       <c r="AD108" s="24" t="n"/>
       <c r="AE108" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Camila Osorio p=0.737 vs Lucrezia Stefanini. Executable ask 0.6800 (aec-wta-lucste-camoso-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6500 (aec-wta-emejon-lantar-2026-08-02).</t>
         </is>
       </c>
       <c r="AF108" s="31" t="inlineStr">
@@ -31339,7 +31395,7 @@
       <c r="AJ108" s="31" t="n"/>
       <c r="AK108" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL108" s="26" t="n">
@@ -31347,47 +31403,47 @@
       </c>
       <c r="AM108" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN108" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO108" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP108" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AQ108" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AR108" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AS108" s="24" t="inlineStr">
         <is>
-          <t>Lucrezia Stefanini</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AT108" s="24" t="inlineStr">
         <is>
-          <t>Lucrezia Stefanini</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AU108" s="24" t="inlineStr">
         <is>
-          <t>Lucrezia Stefanini</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AV108" s="24" t="n"/>
@@ -31440,7 +31496,7 @@
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:56.120241Z</t>
+          <t>2026-08-02T15:46:51.741348Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -31450,13 +31506,13 @@
       </c>
       <c r="BJ108" s="25" t="n"/>
       <c r="BK108" s="26" t="n">
-        <v>-213</v>
+        <v>-186</v>
       </c>
       <c r="BL108" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.537634</v>
       </c>
       <c r="BM108" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.65035</v>
       </c>
       <c r="BN108" s="28" t="n"/>
       <c r="BO108" s="28" t="n"/>
@@ -31486,27 +31542,31 @@
       <c r="CM108" s="24" t="n"/>
       <c r="CN108" s="24" t="n"/>
       <c r="CO108" s="24" t="n"/>
-      <c r="CP108" s="24" t="n"/>
+      <c r="CP108" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>da00bccb495b4f35</t>
+          <t>8c5a4b8f1d9449a4</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:30Z</t>
+          <t>2026-08-02T21:00Z</t>
         </is>
       </c>
       <c r="D109" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182241</t>
+          <t>421-2026:182240</t>
         </is>
       </c>
       <c r="E109" s="24" t="inlineStr">
@@ -31516,12 +31576,12 @@
       </c>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Cadence Brace</t>
         </is>
       </c>
       <c r="G109" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr">
@@ -31541,28 +31601,28 @@
         </is>
       </c>
       <c r="L109" s="26" t="n">
-        <v>117</v>
+        <v>-614</v>
       </c>
       <c r="M109" s="27" t="n">
-        <v>2.17</v>
+        <v>1.162866</v>
       </c>
       <c r="N109" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.859944</v>
       </c>
       <c r="O109" s="28" t="n">
-        <v>0.53051</v>
+        <v>0.7637620000000001</v>
       </c>
       <c r="P109" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q109" s="28" t="n">
-        <v>0.06968100000000001</v>
+        <v>-0.096182</v>
       </c>
       <c r="R109" s="26" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S109" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T109" s="24" t="inlineStr">
         <is>
@@ -31585,7 +31645,7 @@
       <c r="AD109" s="24" t="n"/>
       <c r="AE109" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Anna Blinkova p=0.469 vs Rebecca Sramkova. Executable ask 0.4600 (aec-wta-rebsra-annbli-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Cadence Brace p=0.236 vs McCartney Kessler. Executable ask 0.8600 (aec-wta-mcckes-cadbra-2026-08-02).</t>
         </is>
       </c>
       <c r="AF109" s="31" t="inlineStr">
@@ -31621,37 +31681,37 @@
       </c>
       <c r="AO109" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP109" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Cadence Brace</t>
         </is>
       </c>
       <c r="AQ109" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Cadence Brace</t>
         </is>
       </c>
       <c r="AR109" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Cadence Brace</t>
         </is>
       </c>
       <c r="AS109" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AT109" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AU109" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AV109" s="24" t="n"/>
@@ -31704,7 +31764,7 @@
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:03:02.249448Z</t>
+          <t>2026-08-02T15:46:54.553392Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -31714,13 +31774,13 @@
       </c>
       <c r="BJ109" s="25" t="n"/>
       <c r="BK109" s="26" t="n">
-        <v>117</v>
+        <v>-614</v>
       </c>
       <c r="BL109" s="27" t="n">
-        <v>2.17</v>
+        <v>1.162866</v>
       </c>
       <c r="BM109" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.859944</v>
       </c>
       <c r="BN109" s="28" t="n"/>
       <c r="BO109" s="28" t="n"/>
@@ -31750,27 +31810,31 @@
       <c r="CM109" s="24" t="n"/>
       <c r="CN109" s="24" t="n"/>
       <c r="CO109" s="24" t="n"/>
-      <c r="CP109" s="24" t="n"/>
+      <c r="CP109" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>1753b525b0f44db0</t>
+          <t>6240c2227d994ec7</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:00Z</t>
+          <t>2026-08-02T21:30Z</t>
         </is>
       </c>
       <c r="D110" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182273</t>
+          <t>421-2026:182283</t>
         </is>
       </c>
       <c r="E110" s="24" t="inlineStr">
@@ -31780,12 +31844,12 @@
       </c>
       <c r="F110" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Elisabetta Cocciaretto</t>
         </is>
       </c>
       <c r="G110" s="24" t="inlineStr">
         <is>
-          <t>Emerson Jones</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr">
@@ -31805,28 +31869,28 @@
         </is>
       </c>
       <c r="L110" s="26" t="n">
-        <v>-186</v>
+        <v>-144</v>
       </c>
       <c r="M110" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.694444</v>
       </c>
       <c r="N110" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.590164</v>
       </c>
       <c r="O110" s="28" t="n">
-        <v>0.756798</v>
+        <v>0.578226</v>
       </c>
       <c r="P110" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q110" s="28" t="n">
-        <v>0.106448</v>
+        <v>-0.011938</v>
       </c>
       <c r="R110" s="26" t="n">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="S110" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T110" s="24" t="inlineStr">
         <is>
@@ -31849,7 +31913,7 @@
       <c r="AD110" s="24" t="n"/>
       <c r="AE110" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6500 (aec-wta-emejon-lantar-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Elisabetta Cocciaretto p=0.578 vs Talia Gibson. Executable ask 0.5900 (aec-wta-talgib-elicoc-2026-08-02).</t>
         </is>
       </c>
       <c r="AF110" s="31" t="inlineStr">
@@ -31885,37 +31949,37 @@
       </c>
       <c r="AO110" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP110" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Elisabetta Cocciaretto</t>
         </is>
       </c>
       <c r="AQ110" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Elisabetta Cocciaretto</t>
         </is>
       </c>
       <c r="AR110" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Elisabetta Cocciaretto</t>
         </is>
       </c>
       <c r="AS110" s="24" t="inlineStr">
         <is>
-          <t>Emerson Jones</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AT110" s="24" t="inlineStr">
         <is>
-          <t>Emerson Jones</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AU110" s="24" t="inlineStr">
         <is>
-          <t>Emerson Jones</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AV110" s="24" t="n"/>
@@ -31968,7 +32032,7 @@
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:03:03.966317Z</t>
+          <t>2026-08-02T15:46:55.125883Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -31978,13 +32042,13 @@
       </c>
       <c r="BJ110" s="25" t="n"/>
       <c r="BK110" s="26" t="n">
-        <v>-186</v>
+        <v>-144</v>
       </c>
       <c r="BL110" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.694444</v>
       </c>
       <c r="BM110" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.590164</v>
       </c>
       <c r="BN110" s="28" t="n"/>
       <c r="BO110" s="28" t="n"/>
@@ -32014,27 +32078,31 @@
       <c r="CM110" s="24" t="n"/>
       <c r="CN110" s="24" t="n"/>
       <c r="CO110" s="24" t="n"/>
-      <c r="CP110" s="24" t="n"/>
+      <c r="CP110" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>4d7224f9b9324e14</t>
+          <t>d8eff19de3f843cc</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T21:00Z</t>
+          <t>2026-08-02T23:00Z</t>
         </is>
       </c>
       <c r="D111" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182240</t>
+          <t>421-2026:182274</t>
         </is>
       </c>
       <c r="E111" s="24" t="inlineStr">
@@ -32044,12 +32112,12 @@
       </c>
       <c r="F111" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Bianca Andreescu</t>
         </is>
       </c>
       <c r="G111" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="H111" s="24" t="inlineStr">
@@ -32069,28 +32137,28 @@
         </is>
       </c>
       <c r="L111" s="26" t="n">
-        <v>-669</v>
+        <v>-150</v>
       </c>
       <c r="M111" s="27" t="n">
-        <v>1.149477</v>
+        <v>1.666667</v>
       </c>
       <c r="N111" s="28" t="n">
-        <v>0.869961</v>
+        <v>0.6</v>
       </c>
       <c r="O111" s="28" t="n">
-        <v>0.7637620000000001</v>
+        <v>0.617346</v>
       </c>
       <c r="P111" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q111" s="28" t="n">
-        <v>-0.106199</v>
+        <v>0.017346</v>
       </c>
       <c r="R111" s="26" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S111" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T111" s="24" t="inlineStr">
         <is>
@@ -32113,7 +32181,7 @@
       <c r="AD111" s="24" t="n"/>
       <c r="AE111" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Cadence Brace p=0.236 vs McCartney Kessler. Executable ask 0.8700 (aec-wta-mcckes-cadbra-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Bianca Andreescu p=0.383 vs Nikola Bartunkova. Executable ask 0.6000 (aec-wta-nikbar-biaand-2026-08-02).</t>
         </is>
       </c>
       <c r="AF111" s="31" t="inlineStr">
@@ -32149,37 +32217,37 @@
       </c>
       <c r="AO111" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP111" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Bianca Andreescu</t>
         </is>
       </c>
       <c r="AQ111" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Bianca Andreescu</t>
         </is>
       </c>
       <c r="AR111" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Bianca Andreescu</t>
         </is>
       </c>
       <c r="AS111" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AT111" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AU111" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AV111" s="24" t="n"/>
@@ -32232,7 +32300,7 @@
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:03:05.518836Z</t>
+          <t>2026-08-02T15:46:55.388422Z</t>
         </is>
       </c>
       <c r="BI111" s="24" t="inlineStr">
@@ -32242,13 +32310,13 @@
       </c>
       <c r="BJ111" s="25" t="n"/>
       <c r="BK111" s="26" t="n">
-        <v>-669</v>
+        <v>-150</v>
       </c>
       <c r="BL111" s="27" t="n">
-        <v>1.149477</v>
+        <v>1.666667</v>
       </c>
       <c r="BM111" s="28" t="n">
-        <v>0.869961</v>
+        <v>0.6</v>
       </c>
       <c r="BN111" s="28" t="n"/>
       <c r="BO111" s="28" t="n"/>
@@ -32278,27 +32346,31 @@
       <c r="CM111" s="24" t="n"/>
       <c r="CN111" s="24" t="n"/>
       <c r="CO111" s="24" t="n"/>
-      <c r="CP111" s="24" t="n"/>
+      <c r="CP111" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>9051b14886ef491b</t>
+          <t>fc4cd1d6df72434b</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
+          <t>2026-08-02T15:50:00.179683Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T21:30Z</t>
+          <t>2026-08-03T00:30Z</t>
         </is>
       </c>
       <c r="D112" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182283</t>
+          <t>421-2026:182281</t>
         </is>
       </c>
       <c r="E112" s="24" t="inlineStr">
@@ -32308,12 +32380,12 @@
       </c>
       <c r="F112" s="24" t="inlineStr">
         <is>
-          <t>Elisabetta Cocciaretto</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="G112" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Yulia Putintseva</t>
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr">
@@ -32323,7 +32395,7 @@
       </c>
       <c r="I112" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J112" s="25" t="n"/>
@@ -32333,28 +32405,28 @@
         </is>
       </c>
       <c r="L112" s="26" t="n">
-        <v>-144</v>
+        <v>-186</v>
       </c>
       <c r="M112" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.537634</v>
       </c>
       <c r="N112" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.65035</v>
       </c>
       <c r="O112" s="28" t="n">
-        <v>0.578226</v>
+        <v>0.630736</v>
       </c>
       <c r="P112" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q112" s="28" t="n">
-        <v>-0.011938</v>
+        <v>-0.019614</v>
       </c>
       <c r="R112" s="26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S112" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T112" s="24" t="inlineStr">
         <is>
@@ -32377,7 +32449,7 @@
       <c r="AD112" s="24" t="n"/>
       <c r="AE112" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Elisabetta Cocciaretto p=0.578 vs Talia Gibson. Executable ask 0.5900 (aec-wta-talgib-elicoc-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Zhang Shuai p=0.369 vs Yulia Putintseva. Executable ask 0.6500 (aec-wta-yulput-shuzha-2026-08-02).</t>
         </is>
       </c>
       <c r="AF112" s="31" t="inlineStr">
@@ -32413,37 +32485,37 @@
       </c>
       <c r="AO112" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP112" s="24" t="inlineStr">
         <is>
-          <t>Elisabetta Cocciaretto</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AQ112" s="24" t="inlineStr">
         <is>
-          <t>Elisabetta Cocciaretto</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AR112" s="24" t="inlineStr">
         <is>
-          <t>Elisabetta Cocciaretto</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AS112" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Yulia Putintseva</t>
         </is>
       </c>
       <c r="AT112" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Yulia Putintseva</t>
         </is>
       </c>
       <c r="AU112" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Yulia Putintseva</t>
         </is>
       </c>
       <c r="AV112" s="24" t="n"/>
@@ -32496,7 +32568,7 @@
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:03:08.039049Z</t>
+          <t>2026-08-02T15:46:55.697720Z</t>
         </is>
       </c>
       <c r="BI112" s="24" t="inlineStr">
@@ -32506,13 +32578,13 @@
       </c>
       <c r="BJ112" s="25" t="n"/>
       <c r="BK112" s="26" t="n">
-        <v>-144</v>
+        <v>-186</v>
       </c>
       <c r="BL112" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.537634</v>
       </c>
       <c r="BM112" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.65035</v>
       </c>
       <c r="BN112" s="28" t="n"/>
       <c r="BO112" s="28" t="n"/>
@@ -32542,535 +32614,11 @@
       <c r="CM112" s="24" t="n"/>
       <c r="CN112" s="24" t="n"/>
       <c r="CO112" s="24" t="n"/>
-      <c r="CP112" s="24" t="n"/>
-    </row>
-    <row r="113" ht="36" customHeight="1">
-      <c r="A113" s="24" t="inlineStr">
-        <is>
-          <t>052104783b3b428d</t>
-        </is>
-      </c>
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
-        </is>
-      </c>
-      <c r="C113" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T23:00Z</t>
-        </is>
-      </c>
-      <c r="D113" s="24" t="inlineStr">
-        <is>
-          <t>421-2026:182274</t>
-        </is>
-      </c>
-      <c r="E113" s="24" t="inlineStr">
-        <is>
-          <t>TENNIS</t>
-        </is>
-      </c>
-      <c r="F113" s="24" t="inlineStr">
-        <is>
-          <t>Bianca Andreescu</t>
-        </is>
-      </c>
-      <c r="G113" s="24" t="inlineStr">
-        <is>
-          <t>Nikola Bartunkova</t>
-        </is>
-      </c>
-      <c r="H113" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I113" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J113" s="25" t="n"/>
-      <c r="K113" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L113" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M113" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="N113" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O113" s="28" t="n">
-        <v>0.617346</v>
-      </c>
-      <c r="P113" s="28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q113" s="28" t="n">
-        <v>0.017346</v>
-      </c>
-      <c r="R113" s="26" t="n">
-        <v>29</v>
-      </c>
-      <c r="S113" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T113" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="U113" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V113" s="24" t="n"/>
-      <c r="W113" s="26" t="n"/>
-      <c r="X113" s="26" t="n"/>
-      <c r="Y113" s="25" t="n"/>
-      <c r="Z113" s="26" t="n"/>
-      <c r="AA113" s="28" t="n"/>
-      <c r="AB113" s="28" t="n"/>
-      <c r="AC113" s="30" t="n"/>
-      <c r="AD113" s="24" t="n"/>
-      <c r="AE113" s="31" t="inlineStr">
-        <is>
-          <t>Surface-blended Elo on Hard: Bianca Andreescu p=0.383 vs Nikola Bartunkova. Executable ask 0.6000 (aec-wta-nikbar-biaand-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF113" s="31" t="inlineStr">
-        <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
-        </is>
-      </c>
-      <c r="AG113" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH113" s="24" t="n"/>
-      <c r="AI113" s="31" t="n"/>
-      <c r="AJ113" s="31" t="n"/>
-      <c r="AK113" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL113" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM113" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN113" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO113" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP113" s="24" t="inlineStr">
-        <is>
-          <t>Bianca Andreescu</t>
-        </is>
-      </c>
-      <c r="AQ113" s="24" t="inlineStr">
-        <is>
-          <t>Bianca Andreescu</t>
-        </is>
-      </c>
-      <c r="AR113" s="24" t="inlineStr">
-        <is>
-          <t>Bianca Andreescu</t>
-        </is>
-      </c>
-      <c r="AS113" s="24" t="inlineStr">
-        <is>
-          <t>Nikola Bartunkova</t>
-        </is>
-      </c>
-      <c r="AT113" s="24" t="inlineStr">
-        <is>
-          <t>Nikola Bartunkova</t>
-        </is>
-      </c>
-      <c r="AU113" s="24" t="inlineStr">
-        <is>
-          <t>Nikola Bartunkova</t>
-        </is>
-      </c>
-      <c r="AV113" s="24" t="n"/>
-      <c r="AW113" s="24" t="n"/>
-      <c r="AX113" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY113" s="24" t="n"/>
-      <c r="AZ113" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA113" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BB113" s="24" t="inlineStr">
-        <is>
-          <t>surface_blended_elo</t>
-        </is>
-      </c>
-      <c r="BC113" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD113" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BE113" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BF113" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG113" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BH113" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T13:03:08.272891Z</t>
-        </is>
-      </c>
-      <c r="BI113" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ113" s="25" t="n"/>
-      <c r="BK113" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BL113" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BM113" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN113" s="28" t="n"/>
-      <c r="BO113" s="28" t="n"/>
-      <c r="BP113" s="25" t="n"/>
-      <c r="BQ113" s="27" t="n"/>
-      <c r="BR113" s="28" t="n"/>
-      <c r="BS113" s="28" t="n"/>
-      <c r="BT113" s="28" t="n"/>
-      <c r="BU113" s="25" t="n"/>
-      <c r="BV113" s="29" t="n"/>
-      <c r="BW113" s="24" t="n"/>
-      <c r="BX113" s="30" t="n"/>
-      <c r="BY113" s="27" t="n"/>
-      <c r="BZ113" s="24" t="n"/>
-      <c r="CA113" s="31" t="n"/>
-      <c r="CB113" s="24" t="n"/>
-      <c r="CC113" s="24" t="n"/>
-      <c r="CD113" s="24" t="n"/>
-      <c r="CE113" s="24" t="n"/>
-      <c r="CF113" s="24" t="n"/>
-      <c r="CG113" s="24" t="n"/>
-      <c r="CH113" s="24" t="n"/>
-      <c r="CI113" s="24" t="n"/>
-      <c r="CJ113" s="24" t="n"/>
-      <c r="CK113" s="24" t="n"/>
-      <c r="CL113" s="24" t="n"/>
-      <c r="CM113" s="24" t="n"/>
-      <c r="CN113" s="24" t="n"/>
-      <c r="CO113" s="24" t="n"/>
-      <c r="CP113" s="24" t="n"/>
-    </row>
-    <row r="114" ht="36" customHeight="1">
-      <c r="A114" s="24" t="inlineStr">
-        <is>
-          <t>cedaf60a1a1b4b62</t>
-        </is>
-      </c>
-      <c r="B114" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T13:06:07.951791Z</t>
-        </is>
-      </c>
-      <c r="C114" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T00:30Z</t>
-        </is>
-      </c>
-      <c r="D114" s="24" t="inlineStr">
-        <is>
-          <t>421-2026:182281</t>
-        </is>
-      </c>
-      <c r="E114" s="24" t="inlineStr">
-        <is>
-          <t>TENNIS</t>
-        </is>
-      </c>
-      <c r="F114" s="24" t="inlineStr">
-        <is>
-          <t>Zhang Shuai</t>
-        </is>
-      </c>
-      <c r="G114" s="24" t="inlineStr">
-        <is>
-          <t>Yulia Putintseva</t>
-        </is>
-      </c>
-      <c r="H114" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I114" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J114" s="25" t="n"/>
-      <c r="K114" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L114" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="M114" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="N114" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="O114" s="28" t="n">
-        <v>0.630736</v>
-      </c>
-      <c r="P114" s="28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q114" s="28" t="n">
-        <v>-0.019614</v>
-      </c>
-      <c r="R114" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="S114" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T114" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="U114" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V114" s="24" t="n"/>
-      <c r="W114" s="26" t="n"/>
-      <c r="X114" s="26" t="n"/>
-      <c r="Y114" s="25" t="n"/>
-      <c r="Z114" s="26" t="n"/>
-      <c r="AA114" s="28" t="n"/>
-      <c r="AB114" s="28" t="n"/>
-      <c r="AC114" s="30" t="n"/>
-      <c r="AD114" s="24" t="n"/>
-      <c r="AE114" s="31" t="inlineStr">
-        <is>
-          <t>Surface-blended Elo on Hard: Zhang Shuai p=0.369 vs Yulia Putintseva. Executable ask 0.6500 (aec-wta-yulput-shuzha-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF114" s="31" t="inlineStr">
-        <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
-        </is>
-      </c>
-      <c r="AG114" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH114" s="24" t="n"/>
-      <c r="AI114" s="31" t="n"/>
-      <c r="AJ114" s="31" t="n"/>
-      <c r="AK114" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL114" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM114" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN114" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO114" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP114" s="24" t="inlineStr">
-        <is>
-          <t>Zhang Shuai</t>
-        </is>
-      </c>
-      <c r="AQ114" s="24" t="inlineStr">
-        <is>
-          <t>Zhang Shuai</t>
-        </is>
-      </c>
-      <c r="AR114" s="24" t="inlineStr">
-        <is>
-          <t>Zhang Shuai</t>
-        </is>
-      </c>
-      <c r="AS114" s="24" t="inlineStr">
-        <is>
-          <t>Yulia Putintseva</t>
-        </is>
-      </c>
-      <c r="AT114" s="24" t="inlineStr">
-        <is>
-          <t>Yulia Putintseva</t>
-        </is>
-      </c>
-      <c r="AU114" s="24" t="inlineStr">
-        <is>
-          <t>Yulia Putintseva</t>
-        </is>
-      </c>
-      <c r="AV114" s="24" t="n"/>
-      <c r="AW114" s="24" t="n"/>
-      <c r="AX114" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY114" s="24" t="n"/>
-      <c r="AZ114" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA114" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BB114" s="24" t="inlineStr">
-        <is>
-          <t>surface_blended_elo</t>
-        </is>
-      </c>
-      <c r="BC114" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD114" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BE114" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BF114" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG114" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BH114" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T13:03:08.587763Z</t>
-        </is>
-      </c>
-      <c r="BI114" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ114" s="25" t="n"/>
-      <c r="BK114" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="BL114" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="BM114" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="BN114" s="28" t="n"/>
-      <c r="BO114" s="28" t="n"/>
-      <c r="BP114" s="25" t="n"/>
-      <c r="BQ114" s="27" t="n"/>
-      <c r="BR114" s="28" t="n"/>
-      <c r="BS114" s="28" t="n"/>
-      <c r="BT114" s="28" t="n"/>
-      <c r="BU114" s="25" t="n"/>
-      <c r="BV114" s="29" t="n"/>
-      <c r="BW114" s="24" t="n"/>
-      <c r="BX114" s="30" t="n"/>
-      <c r="BY114" s="27" t="n"/>
-      <c r="BZ114" s="24" t="n"/>
-      <c r="CA114" s="31" t="n"/>
-      <c r="CB114" s="24" t="n"/>
-      <c r="CC114" s="24" t="n"/>
-      <c r="CD114" s="24" t="n"/>
-      <c r="CE114" s="24" t="n"/>
-      <c r="CF114" s="24" t="n"/>
-      <c r="CG114" s="24" t="n"/>
-      <c r="CH114" s="24" t="n"/>
-      <c r="CI114" s="24" t="n"/>
-      <c r="CJ114" s="24" t="n"/>
-      <c r="CK114" s="24" t="n"/>
-      <c r="CL114" s="24" t="n"/>
-      <c r="CM114" s="24" t="n"/>
-      <c r="CN114" s="24" t="n"/>
-      <c r="CO114" s="24" t="n"/>
-      <c r="CP114" s="24" t="n"/>
+      <c r="CP112" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP112" headerRowCount="1">
-  <autoFilter ref="A1:CP112"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ110" headerRowCount="1">
+  <autoFilter ref="A1:CQ110"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -753,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$112)</f>
+        <f>COUNTA('Picks'!$A$2:$A$110)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$112,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$110,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$112,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$110,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"win")+COUNTIFS('Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"win")+COUNTIFS('Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$112,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$110,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"win")/(COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"win")+COUNTIFS('Picks'!$BX$2:$BX$112,"&gt;0",'Picks'!$V$2:$V$112,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"win")/(COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"win")+COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$112)/SUM('Picks'!$BX$2:$BX$112),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$110)/SUM('Picks'!$BX$2:$BX$110),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$112)</f>
+        <f>SUM('Picks'!$BY$2:$BY$110)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$112,"&lt;&gt;",'Picks'!$AB$2:$AB$112),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$110,"&lt;&gt;",'Picks'!$AB$2:$AB$110),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$112,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$112,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$110,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$110,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$112,'Picks'!$AM$2:$AM$112,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$110,'Picks'!$AM$2:$AM$110,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A14,'Picks'!$U$2:$U$112,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A14,'Picks'!$U$2:$U$110,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A14,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A14,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A14,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A14,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$112,'Picks'!$H$2:$H$112,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$110,'Picks'!$H$2:$H$110,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$112,'Picks'!$H$2:$H$112,$A14,'Picks'!$U$2:$U$112,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$110,'Picks'!$H$2:$H$110,$A14,'Picks'!$U$2:$U$110,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A15,'Picks'!$U$2:$U$112,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A15,'Picks'!$U$2:$U$110,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A15,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A15,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A15,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A15,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$112,'Picks'!$H$2:$H$112,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$110,'Picks'!$H$2:$H$110,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$112,'Picks'!$H$2:$H$112,$A15,'Picks'!$U$2:$U$112,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$110,'Picks'!$H$2:$H$110,$A15,'Picks'!$U$2:$U$110,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A16,'Picks'!$U$2:$U$112,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A16,'Picks'!$U$2:$U$110,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A16,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A16,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$112,$A16,'Picks'!$U$2:$U$112,"settled",'Picks'!$V$2:$V$112,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$110,$A16,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$112,'Picks'!$H$2:$H$112,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$110,'Picks'!$H$2:$H$110,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$112,'Picks'!$H$2:$H$112,$A16,'Picks'!$U$2:$U$112,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$110,'Picks'!$H$2:$H$110,$A16,'Picks'!$U$2:$U$110,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP112"/>
+  <dimension ref="A1:CQ110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1859,6 +1866,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2137,6 +2145,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2415,6 +2424,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2693,6 +2703,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2971,6 +2982,7 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3249,6 +3261,7 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3527,6 +3540,7 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3805,6 +3819,7 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4083,6 +4098,7 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4361,6 +4377,7 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4639,6 +4656,7 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4917,6 +4935,7 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5195,6 +5214,7 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5473,6 +5493,7 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5751,6 +5772,7 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6029,6 +6051,7 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6307,6 +6330,7 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6585,6 +6609,7 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6863,6 +6888,7 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7141,6 +7167,7 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7419,6 +7446,7 @@
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7697,6 +7725,7 @@
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -7975,6 +8004,7 @@
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8253,6 +8283,7 @@
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8531,6 +8562,7 @@
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -8809,6 +8841,7 @@
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
       <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9087,6 +9120,7 @@
       <c r="CN28" s="24" t="n"/>
       <c r="CO28" s="24" t="n"/>
       <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9365,6 +9399,7 @@
       <c r="CN29" s="24" t="n"/>
       <c r="CO29" s="24" t="n"/>
       <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9643,6 +9678,7 @@
       <c r="CN30" s="24" t="n"/>
       <c r="CO30" s="24" t="n"/>
       <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -9921,6 +9957,7 @@
       <c r="CN31" s="24" t="n"/>
       <c r="CO31" s="24" t="n"/>
       <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10199,6 +10236,7 @@
       <c r="CN32" s="24" t="n"/>
       <c r="CO32" s="24" t="n"/>
       <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10477,6 +10515,7 @@
       <c r="CN33" s="24" t="n"/>
       <c r="CO33" s="24" t="n"/>
       <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -10755,6 +10794,7 @@
       <c r="CN34" s="24" t="n"/>
       <c r="CO34" s="24" t="n"/>
       <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11033,6 +11073,7 @@
       <c r="CN35" s="24" t="n"/>
       <c r="CO35" s="24" t="n"/>
       <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11311,6 +11352,7 @@
       <c r="CN36" s="24" t="n"/>
       <c r="CO36" s="24" t="n"/>
       <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11589,6 +11631,7 @@
       <c r="CN37" s="24" t="n"/>
       <c r="CO37" s="24" t="n"/>
       <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -11867,6 +11910,7 @@
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
       <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
@@ -12145,6 +12189,7 @@
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
       <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
@@ -12423,6 +12468,7 @@
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
       <c r="CP40" s="24" t="n"/>
+      <c r="CQ40" s="24" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
@@ -12701,6 +12747,7 @@
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
       <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
@@ -12979,6 +13026,7 @@
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
       <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
@@ -13257,6 +13305,7 @@
       <c r="CN43" s="24" t="n"/>
       <c r="CO43" s="24" t="n"/>
       <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
@@ -13535,6 +13584,7 @@
       <c r="CN44" s="24" t="n"/>
       <c r="CO44" s="24" t="n"/>
       <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
@@ -13813,6 +13863,7 @@
       <c r="CN45" s="24" t="n"/>
       <c r="CO45" s="24" t="n"/>
       <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
@@ -14091,6 +14142,7 @@
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
@@ -14369,6 +14421,7 @@
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
       <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
@@ -14647,6 +14700,7 @@
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
       <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
@@ -14925,6 +14979,7 @@
       <c r="CN49" s="24" t="n"/>
       <c r="CO49" s="24" t="n"/>
       <c r="CP49" s="24" t="n"/>
+      <c r="CQ49" s="24" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
@@ -15203,6 +15258,7 @@
       <c r="CN50" s="24" t="n"/>
       <c r="CO50" s="24" t="n"/>
       <c r="CP50" s="24" t="n"/>
+      <c r="CQ50" s="24" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
@@ -15481,6 +15537,7 @@
       <c r="CN51" s="24" t="n"/>
       <c r="CO51" s="24" t="n"/>
       <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
@@ -15759,6 +15816,7 @@
       <c r="CN52" s="24" t="n"/>
       <c r="CO52" s="24" t="n"/>
       <c r="CP52" s="24" t="n"/>
+      <c r="CQ52" s="24" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
@@ -16037,6 +16095,7 @@
       <c r="CN53" s="24" t="n"/>
       <c r="CO53" s="24" t="n"/>
       <c r="CP53" s="24" t="n"/>
+      <c r="CQ53" s="24" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
@@ -16315,6 +16374,7 @@
       <c r="CN54" s="24" t="n"/>
       <c r="CO54" s="24" t="n"/>
       <c r="CP54" s="24" t="n"/>
+      <c r="CQ54" s="24" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
@@ -16593,6 +16653,7 @@
       <c r="CN55" s="24" t="n"/>
       <c r="CO55" s="24" t="n"/>
       <c r="CP55" s="24" t="n"/>
+      <c r="CQ55" s="24" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
@@ -16871,6 +16932,7 @@
       <c r="CN56" s="24" t="n"/>
       <c r="CO56" s="24" t="n"/>
       <c r="CP56" s="24" t="n"/>
+      <c r="CQ56" s="24" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
@@ -17149,6 +17211,7 @@
       <c r="CN57" s="24" t="n"/>
       <c r="CO57" s="24" t="n"/>
       <c r="CP57" s="24" t="n"/>
+      <c r="CQ57" s="24" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
@@ -17427,6 +17490,7 @@
       <c r="CN58" s="24" t="n"/>
       <c r="CO58" s="24" t="n"/>
       <c r="CP58" s="24" t="n"/>
+      <c r="CQ58" s="24" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
@@ -17705,6 +17769,7 @@
       <c r="CN59" s="24" t="n"/>
       <c r="CO59" s="24" t="n"/>
       <c r="CP59" s="24" t="n"/>
+      <c r="CQ59" s="24" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
@@ -17983,6 +18048,7 @@
       <c r="CN60" s="24" t="n"/>
       <c r="CO60" s="24" t="n"/>
       <c r="CP60" s="24" t="n"/>
+      <c r="CQ60" s="24" t="n"/>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
@@ -18261,6 +18327,7 @@
       <c r="CN61" s="24" t="n"/>
       <c r="CO61" s="24" t="n"/>
       <c r="CP61" s="24" t="n"/>
+      <c r="CQ61" s="24" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
@@ -18539,6 +18606,7 @@
       <c r="CN62" s="24" t="n"/>
       <c r="CO62" s="24" t="n"/>
       <c r="CP62" s="24" t="n"/>
+      <c r="CQ62" s="24" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
@@ -18817,6 +18885,7 @@
       <c r="CN63" s="24" t="n"/>
       <c r="CO63" s="24" t="n"/>
       <c r="CP63" s="24" t="n"/>
+      <c r="CQ63" s="24" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
@@ -19095,6 +19164,7 @@
       <c r="CN64" s="24" t="n"/>
       <c r="CO64" s="24" t="n"/>
       <c r="CP64" s="24" t="n"/>
+      <c r="CQ64" s="24" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
@@ -19373,6 +19443,7 @@
       <c r="CN65" s="24" t="n"/>
       <c r="CO65" s="24" t="n"/>
       <c r="CP65" s="24" t="n"/>
+      <c r="CQ65" s="24" t="n"/>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
@@ -19651,6 +19722,7 @@
       <c r="CN66" s="24" t="n"/>
       <c r="CO66" s="24" t="n"/>
       <c r="CP66" s="24" t="n"/>
+      <c r="CQ66" s="24" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
@@ -19929,6 +20001,7 @@
       <c r="CN67" s="24" t="n"/>
       <c r="CO67" s="24" t="n"/>
       <c r="CP67" s="24" t="n"/>
+      <c r="CQ67" s="24" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
@@ -20217,6 +20290,7 @@
       <c r="CN68" s="24" t="n"/>
       <c r="CO68" s="24" t="n"/>
       <c r="CP68" s="24" t="n"/>
+      <c r="CQ68" s="24" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
@@ -20505,6 +20579,7 @@
       <c r="CN69" s="24" t="n"/>
       <c r="CO69" s="24" t="n"/>
       <c r="CP69" s="24" t="n"/>
+      <c r="CQ69" s="24" t="n"/>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
@@ -20793,6 +20868,7 @@
       <c r="CN70" s="24" t="n"/>
       <c r="CO70" s="24" t="n"/>
       <c r="CP70" s="24" t="n"/>
+      <c r="CQ70" s="24" t="n"/>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
@@ -21081,6 +21157,7 @@
       <c r="CN71" s="24" t="n"/>
       <c r="CO71" s="24" t="n"/>
       <c r="CP71" s="24" t="n"/>
+      <c r="CQ71" s="24" t="n"/>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
@@ -21369,6 +21446,7 @@
       <c r="CN72" s="24" t="n"/>
       <c r="CO72" s="24" t="n"/>
       <c r="CP72" s="24" t="n"/>
+      <c r="CQ72" s="24" t="n"/>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
@@ -21657,6 +21735,7 @@
       <c r="CN73" s="24" t="n"/>
       <c r="CO73" s="24" t="n"/>
       <c r="CP73" s="24" t="n"/>
+      <c r="CQ73" s="24" t="n"/>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
@@ -21945,6 +22024,7 @@
       <c r="CN74" s="24" t="n"/>
       <c r="CO74" s="24" t="n"/>
       <c r="CP74" s="24" t="n"/>
+      <c r="CQ74" s="24" t="n"/>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
@@ -22233,6 +22313,7 @@
       <c r="CN75" s="24" t="n"/>
       <c r="CO75" s="24" t="n"/>
       <c r="CP75" s="24" t="n"/>
+      <c r="CQ75" s="24" t="n"/>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
@@ -22521,6 +22602,7 @@
       <c r="CN76" s="24" t="n"/>
       <c r="CO76" s="24" t="n"/>
       <c r="CP76" s="24" t="n"/>
+      <c r="CQ76" s="24" t="n"/>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
@@ -22809,6 +22891,7 @@
       <c r="CN77" s="24" t="n"/>
       <c r="CO77" s="24" t="n"/>
       <c r="CP77" s="24" t="n"/>
+      <c r="CQ77" s="24" t="n"/>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
@@ -23097,6 +23180,7 @@
       <c r="CN78" s="24" t="n"/>
       <c r="CO78" s="24" t="n"/>
       <c r="CP78" s="24" t="n"/>
+      <c r="CQ78" s="24" t="n"/>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
@@ -23385,6 +23469,7 @@
       <c r="CN79" s="24" t="n"/>
       <c r="CO79" s="24" t="n"/>
       <c r="CP79" s="24" t="n"/>
+      <c r="CQ79" s="24" t="n"/>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
@@ -23673,6 +23758,7 @@
       <c r="CN80" s="24" t="n"/>
       <c r="CO80" s="24" t="n"/>
       <c r="CP80" s="24" t="n"/>
+      <c r="CQ80" s="24" t="n"/>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
@@ -23961,6 +24047,7 @@
       <c r="CN81" s="24" t="n"/>
       <c r="CO81" s="24" t="n"/>
       <c r="CP81" s="24" t="n"/>
+      <c r="CQ81" s="24" t="n"/>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
@@ -24249,6 +24336,7 @@
       <c r="CN82" s="24" t="n"/>
       <c r="CO82" s="24" t="n"/>
       <c r="CP82" s="24" t="n"/>
+      <c r="CQ82" s="24" t="n"/>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
@@ -24537,6 +24625,7 @@
       <c r="CN83" s="24" t="n"/>
       <c r="CO83" s="24" t="n"/>
       <c r="CP83" s="24" t="n"/>
+      <c r="CQ83" s="24" t="n"/>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
@@ -24825,6 +24914,7 @@
       <c r="CN84" s="24" t="n"/>
       <c r="CO84" s="24" t="n"/>
       <c r="CP84" s="24" t="n"/>
+      <c r="CQ84" s="24" t="n"/>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
@@ -25113,6 +25203,7 @@
       <c r="CN85" s="24" t="n"/>
       <c r="CO85" s="24" t="n"/>
       <c r="CP85" s="24" t="n"/>
+      <c r="CQ85" s="24" t="n"/>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
@@ -25401,6 +25492,7 @@
       <c r="CN86" s="24" t="n"/>
       <c r="CO86" s="24" t="n"/>
       <c r="CP86" s="24" t="n"/>
+      <c r="CQ86" s="24" t="n"/>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
@@ -25679,6 +25771,7 @@
       <c r="CN87" s="24" t="n"/>
       <c r="CO87" s="24" t="n"/>
       <c r="CP87" s="24" t="n"/>
+      <c r="CQ87" s="24" t="n"/>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
@@ -25967,6 +26060,7 @@
       <c r="CN88" s="24" t="n"/>
       <c r="CO88" s="24" t="n"/>
       <c r="CP88" s="24" t="n"/>
+      <c r="CQ88" s="24" t="n"/>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="24" t="inlineStr">
@@ -26255,6 +26349,7 @@
       <c r="CN89" s="24" t="n"/>
       <c r="CO89" s="24" t="n"/>
       <c r="CP89" s="24" t="n"/>
+      <c r="CQ89" s="24" t="n"/>
     </row>
     <row r="90" ht="36" customHeight="1">
       <c r="A90" s="24" t="inlineStr">
@@ -26543,6 +26638,7 @@
       <c r="CN90" s="24" t="n"/>
       <c r="CO90" s="24" t="n"/>
       <c r="CP90" s="24" t="n"/>
+      <c r="CQ90" s="24" t="n"/>
     </row>
     <row r="91" ht="36" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
@@ -26831,6 +26927,7 @@
       <c r="CN91" s="24" t="n"/>
       <c r="CO91" s="24" t="n"/>
       <c r="CP91" s="24" t="n"/>
+      <c r="CQ91" s="24" t="n"/>
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="24" t="inlineStr">
@@ -27119,6 +27216,7 @@
       <c r="CN92" s="24" t="n"/>
       <c r="CO92" s="24" t="n"/>
       <c r="CP92" s="24" t="n"/>
+      <c r="CQ92" s="24" t="n"/>
     </row>
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
@@ -27407,6 +27505,7 @@
       <c r="CN93" s="24" t="n"/>
       <c r="CO93" s="24" t="n"/>
       <c r="CP93" s="24" t="n"/>
+      <c r="CQ93" s="24" t="n"/>
     </row>
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
@@ -27695,6 +27794,7 @@
       <c r="CN94" s="24" t="n"/>
       <c r="CO94" s="24" t="n"/>
       <c r="CP94" s="24" t="n"/>
+      <c r="CQ94" s="24" t="n"/>
     </row>
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
@@ -27983,6 +28083,7 @@
       <c r="CN95" s="24" t="n"/>
       <c r="CO95" s="24" t="n"/>
       <c r="CP95" s="24" t="n"/>
+      <c r="CQ95" s="24" t="n"/>
     </row>
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="24" t="inlineStr">
@@ -28271,6 +28372,7 @@
       <c r="CN96" s="24" t="n"/>
       <c r="CO96" s="24" t="n"/>
       <c r="CP96" s="24" t="n"/>
+      <c r="CQ96" s="24" t="n"/>
     </row>
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="24" t="inlineStr">
@@ -28559,6 +28661,7 @@
       <c r="CN97" s="24" t="n"/>
       <c r="CO97" s="24" t="n"/>
       <c r="CP97" s="24" t="n"/>
+      <c r="CQ97" s="24" t="n"/>
     </row>
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="24" t="inlineStr">
@@ -28847,6 +28950,7 @@
       <c r="CN98" s="24" t="n"/>
       <c r="CO98" s="24" t="n"/>
       <c r="CP98" s="24" t="n"/>
+      <c r="CQ98" s="24" t="n"/>
     </row>
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="24" t="inlineStr">
@@ -29135,6 +29239,7 @@
       <c r="CN99" s="24" t="n"/>
       <c r="CO99" s="24" t="n"/>
       <c r="CP99" s="24" t="n"/>
+      <c r="CQ99" s="24" t="n"/>
     </row>
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
@@ -29398,7 +29503,8 @@
       <c r="CM100" s="24" t="n"/>
       <c r="CN100" s="24" t="n"/>
       <c r="CO100" s="24" t="n"/>
-      <c r="CP100" s="24" t="inlineStr">
+      <c r="CP100" s="24" t="n"/>
+      <c r="CQ100" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -29407,12 +29513,12 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>a7f951016379499b</t>
+          <t>bbb64c4b671648ef</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -29620,7 +29726,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:42.019193Z</t>
+          <t>2026-08-02T16:10:21.022990Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -29666,7 +29772,8 @@
       <c r="CM101" s="24" t="n"/>
       <c r="CN101" s="24" t="n"/>
       <c r="CO101" s="24" t="n"/>
-      <c r="CP101" s="24" t="inlineStr">
+      <c r="CP101" s="24" t="n"/>
+      <c r="CQ101" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -29675,12 +29782,12 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>c0cf59bfb705465c</t>
+          <t>963db413afc049d0</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -29725,13 +29832,13 @@
         </is>
       </c>
       <c r="L102" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="M102" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="N102" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="O102" s="28" t="n">
         <v>0.530496</v>
@@ -29740,10 +29847,10 @@
         <v>0.05</v>
       </c>
       <c r="Q102" s="28" t="n">
-        <v>0.020692</v>
+        <v>0.011265</v>
       </c>
       <c r="R102" s="26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S102" s="29" t="n">
         <v>1</v>
@@ -29769,7 +29876,7 @@
       <c r="AD102" s="24" t="n"/>
       <c r="AE102" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Viktorija Golubic p=0.470 vs Kimberly Birrell. Executable ask 0.5100 (aec-wta-kimbir-vikgol-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Viktorija Golubic p=0.470 vs Kimberly Birrell. Executable ask 0.5200 (aec-wta-kimbir-vikgol-2026-08-02).</t>
         </is>
       </c>
       <c r="AF102" s="31" t="inlineStr">
@@ -29888,7 +29995,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:40.733235Z</t>
+          <t>2026-08-02T16:10:19.496539Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -29898,13 +30005,13 @@
       </c>
       <c r="BJ102" s="25" t="n"/>
       <c r="BK102" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="BL102" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="BM102" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="BN102" s="28" t="n"/>
       <c r="BO102" s="28" t="n"/>
@@ -29934,7 +30041,8 @@
       <c r="CM102" s="24" t="n"/>
       <c r="CN102" s="24" t="n"/>
       <c r="CO102" s="24" t="n"/>
-      <c r="CP102" s="24" t="inlineStr">
+      <c r="CP102" s="24" t="n"/>
+      <c r="CQ102" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -29943,12 +30051,12 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>1631795568fd45da</t>
+          <t>41b4f49e70934391</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -30156,7 +30264,7 @@
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:41.086960Z</t>
+          <t>2026-08-02T16:10:19.991470Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -30202,7 +30310,8 @@
       <c r="CM103" s="24" t="n"/>
       <c r="CN103" s="24" t="n"/>
       <c r="CO103" s="24" t="n"/>
-      <c r="CP103" s="24" t="inlineStr">
+      <c r="CP103" s="24" t="n"/>
+      <c r="CQ103" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -30211,12 +30320,12 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>aa80b38afdc44bf2</t>
+          <t>109adbd9ac73439e</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -30424,7 +30533,7 @@
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:48.248249Z</t>
+          <t>2026-08-02T16:10:27.371644Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -30470,7 +30579,8 @@
       <c r="CM104" s="24" t="n"/>
       <c r="CN104" s="24" t="n"/>
       <c r="CO104" s="24" t="n"/>
-      <c r="CP104" s="24" t="inlineStr">
+      <c r="CP104" s="24" t="n"/>
+      <c r="CQ104" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -30479,12 +30589,12 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>d1fcb39b0d8f4e1a</t>
+          <t>e2d20c0f4efa47e9</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -30692,7 +30802,7 @@
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:44.674546Z</t>
+          <t>2026-08-02T16:10:25.412710Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -30738,7 +30848,8 @@
       <c r="CM105" s="24" t="n"/>
       <c r="CN105" s="24" t="n"/>
       <c r="CO105" s="24" t="n"/>
-      <c r="CP105" s="24" t="inlineStr">
+      <c r="CP105" s="24" t="n"/>
+      <c r="CQ105" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -30747,22 +30858,22 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>c061c5b94c184f35</t>
+          <t>2151fa7641cb4496</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T20:00Z</t>
         </is>
       </c>
       <c r="D106" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182284</t>
+          <t>421-2026:182273</t>
         </is>
       </c>
       <c r="E106" s="24" t="inlineStr">
@@ -30772,12 +30883,12 @@
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="G106" s="24" t="inlineStr">
         <is>
-          <t>Lucrezia Stefanini</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr">
@@ -30797,25 +30908,25 @@
         </is>
       </c>
       <c r="L106" s="26" t="n">
-        <v>-233</v>
+        <v>-186</v>
       </c>
       <c r="M106" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.537634</v>
       </c>
       <c r="N106" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.65035</v>
       </c>
       <c r="O106" s="28" t="n">
-        <v>0.736958</v>
+        <v>0.756798</v>
       </c>
       <c r="P106" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q106" s="28" t="n">
-        <v>0.037258</v>
+        <v>0.106448</v>
       </c>
       <c r="R106" s="26" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="S106" s="29" t="n">
         <v>2</v>
@@ -30841,7 +30952,7 @@
       <c r="AD106" s="24" t="n"/>
       <c r="AE106" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Camila Osorio p=0.737 vs Lucrezia Stefanini. Executable ask 0.7000 (aec-wta-lucste-camoso-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6500 (aec-wta-emejon-lantar-2026-08-02).</t>
         </is>
       </c>
       <c r="AF106" s="31" t="inlineStr">
@@ -30859,7 +30970,7 @@
       <c r="AJ106" s="31" t="n"/>
       <c r="AK106" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL106" s="26" t="n">
@@ -30867,47 +30978,47 @@
       </c>
       <c r="AM106" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN106" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO106" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP106" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AQ106" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AR106" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AS106" s="24" t="inlineStr">
         <is>
-          <t>Lucrezia Stefanini</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AT106" s="24" t="inlineStr">
         <is>
-          <t>Lucrezia Stefanini</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AU106" s="24" t="inlineStr">
         <is>
-          <t>Lucrezia Stefanini</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AV106" s="24" t="n"/>
@@ -30960,7 +31071,7 @@
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:43.798568Z</t>
+          <t>2026-08-02T16:10:31.074598Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -30970,13 +31081,13 @@
       </c>
       <c r="BJ106" s="25" t="n"/>
       <c r="BK106" s="26" t="n">
-        <v>-233</v>
+        <v>-186</v>
       </c>
       <c r="BL106" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.537634</v>
       </c>
       <c r="BM106" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.65035</v>
       </c>
       <c r="BN106" s="28" t="n"/>
       <c r="BO106" s="28" t="n"/>
@@ -31006,7 +31117,8 @@
       <c r="CM106" s="24" t="n"/>
       <c r="CN106" s="24" t="n"/>
       <c r="CO106" s="24" t="n"/>
-      <c r="CP106" s="24" t="inlineStr">
+      <c r="CP106" s="24" t="n"/>
+      <c r="CQ106" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -31015,22 +31127,22 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>68186bba3f2b4e2e</t>
+          <t>38fab0cc0ac54bb2</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:30Z</t>
+          <t>2026-08-02T21:00Z</t>
         </is>
       </c>
       <c r="D107" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182241</t>
+          <t>421-2026:182240</t>
         </is>
       </c>
       <c r="E107" s="24" t="inlineStr">
@@ -31040,12 +31152,12 @@
       </c>
       <c r="F107" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Cadence Brace</t>
         </is>
       </c>
       <c r="G107" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="H107" s="24" t="inlineStr">
@@ -31065,28 +31177,28 @@
         </is>
       </c>
       <c r="L107" s="26" t="n">
-        <v>117</v>
+        <v>-614</v>
       </c>
       <c r="M107" s="27" t="n">
-        <v>2.17</v>
+        <v>1.162866</v>
       </c>
       <c r="N107" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.859944</v>
       </c>
       <c r="O107" s="28" t="n">
-        <v>0.53051</v>
+        <v>0.7637620000000001</v>
       </c>
       <c r="P107" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q107" s="28" t="n">
-        <v>0.06968100000000001</v>
+        <v>-0.096182</v>
       </c>
       <c r="R107" s="26" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S107" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T107" s="24" t="inlineStr">
         <is>
@@ -31109,7 +31221,7 @@
       <c r="AD107" s="24" t="n"/>
       <c r="AE107" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Anna Blinkova p=0.469 vs Rebecca Sramkova. Executable ask 0.4600 (aec-wta-rebsra-annbli-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Cadence Brace p=0.236 vs McCartney Kessler. Executable ask 0.8600 (aec-wta-mcckes-cadbra-2026-08-02).</t>
         </is>
       </c>
       <c r="AF107" s="31" t="inlineStr">
@@ -31127,7 +31239,7 @@
       <c r="AJ107" s="31" t="n"/>
       <c r="AK107" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL107" s="26" t="n">
@@ -31135,47 +31247,47 @@
       </c>
       <c r="AM107" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN107" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO107" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP107" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Cadence Brace</t>
         </is>
       </c>
       <c r="AQ107" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Cadence Brace</t>
         </is>
       </c>
       <c r="AR107" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Cadence Brace</t>
         </is>
       </c>
       <c r="AS107" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AT107" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AU107" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AV107" s="24" t="n"/>
@@ -31228,7 +31340,7 @@
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:49.636292Z</t>
+          <t>2026-08-02T16:10:33.949248Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -31238,13 +31350,13 @@
       </c>
       <c r="BJ107" s="25" t="n"/>
       <c r="BK107" s="26" t="n">
-        <v>117</v>
+        <v>-614</v>
       </c>
       <c r="BL107" s="27" t="n">
-        <v>2.17</v>
+        <v>1.162866</v>
       </c>
       <c r="BM107" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.859944</v>
       </c>
       <c r="BN107" s="28" t="n"/>
       <c r="BO107" s="28" t="n"/>
@@ -31274,31 +31386,32 @@
       <c r="CM107" s="24" t="n"/>
       <c r="CN107" s="24" t="n"/>
       <c r="CO107" s="24" t="n"/>
-      <c r="CP107" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CP107" s="24" t="n"/>
+      <c r="CQ107" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>e5a2586d0b754134</t>
+          <t>dd62677d835943e7</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:00Z</t>
+          <t>2026-08-02T21:30Z</t>
         </is>
       </c>
       <c r="D108" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182273</t>
+          <t>421-2026:182283</t>
         </is>
       </c>
       <c r="E108" s="24" t="inlineStr">
@@ -31308,12 +31421,12 @@
       </c>
       <c r="F108" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Elisabetta Cocciaretto</t>
         </is>
       </c>
       <c r="G108" s="24" t="inlineStr">
         <is>
-          <t>Emerson Jones</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr">
@@ -31333,28 +31446,28 @@
         </is>
       </c>
       <c r="L108" s="26" t="n">
-        <v>-186</v>
+        <v>-144</v>
       </c>
       <c r="M108" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.694444</v>
       </c>
       <c r="N108" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.590164</v>
       </c>
       <c r="O108" s="28" t="n">
-        <v>0.756798</v>
+        <v>0.578226</v>
       </c>
       <c r="P108" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q108" s="28" t="n">
-        <v>0.106448</v>
+        <v>-0.011938</v>
       </c>
       <c r="R108" s="26" t="n">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="S108" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T108" s="24" t="inlineStr">
         <is>
@@ -31377,7 +31490,7 @@
       <c r="AD108" s="24" t="n"/>
       <c r="AE108" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6500 (aec-wta-emejon-lantar-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Elisabetta Cocciaretto p=0.578 vs Talia Gibson. Executable ask 0.5900 (aec-wta-talgib-elicoc-2026-08-02).</t>
         </is>
       </c>
       <c r="AF108" s="31" t="inlineStr">
@@ -31395,7 +31508,7 @@
       <c r="AJ108" s="31" t="n"/>
       <c r="AK108" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL108" s="26" t="n">
@@ -31403,47 +31516,47 @@
       </c>
       <c r="AM108" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN108" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO108" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP108" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Elisabetta Cocciaretto</t>
         </is>
       </c>
       <c r="AQ108" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Elisabetta Cocciaretto</t>
         </is>
       </c>
       <c r="AR108" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Elisabetta Cocciaretto</t>
         </is>
       </c>
       <c r="AS108" s="24" t="inlineStr">
         <is>
-          <t>Emerson Jones</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AT108" s="24" t="inlineStr">
         <is>
-          <t>Emerson Jones</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AU108" s="24" t="inlineStr">
         <is>
-          <t>Emerson Jones</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AV108" s="24" t="n"/>
@@ -31496,7 +31609,7 @@
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:51.741348Z</t>
+          <t>2026-08-02T16:10:34.606897Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -31506,13 +31619,13 @@
       </c>
       <c r="BJ108" s="25" t="n"/>
       <c r="BK108" s="26" t="n">
-        <v>-186</v>
+        <v>-144</v>
       </c>
       <c r="BL108" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.694444</v>
       </c>
       <c r="BM108" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.590164</v>
       </c>
       <c r="BN108" s="28" t="n"/>
       <c r="BO108" s="28" t="n"/>
@@ -31542,31 +31655,32 @@
       <c r="CM108" s="24" t="n"/>
       <c r="CN108" s="24" t="n"/>
       <c r="CO108" s="24" t="n"/>
-      <c r="CP108" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CP108" s="24" t="n"/>
+      <c r="CQ108" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>8c5a4b8f1d9449a4</t>
+          <t>8957cc55f0f84688</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T21:00Z</t>
+          <t>2026-08-02T23:00Z</t>
         </is>
       </c>
       <c r="D109" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182240</t>
+          <t>421-2026:182274</t>
         </is>
       </c>
       <c r="E109" s="24" t="inlineStr">
@@ -31576,12 +31690,12 @@
       </c>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Bianca Andreescu</t>
         </is>
       </c>
       <c r="G109" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr">
@@ -31601,28 +31715,28 @@
         </is>
       </c>
       <c r="L109" s="26" t="n">
-        <v>-614</v>
+        <v>-150</v>
       </c>
       <c r="M109" s="27" t="n">
-        <v>1.162866</v>
+        <v>1.666667</v>
       </c>
       <c r="N109" s="28" t="n">
-        <v>0.859944</v>
+        <v>0.6</v>
       </c>
       <c r="O109" s="28" t="n">
-        <v>0.7637620000000001</v>
+        <v>0.617346</v>
       </c>
       <c r="P109" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q109" s="28" t="n">
-        <v>-0.096182</v>
+        <v>0.017346</v>
       </c>
       <c r="R109" s="26" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S109" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T109" s="24" t="inlineStr">
         <is>
@@ -31645,7 +31759,7 @@
       <c r="AD109" s="24" t="n"/>
       <c r="AE109" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Cadence Brace p=0.236 vs McCartney Kessler. Executable ask 0.8600 (aec-wta-mcckes-cadbra-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Bianca Andreescu p=0.383 vs Nikola Bartunkova. Executable ask 0.6000 (aec-wta-nikbar-biaand-2026-08-02).</t>
         </is>
       </c>
       <c r="AF109" s="31" t="inlineStr">
@@ -31686,32 +31800,32 @@
       </c>
       <c r="AP109" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Bianca Andreescu</t>
         </is>
       </c>
       <c r="AQ109" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Bianca Andreescu</t>
         </is>
       </c>
       <c r="AR109" s="24" t="inlineStr">
         <is>
-          <t>Cadence Brace</t>
+          <t>Bianca Andreescu</t>
         </is>
       </c>
       <c r="AS109" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AT109" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AU109" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AV109" s="24" t="n"/>
@@ -31764,7 +31878,7 @@
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:54.553392Z</t>
+          <t>2026-08-02T16:10:34.760408Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -31774,13 +31888,13 @@
       </c>
       <c r="BJ109" s="25" t="n"/>
       <c r="BK109" s="26" t="n">
-        <v>-614</v>
+        <v>-150</v>
       </c>
       <c r="BL109" s="27" t="n">
-        <v>1.162866</v>
+        <v>1.666667</v>
       </c>
       <c r="BM109" s="28" t="n">
-        <v>0.859944</v>
+        <v>0.6</v>
       </c>
       <c r="BN109" s="28" t="n"/>
       <c r="BO109" s="28" t="n"/>
@@ -31810,31 +31924,32 @@
       <c r="CM109" s="24" t="n"/>
       <c r="CN109" s="24" t="n"/>
       <c r="CO109" s="24" t="n"/>
-      <c r="CP109" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CP109" s="24" t="n"/>
+      <c r="CQ109" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>6240c2227d994ec7</t>
+          <t>869516178c3f430a</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T21:30Z</t>
+          <t>2026-08-03T00:30Z</t>
         </is>
       </c>
       <c r="D110" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182283</t>
+          <t>421-2026:182281</t>
         </is>
       </c>
       <c r="E110" s="24" t="inlineStr">
@@ -31844,12 +31959,12 @@
       </c>
       <c r="F110" s="24" t="inlineStr">
         <is>
-          <t>Elisabetta Cocciaretto</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="G110" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Yulia Putintseva</t>
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr">
@@ -31859,7 +31974,7 @@
       </c>
       <c r="I110" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J110" s="25" t="n"/>
@@ -31869,28 +31984,28 @@
         </is>
       </c>
       <c r="L110" s="26" t="n">
-        <v>-144</v>
+        <v>-186</v>
       </c>
       <c r="M110" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.537634</v>
       </c>
       <c r="N110" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.65035</v>
       </c>
       <c r="O110" s="28" t="n">
-        <v>0.578226</v>
+        <v>0.630736</v>
       </c>
       <c r="P110" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q110" s="28" t="n">
-        <v>-0.011938</v>
+        <v>-0.019614</v>
       </c>
       <c r="R110" s="26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S110" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T110" s="24" t="inlineStr">
         <is>
@@ -31913,7 +32028,7 @@
       <c r="AD110" s="24" t="n"/>
       <c r="AE110" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Elisabetta Cocciaretto p=0.578 vs Talia Gibson. Executable ask 0.5900 (aec-wta-talgib-elicoc-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Zhang Shuai p=0.369 vs Yulia Putintseva. Executable ask 0.6500 (aec-wta-yulput-shuzha-2026-08-02).</t>
         </is>
       </c>
       <c r="AF110" s="31" t="inlineStr">
@@ -31954,32 +32069,32 @@
       </c>
       <c r="AP110" s="24" t="inlineStr">
         <is>
-          <t>Elisabetta Cocciaretto</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AQ110" s="24" t="inlineStr">
         <is>
-          <t>Elisabetta Cocciaretto</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AR110" s="24" t="inlineStr">
         <is>
-          <t>Elisabetta Cocciaretto</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AS110" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Yulia Putintseva</t>
         </is>
       </c>
       <c r="AT110" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Yulia Putintseva</t>
         </is>
       </c>
       <c r="AU110" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Yulia Putintseva</t>
         </is>
       </c>
       <c r="AV110" s="24" t="n"/>
@@ -32032,7 +32147,7 @@
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:55.125883Z</t>
+          <t>2026-08-02T16:10:35.088581Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -32042,13 +32157,13 @@
       </c>
       <c r="BJ110" s="25" t="n"/>
       <c r="BK110" s="26" t="n">
-        <v>-144</v>
+        <v>-186</v>
       </c>
       <c r="BL110" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.537634</v>
       </c>
       <c r="BM110" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.65035</v>
       </c>
       <c r="BN110" s="28" t="n"/>
       <c r="BO110" s="28" t="n"/>
@@ -32078,543 +32193,8 @@
       <c r="CM110" s="24" t="n"/>
       <c r="CN110" s="24" t="n"/>
       <c r="CO110" s="24" t="n"/>
-      <c r="CP110" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="36" customHeight="1">
-      <c r="A111" s="24" t="inlineStr">
-        <is>
-          <t>d8eff19de3f843cc</t>
-        </is>
-      </c>
-      <c r="B111" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
-        </is>
-      </c>
-      <c r="C111" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T23:00Z</t>
-        </is>
-      </c>
-      <c r="D111" s="24" t="inlineStr">
-        <is>
-          <t>421-2026:182274</t>
-        </is>
-      </c>
-      <c r="E111" s="24" t="inlineStr">
-        <is>
-          <t>TENNIS</t>
-        </is>
-      </c>
-      <c r="F111" s="24" t="inlineStr">
-        <is>
-          <t>Bianca Andreescu</t>
-        </is>
-      </c>
-      <c r="G111" s="24" t="inlineStr">
-        <is>
-          <t>Nikola Bartunkova</t>
-        </is>
-      </c>
-      <c r="H111" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I111" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J111" s="25" t="n"/>
-      <c r="K111" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L111" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M111" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="N111" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O111" s="28" t="n">
-        <v>0.617346</v>
-      </c>
-      <c r="P111" s="28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q111" s="28" t="n">
-        <v>0.017346</v>
-      </c>
-      <c r="R111" s="26" t="n">
-        <v>29</v>
-      </c>
-      <c r="S111" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T111" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="U111" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V111" s="24" t="n"/>
-      <c r="W111" s="26" t="n"/>
-      <c r="X111" s="26" t="n"/>
-      <c r="Y111" s="25" t="n"/>
-      <c r="Z111" s="26" t="n"/>
-      <c r="AA111" s="28" t="n"/>
-      <c r="AB111" s="28" t="n"/>
-      <c r="AC111" s="30" t="n"/>
-      <c r="AD111" s="24" t="n"/>
-      <c r="AE111" s="31" t="inlineStr">
-        <is>
-          <t>Surface-blended Elo on Hard: Bianca Andreescu p=0.383 vs Nikola Bartunkova. Executable ask 0.6000 (aec-wta-nikbar-biaand-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF111" s="31" t="inlineStr">
-        <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
-        </is>
-      </c>
-      <c r="AG111" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH111" s="24" t="n"/>
-      <c r="AI111" s="31" t="n"/>
-      <c r="AJ111" s="31" t="n"/>
-      <c r="AK111" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL111" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM111" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN111" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO111" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP111" s="24" t="inlineStr">
-        <is>
-          <t>Bianca Andreescu</t>
-        </is>
-      </c>
-      <c r="AQ111" s="24" t="inlineStr">
-        <is>
-          <t>Bianca Andreescu</t>
-        </is>
-      </c>
-      <c r="AR111" s="24" t="inlineStr">
-        <is>
-          <t>Bianca Andreescu</t>
-        </is>
-      </c>
-      <c r="AS111" s="24" t="inlineStr">
-        <is>
-          <t>Nikola Bartunkova</t>
-        </is>
-      </c>
-      <c r="AT111" s="24" t="inlineStr">
-        <is>
-          <t>Nikola Bartunkova</t>
-        </is>
-      </c>
-      <c r="AU111" s="24" t="inlineStr">
-        <is>
-          <t>Nikola Bartunkova</t>
-        </is>
-      </c>
-      <c r="AV111" s="24" t="n"/>
-      <c r="AW111" s="24" t="n"/>
-      <c r="AX111" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY111" s="24" t="n"/>
-      <c r="AZ111" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA111" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BB111" s="24" t="inlineStr">
-        <is>
-          <t>surface_blended_elo</t>
-        </is>
-      </c>
-      <c r="BC111" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD111" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BE111" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BF111" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG111" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BH111" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T15:46:55.388422Z</t>
-        </is>
-      </c>
-      <c r="BI111" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ111" s="25" t="n"/>
-      <c r="BK111" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BL111" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BM111" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN111" s="28" t="n"/>
-      <c r="BO111" s="28" t="n"/>
-      <c r="BP111" s="25" t="n"/>
-      <c r="BQ111" s="27" t="n"/>
-      <c r="BR111" s="28" t="n"/>
-      <c r="BS111" s="28" t="n"/>
-      <c r="BT111" s="28" t="n"/>
-      <c r="BU111" s="25" t="n"/>
-      <c r="BV111" s="29" t="n"/>
-      <c r="BW111" s="24" t="n"/>
-      <c r="BX111" s="30" t="n"/>
-      <c r="BY111" s="27" t="n"/>
-      <c r="BZ111" s="24" t="n"/>
-      <c r="CA111" s="31" t="n"/>
-      <c r="CB111" s="24" t="n"/>
-      <c r="CC111" s="24" t="n"/>
-      <c r="CD111" s="24" t="n"/>
-      <c r="CE111" s="24" t="n"/>
-      <c r="CF111" s="24" t="n"/>
-      <c r="CG111" s="24" t="n"/>
-      <c r="CH111" s="24" t="n"/>
-      <c r="CI111" s="24" t="n"/>
-      <c r="CJ111" s="24" t="n"/>
-      <c r="CK111" s="24" t="n"/>
-      <c r="CL111" s="24" t="n"/>
-      <c r="CM111" s="24" t="n"/>
-      <c r="CN111" s="24" t="n"/>
-      <c r="CO111" s="24" t="n"/>
-      <c r="CP111" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="36" customHeight="1">
-      <c r="A112" s="24" t="inlineStr">
-        <is>
-          <t>fc4cd1d6df72434b</t>
-        </is>
-      </c>
-      <c r="B112" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
-        </is>
-      </c>
-      <c r="C112" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T00:30Z</t>
-        </is>
-      </c>
-      <c r="D112" s="24" t="inlineStr">
-        <is>
-          <t>421-2026:182281</t>
-        </is>
-      </c>
-      <c r="E112" s="24" t="inlineStr">
-        <is>
-          <t>TENNIS</t>
-        </is>
-      </c>
-      <c r="F112" s="24" t="inlineStr">
-        <is>
-          <t>Zhang Shuai</t>
-        </is>
-      </c>
-      <c r="G112" s="24" t="inlineStr">
-        <is>
-          <t>Yulia Putintseva</t>
-        </is>
-      </c>
-      <c r="H112" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I112" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J112" s="25" t="n"/>
-      <c r="K112" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L112" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="M112" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="N112" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="O112" s="28" t="n">
-        <v>0.630736</v>
-      </c>
-      <c r="P112" s="28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q112" s="28" t="n">
-        <v>-0.019614</v>
-      </c>
-      <c r="R112" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="S112" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T112" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="U112" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V112" s="24" t="n"/>
-      <c r="W112" s="26" t="n"/>
-      <c r="X112" s="26" t="n"/>
-      <c r="Y112" s="25" t="n"/>
-      <c r="Z112" s="26" t="n"/>
-      <c r="AA112" s="28" t="n"/>
-      <c r="AB112" s="28" t="n"/>
-      <c r="AC112" s="30" t="n"/>
-      <c r="AD112" s="24" t="n"/>
-      <c r="AE112" s="31" t="inlineStr">
-        <is>
-          <t>Surface-blended Elo on Hard: Zhang Shuai p=0.369 vs Yulia Putintseva. Executable ask 0.6500 (aec-wta-yulput-shuzha-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF112" s="31" t="inlineStr">
-        <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
-        </is>
-      </c>
-      <c r="AG112" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH112" s="24" t="n"/>
-      <c r="AI112" s="31" t="n"/>
-      <c r="AJ112" s="31" t="n"/>
-      <c r="AK112" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL112" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM112" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN112" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO112" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP112" s="24" t="inlineStr">
-        <is>
-          <t>Zhang Shuai</t>
-        </is>
-      </c>
-      <c r="AQ112" s="24" t="inlineStr">
-        <is>
-          <t>Zhang Shuai</t>
-        </is>
-      </c>
-      <c r="AR112" s="24" t="inlineStr">
-        <is>
-          <t>Zhang Shuai</t>
-        </is>
-      </c>
-      <c r="AS112" s="24" t="inlineStr">
-        <is>
-          <t>Yulia Putintseva</t>
-        </is>
-      </c>
-      <c r="AT112" s="24" t="inlineStr">
-        <is>
-          <t>Yulia Putintseva</t>
-        </is>
-      </c>
-      <c r="AU112" s="24" t="inlineStr">
-        <is>
-          <t>Yulia Putintseva</t>
-        </is>
-      </c>
-      <c r="AV112" s="24" t="n"/>
-      <c r="AW112" s="24" t="n"/>
-      <c r="AX112" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY112" s="24" t="n"/>
-      <c r="AZ112" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA112" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BB112" s="24" t="inlineStr">
-        <is>
-          <t>surface_blended_elo</t>
-        </is>
-      </c>
-      <c r="BC112" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD112" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BE112" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BF112" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG112" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BH112" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T15:46:55.697720Z</t>
-        </is>
-      </c>
-      <c r="BI112" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ112" s="25" t="n"/>
-      <c r="BK112" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="BL112" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="BM112" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="BN112" s="28" t="n"/>
-      <c r="BO112" s="28" t="n"/>
-      <c r="BP112" s="25" t="n"/>
-      <c r="BQ112" s="27" t="n"/>
-      <c r="BR112" s="28" t="n"/>
-      <c r="BS112" s="28" t="n"/>
-      <c r="BT112" s="28" t="n"/>
-      <c r="BU112" s="25" t="n"/>
-      <c r="BV112" s="29" t="n"/>
-      <c r="BW112" s="24" t="n"/>
-      <c r="BX112" s="30" t="n"/>
-      <c r="BY112" s="27" t="n"/>
-      <c r="BZ112" s="24" t="n"/>
-      <c r="CA112" s="31" t="n"/>
-      <c r="CB112" s="24" t="n"/>
-      <c r="CC112" s="24" t="n"/>
-      <c r="CD112" s="24" t="n"/>
-      <c r="CE112" s="24" t="n"/>
-      <c r="CF112" s="24" t="n"/>
-      <c r="CG112" s="24" t="n"/>
-      <c r="CH112" s="24" t="n"/>
-      <c r="CI112" s="24" t="n"/>
-      <c r="CJ112" s="24" t="n"/>
-      <c r="CK112" s="24" t="n"/>
-      <c r="CL112" s="24" t="n"/>
-      <c r="CM112" s="24" t="n"/>
-      <c r="CN112" s="24" t="n"/>
-      <c r="CO112" s="24" t="n"/>
-      <c r="CP112" s="24" t="inlineStr">
+      <c r="CP110" s="24" t="n"/>
+      <c r="CQ110" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/research/tennis.xlsx
+++ b/data/research/tennis.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ110" headerRowCount="1">
-  <autoFilter ref="A1:CQ110"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ117" headerRowCount="1">
+  <autoFilter ref="A1:CQ117"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$110)</f>
+        <f>COUNTA('Picks'!$A$2:$A$117)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$110,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$117,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$110,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"win")+COUNTIFS('Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")+COUNTIFS('Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$110,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$117,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"win")/(COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"win")+COUNTIFS('Picks'!$BX$2:$BX$110,"&gt;0",'Picks'!$V$2:$V$110,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")/(COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")+COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$110)/SUM('Picks'!$BX$2:$BX$110),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$117)/SUM('Picks'!$BX$2:$BX$117),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$110)</f>
+        <f>SUM('Picks'!$BY$2:$BY$117)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$110,"&lt;&gt;",'Picks'!$AB$2:$AB$110),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$117,"&lt;&gt;",'Picks'!$AB$2:$AB$117),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$110,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$110,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$117,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$110,'Picks'!$AM$2:$AM$110,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$117,'Picks'!$AM$2:$AM$117,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A14,'Picks'!$U$2:$U$110,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A14,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A14,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$110,'Picks'!$H$2:$H$110,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$110,'Picks'!$H$2:$H$110,$A14,'Picks'!$U$2:$U$110,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A15,'Picks'!$U$2:$U$110,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A15,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A15,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$110,'Picks'!$H$2:$H$110,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$110,'Picks'!$H$2:$H$110,$A15,'Picks'!$U$2:$U$110,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A16,'Picks'!$U$2:$U$110,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A16,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$110,$A16,'Picks'!$U$2:$U$110,"settled",'Picks'!$V$2:$V$110,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$110,'Picks'!$H$2:$H$110,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$110,'Picks'!$H$2:$H$110,$A16,'Picks'!$U$2:$U$110,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ110"/>
+  <dimension ref="A1:CQ117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29513,7 +29513,7 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>bbb64c4b671648ef</t>
+          <t>963db413afc049d0</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
@@ -29523,12 +29523,12 @@
       </c>
       <c r="C101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:30Z</t>
+          <t>2026-08-02T16:30Z</t>
         </is>
       </c>
       <c r="D101" s="24" t="inlineStr">
         <is>
-          <t>1067-2026:179469</t>
+          <t>421-2026:182259</t>
         </is>
       </c>
       <c r="E101" s="24" t="inlineStr">
@@ -29538,12 +29538,12 @@
       </c>
       <c r="F101" s="24" t="inlineStr">
         <is>
-          <t>Darja Vidmanova</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="G101" s="24" t="inlineStr">
         <is>
-          <t>Kristina Liutova</t>
+          <t>Kimberly Birrell</t>
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr">
@@ -29553,7 +29553,7 @@
       </c>
       <c r="I101" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J101" s="25" t="n"/>
@@ -29563,28 +29563,28 @@
         </is>
       </c>
       <c r="L101" s="26" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="M101" s="27" t="n">
-        <v>2.04</v>
+        <v>1.925926</v>
       </c>
       <c r="N101" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.519231</v>
       </c>
       <c r="O101" s="28" t="n">
-        <v>0.639939</v>
+        <v>0.530496</v>
       </c>
       <c r="P101" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q101" s="28" t="n">
-        <v>0.149743</v>
+        <v>0.011265</v>
       </c>
       <c r="R101" s="26" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="S101" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T101" s="24" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
       <c r="AD101" s="24" t="n"/>
       <c r="AE101" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.4900 (aec-wta-kriliu-darvid-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Viktorija Golubic p=0.470 vs Kimberly Birrell. Executable ask 0.5200 (aec-wta-kimbir-vikgol-2026-08-02).</t>
         </is>
       </c>
       <c r="AF101" s="31" t="inlineStr">
@@ -29625,7 +29625,7 @@
       <c r="AJ101" s="31" t="n"/>
       <c r="AK101" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL101" s="26" t="n">
@@ -29633,47 +29633,47 @@
       </c>
       <c r="AM101" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN101" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO101" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP101" s="24" t="inlineStr">
         <is>
-          <t>Darja Vidmanova</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="AQ101" s="24" t="inlineStr">
         <is>
-          <t>Darja Vidmanova</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="AR101" s="24" t="inlineStr">
         <is>
-          <t>Darja Vidmanova</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="AS101" s="24" t="inlineStr">
         <is>
-          <t>Kristina Liutova</t>
+          <t>Kimberly Birrell</t>
         </is>
       </c>
       <c r="AT101" s="24" t="inlineStr">
         <is>
-          <t>Kristina Liutova</t>
+          <t>Kimberly Birrell</t>
         </is>
       </c>
       <c r="AU101" s="24" t="inlineStr">
         <is>
-          <t>Kristina Liutova</t>
+          <t>Kimberly Birrell</t>
         </is>
       </c>
       <c r="AV101" s="24" t="n"/>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:21.022990Z</t>
+          <t>2026-08-02T16:10:19.496539Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -29736,13 +29736,13 @@
       </c>
       <c r="BJ101" s="25" t="n"/>
       <c r="BK101" s="26" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="BL101" s="27" t="n">
-        <v>2.04</v>
+        <v>1.925926</v>
       </c>
       <c r="BM101" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.519231</v>
       </c>
       <c r="BN101" s="28" t="n"/>
       <c r="BO101" s="28" t="n"/>
@@ -29782,7 +29782,7 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>963db413afc049d0</t>
+          <t>41b4f49e70934391</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
@@ -29797,7 +29797,7 @@
       </c>
       <c r="D102" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182259</t>
+          <t>421-2026:182280</t>
         </is>
       </c>
       <c r="E102" s="24" t="inlineStr">
@@ -29807,12 +29807,12 @@
       </c>
       <c r="F102" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="G102" s="24" t="inlineStr">
         <is>
-          <t>Kimberly Birrell</t>
+          <t>Wang Xiyu</t>
         </is>
       </c>
       <c r="H102" s="24" t="inlineStr">
@@ -29822,7 +29822,7 @@
       </c>
       <c r="I102" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J102" s="25" t="n"/>
@@ -29832,28 +29832,28 @@
         </is>
       </c>
       <c r="L102" s="26" t="n">
-        <v>-108</v>
+        <v>-144</v>
       </c>
       <c r="M102" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.694444</v>
       </c>
       <c r="N102" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.590164</v>
       </c>
       <c r="O102" s="28" t="n">
-        <v>0.530496</v>
+        <v>0.597848</v>
       </c>
       <c r="P102" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q102" s="28" t="n">
-        <v>0.011265</v>
+        <v>0.007684</v>
       </c>
       <c r="R102" s="26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="S102" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T102" s="24" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
       <c r="AD102" s="24" t="n"/>
       <c r="AE102" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Viktorija Golubic p=0.470 vs Kimberly Birrell. Executable ask 0.5200 (aec-wta-kimbir-vikgol-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.5900 (aec-wta-xiywan-sarbej-2026-08-02).</t>
         </is>
       </c>
       <c r="AF102" s="31" t="inlineStr">
@@ -29917,32 +29917,32 @@
       </c>
       <c r="AP102" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AQ102" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AR102" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AS102" s="24" t="inlineStr">
         <is>
-          <t>Kimberly Birrell</t>
+          <t>Wang Xiyu</t>
         </is>
       </c>
       <c r="AT102" s="24" t="inlineStr">
         <is>
-          <t>Kimberly Birrell</t>
+          <t>Wang Xiyu</t>
         </is>
       </c>
       <c r="AU102" s="24" t="inlineStr">
         <is>
-          <t>Kimberly Birrell</t>
+          <t>Wang Xiyu</t>
         </is>
       </c>
       <c r="AV102" s="24" t="n"/>
@@ -29995,7 +29995,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:19.496539Z</t>
+          <t>2026-08-02T16:10:19.991470Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -30005,13 +30005,13 @@
       </c>
       <c r="BJ102" s="25" t="n"/>
       <c r="BK102" s="26" t="n">
-        <v>-108</v>
+        <v>-144</v>
       </c>
       <c r="BL102" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.694444</v>
       </c>
       <c r="BM102" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.590164</v>
       </c>
       <c r="BN102" s="28" t="n"/>
       <c r="BO102" s="28" t="n"/>
@@ -30051,22 +30051,22 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>41b4f49e70934391</t>
+          <t>d8110040e8f94cd5</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:30Z</t>
+          <t>2026-08-02T17:30Z</t>
         </is>
       </c>
       <c r="D103" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182280</t>
+          <t>1067-2026:179469</t>
         </is>
       </c>
       <c r="E103" s="24" t="inlineStr">
@@ -30076,12 +30076,12 @@
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Darja Vidmanova</t>
         </is>
       </c>
       <c r="G103" s="24" t="inlineStr">
         <is>
-          <t>Wang Xiyu</t>
+          <t>Kristina Liutova</t>
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr">
@@ -30101,28 +30101,28 @@
         </is>
       </c>
       <c r="L103" s="26" t="n">
-        <v>-144</v>
+        <v>104</v>
       </c>
       <c r="M103" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.04</v>
       </c>
       <c r="N103" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.490196</v>
       </c>
       <c r="O103" s="28" t="n">
-        <v>0.597848</v>
+        <v>0.639939</v>
       </c>
       <c r="P103" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q103" s="28" t="n">
-        <v>0.007684</v>
+        <v>0.149743</v>
       </c>
       <c r="R103" s="26" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="S103" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T103" s="24" t="inlineStr">
         <is>
@@ -30145,12 +30145,12 @@
       <c r="AD103" s="24" t="n"/>
       <c r="AE103" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Sara Bejlek p=0.598 vs Wang Xiyu. Executable ask 0.5900 (aec-wta-xiywan-sarbej-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.4900 (aec-wta-kriliu-darvid-2026-08-02).</t>
         </is>
       </c>
       <c r="AF103" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG103" s="24" t="inlineStr">
@@ -30163,7 +30163,7 @@
       <c r="AJ103" s="31" t="n"/>
       <c r="AK103" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL103" s="26" t="n">
@@ -30171,47 +30171,47 @@
       </c>
       <c r="AM103" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN103" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO103" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP103" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Darja Vidmanova</t>
         </is>
       </c>
       <c r="AQ103" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Darja Vidmanova</t>
         </is>
       </c>
       <c r="AR103" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Darja Vidmanova</t>
         </is>
       </c>
       <c r="AS103" s="24" t="inlineStr">
         <is>
-          <t>Wang Xiyu</t>
+          <t>Kristina Liutova</t>
         </is>
       </c>
       <c r="AT103" s="24" t="inlineStr">
         <is>
-          <t>Wang Xiyu</t>
+          <t>Kristina Liutova</t>
         </is>
       </c>
       <c r="AU103" s="24" t="inlineStr">
         <is>
-          <t>Wang Xiyu</t>
+          <t>Kristina Liutova</t>
         </is>
       </c>
       <c r="AV103" s="24" t="n"/>
@@ -30224,12 +30224,12 @@
       <c r="AY103" s="24" t="n"/>
       <c r="AZ103" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA103" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB103" s="24" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="BD103" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE103" s="24" t="inlineStr">
@@ -30259,12 +30259,12 @@
       </c>
       <c r="BG103" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:19.991470Z</t>
+          <t>2026-08-02T16:47:46.960029Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -30274,13 +30274,13 @@
       </c>
       <c r="BJ103" s="25" t="n"/>
       <c r="BK103" s="26" t="n">
-        <v>-144</v>
+        <v>104</v>
       </c>
       <c r="BL103" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.04</v>
       </c>
       <c r="BM103" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.490196</v>
       </c>
       <c r="BN103" s="28" t="n"/>
       <c r="BO103" s="28" t="n"/>
@@ -30320,12 +30320,12 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>109adbd9ac73439e</t>
+          <t>f422054a8d494ec4</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -30419,7 +30419,7 @@
       </c>
       <c r="AF104" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG104" s="24" t="inlineStr">
@@ -30493,12 +30493,12 @@
       <c r="AY104" s="24" t="n"/>
       <c r="AZ104" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA104" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB104" s="24" t="inlineStr">
@@ -30513,7 +30513,7 @@
       </c>
       <c r="BD104" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE104" s="24" t="inlineStr">
@@ -30528,12 +30528,12 @@
       </c>
       <c r="BG104" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:27.371644Z</t>
+          <t>2026-08-02T16:47:51.852853Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -30589,12 +30589,12 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>e2d20c0f4efa47e9</t>
+          <t>a9d164aa04424e7c</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -30688,7 +30688,7 @@
       </c>
       <c r="AF105" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG105" s="24" t="inlineStr">
@@ -30762,12 +30762,12 @@
       <c r="AY105" s="24" t="n"/>
       <c r="AZ105" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA105" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB105" s="24" t="inlineStr">
@@ -30782,7 +30782,7 @@
       </c>
       <c r="BD105" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE105" s="24" t="inlineStr">
@@ -30797,12 +30797,12 @@
       </c>
       <c r="BG105" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:25.412710Z</t>
+          <t>2026-08-02T16:47:48.148287Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -30858,12 +30858,12 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>2151fa7641cb4496</t>
+          <t>ee2dbd8025fa4b57</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
@@ -30957,7 +30957,7 @@
       </c>
       <c r="AF106" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG106" s="24" t="inlineStr">
@@ -31031,12 +31031,12 @@
       <c r="AY106" s="24" t="n"/>
       <c r="AZ106" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA106" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB106" s="24" t="inlineStr">
@@ -31051,7 +31051,7 @@
       </c>
       <c r="BD106" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE106" s="24" t="inlineStr">
@@ -31066,12 +31066,12 @@
       </c>
       <c r="BG106" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:31.074598Z</t>
+          <t>2026-08-02T16:47:57.265599Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -31127,12 +31127,12 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>38fab0cc0ac54bb2</t>
+          <t>b40625d0c8854689</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
@@ -31226,7 +31226,7 @@
       </c>
       <c r="AF107" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG107" s="24" t="inlineStr">
@@ -31300,12 +31300,12 @@
       <c r="AY107" s="24" t="n"/>
       <c r="AZ107" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA107" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB107" s="24" t="inlineStr">
@@ -31320,7 +31320,7 @@
       </c>
       <c r="BD107" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE107" s="24" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="BG107" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:33.949248Z</t>
+          <t>2026-08-02T16:47:57.823493Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -31396,12 +31396,12 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>dd62677d835943e7</t>
+          <t>59a7e978717c4bfa</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
@@ -31495,7 +31495,7 @@
       </c>
       <c r="AF108" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG108" s="24" t="inlineStr">
@@ -31569,12 +31569,12 @@
       <c r="AY108" s="24" t="n"/>
       <c r="AZ108" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA108" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB108" s="24" t="inlineStr">
@@ -31589,7 +31589,7 @@
       </c>
       <c r="BD108" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE108" s="24" t="inlineStr">
@@ -31604,12 +31604,12 @@
       </c>
       <c r="BG108" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:34.606897Z</t>
+          <t>2026-08-02T16:48:00.384778Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -31665,12 +31665,12 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>8957cc55f0f84688</t>
+          <t>b824500fc56b4ba1</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
@@ -31764,7 +31764,7 @@
       </c>
       <c r="AF109" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG109" s="24" t="inlineStr">
@@ -31838,12 +31838,12 @@
       <c r="AY109" s="24" t="n"/>
       <c r="AZ109" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA109" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB109" s="24" t="inlineStr">
@@ -31858,7 +31858,7 @@
       </c>
       <c r="BD109" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE109" s="24" t="inlineStr">
@@ -31873,12 +31873,12 @@
       </c>
       <c r="BG109" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:34.760408Z</t>
+          <t>2026-08-02T16:48:00.569912Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -31934,12 +31934,12 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>869516178c3f430a</t>
+          <t>d1e9bf80e02a44ee</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
@@ -31984,13 +31984,13 @@
         </is>
       </c>
       <c r="L110" s="26" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="M110" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.515464</v>
       </c>
       <c r="N110" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.659864</v>
       </c>
       <c r="O110" s="28" t="n">
         <v>0.630736</v>
@@ -31999,10 +31999,10 @@
         <v>0.05</v>
       </c>
       <c r="Q110" s="28" t="n">
-        <v>-0.019614</v>
+        <v>-0.029128</v>
       </c>
       <c r="R110" s="26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S110" s="29" t="n">
         <v>1.5</v>
@@ -32028,12 +32028,12 @@
       <c r="AD110" s="24" t="n"/>
       <c r="AE110" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Zhang Shuai p=0.369 vs Yulia Putintseva. Executable ask 0.6500 (aec-wta-yulput-shuzha-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Zhang Shuai p=0.369 vs Yulia Putintseva. Executable ask 0.6600 (aec-wta-yulput-shuzha-2026-08-02).</t>
         </is>
       </c>
       <c r="AF110" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG110" s="24" t="inlineStr">
@@ -32107,12 +32107,12 @@
       <c r="AY110" s="24" t="n"/>
       <c r="AZ110" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA110" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB110" s="24" t="inlineStr">
@@ -32127,7 +32127,7 @@
       </c>
       <c r="BD110" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE110" s="24" t="inlineStr">
@@ -32142,12 +32142,12 @@
       </c>
       <c r="BG110" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:35.088581Z</t>
+          <t>2026-08-02T16:48:00.878431Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -32157,13 +32157,13 @@
       </c>
       <c r="BJ110" s="25" t="n"/>
       <c r="BK110" s="26" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="BL110" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.515464</v>
       </c>
       <c r="BM110" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.659864</v>
       </c>
       <c r="BN110" s="28" t="n"/>
       <c r="BO110" s="28" t="n"/>
@@ -32200,6 +32200,1889 @@
         </is>
       </c>
     </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="A111" s="24" t="inlineStr">
+        <is>
+          <t>9fcddb0134fb40d4</t>
+        </is>
+      </c>
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C111" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr">
+        <is>
+          <t>888-2026:178979</t>
+        </is>
+      </c>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="G111" s="24" t="inlineStr">
+        <is>
+          <t>Taylor Fritz</t>
+        </is>
+      </c>
+      <c r="H111" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I111" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J111" s="25" t="n"/>
+      <c r="K111" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L111" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M111" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N111" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O111" s="28" t="n">
+        <v>0.592585</v>
+      </c>
+      <c r="P111" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q111" s="28" t="n">
+        <v>0.002421</v>
+      </c>
+      <c r="R111" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S111" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T111" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U111" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V111" s="24" t="n"/>
+      <c r="W111" s="26" t="n"/>
+      <c r="X111" s="26" t="n"/>
+      <c r="Y111" s="25" t="n"/>
+      <c r="Z111" s="26" t="n"/>
+      <c r="AA111" s="28" t="n"/>
+      <c r="AB111" s="28" t="n"/>
+      <c r="AC111" s="30" t="n"/>
+      <c r="AD111" s="24" t="n"/>
+      <c r="AE111" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Rafael Jodar p=0.407 vs Taylor Fritz. Executable ask 0.5900 (aec-atp-tayfri-rafjod-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF111" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG111" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH111" s="24" t="n"/>
+      <c r="AI111" s="31" t="n"/>
+      <c r="AJ111" s="31" t="n"/>
+      <c r="AK111" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL111" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM111" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN111" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO111" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP111" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AQ111" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AR111" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AS111" s="24" t="inlineStr">
+        <is>
+          <t>Taylor Fritz</t>
+        </is>
+      </c>
+      <c r="AT111" s="24" t="inlineStr">
+        <is>
+          <t>Taylor Fritz</t>
+        </is>
+      </c>
+      <c r="AU111" s="24" t="inlineStr">
+        <is>
+          <t>Taylor Fritz</t>
+        </is>
+      </c>
+      <c r="AV111" s="24" t="n"/>
+      <c r="AW111" s="24" t="n"/>
+      <c r="AX111" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY111" s="24" t="n"/>
+      <c r="AZ111" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA111" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB111" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC111" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD111" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE111" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF111" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG111" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH111" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:13.867147Z</t>
+        </is>
+      </c>
+      <c r="BI111" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ111" s="25" t="n"/>
+      <c r="BK111" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL111" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM111" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN111" s="28" t="n"/>
+      <c r="BO111" s="28" t="n"/>
+      <c r="BP111" s="25" t="n"/>
+      <c r="BQ111" s="27" t="n"/>
+      <c r="BR111" s="28" t="n"/>
+      <c r="BS111" s="28" t="n"/>
+      <c r="BT111" s="28" t="n"/>
+      <c r="BU111" s="25" t="n"/>
+      <c r="BV111" s="29" t="n"/>
+      <c r="BW111" s="24" t="n"/>
+      <c r="BX111" s="30" t="n"/>
+      <c r="BY111" s="27" t="n"/>
+      <c r="BZ111" s="24" t="n"/>
+      <c r="CA111" s="31" t="n"/>
+      <c r="CB111" s="24" t="n"/>
+      <c r="CC111" s="24" t="n"/>
+      <c r="CD111" s="24" t="n"/>
+      <c r="CE111" s="24" t="n"/>
+      <c r="CF111" s="24" t="n"/>
+      <c r="CG111" s="24" t="n"/>
+      <c r="CH111" s="24" t="n"/>
+      <c r="CI111" s="24" t="n"/>
+      <c r="CJ111" s="24" t="n"/>
+      <c r="CK111" s="24" t="n"/>
+      <c r="CL111" s="24" t="n"/>
+      <c r="CM111" s="24" t="n"/>
+      <c r="CN111" s="24" t="n"/>
+      <c r="CO111" s="24" t="n"/>
+      <c r="CP111" s="24" t="n"/>
+      <c r="CQ111" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="A112" s="24" t="inlineStr">
+        <is>
+          <t>00d2ef13176e466d</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D112" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181785</t>
+        </is>
+      </c>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
+        <is>
+          <t>Titouan Droguet</t>
+        </is>
+      </c>
+      <c r="G112" s="24" t="inlineStr">
+        <is>
+          <t>Luca Van Assche</t>
+        </is>
+      </c>
+      <c r="H112" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I112" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J112" s="25" t="n"/>
+      <c r="K112" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L112" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M112" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N112" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O112" s="28" t="n">
+        <v>0.561017</v>
+      </c>
+      <c r="P112" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q112" s="28" t="n">
+        <v>0.070821</v>
+      </c>
+      <c r="R112" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S112" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U112" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V112" s="24" t="n"/>
+      <c r="W112" s="26" t="n"/>
+      <c r="X112" s="26" t="n"/>
+      <c r="Y112" s="25" t="n"/>
+      <c r="Z112" s="26" t="n"/>
+      <c r="AA112" s="28" t="n"/>
+      <c r="AB112" s="28" t="n"/>
+      <c r="AC112" s="30" t="n"/>
+      <c r="AD112" s="24" t="n"/>
+      <c r="AE112" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Titouan Droguet p=0.561 vs Luca Van Assche. Executable ask 0.4900 (aec-atp-lucass-titdro-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF112" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG112" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH112" s="24" t="n"/>
+      <c r="AI112" s="31" t="n"/>
+      <c r="AJ112" s="31" t="n"/>
+      <c r="AK112" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL112" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM112" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN112" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO112" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP112" s="24" t="inlineStr">
+        <is>
+          <t>Titouan Droguet</t>
+        </is>
+      </c>
+      <c r="AQ112" s="24" t="inlineStr">
+        <is>
+          <t>Titouan Droguet</t>
+        </is>
+      </c>
+      <c r="AR112" s="24" t="inlineStr">
+        <is>
+          <t>Titouan Droguet</t>
+        </is>
+      </c>
+      <c r="AS112" s="24" t="inlineStr">
+        <is>
+          <t>Luca Van Assche</t>
+        </is>
+      </c>
+      <c r="AT112" s="24" t="inlineStr">
+        <is>
+          <t>Luca Van Assche</t>
+        </is>
+      </c>
+      <c r="AU112" s="24" t="inlineStr">
+        <is>
+          <t>Luca Van Assche</t>
+        </is>
+      </c>
+      <c r="AV112" s="24" t="n"/>
+      <c r="AW112" s="24" t="n"/>
+      <c r="AX112" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY112" s="24" t="n"/>
+      <c r="AZ112" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA112" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB112" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC112" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD112" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE112" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF112" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG112" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH112" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:12.259620Z</t>
+        </is>
+      </c>
+      <c r="BI112" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ112" s="25" t="n"/>
+      <c r="BK112" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL112" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM112" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN112" s="28" t="n"/>
+      <c r="BO112" s="28" t="n"/>
+      <c r="BP112" s="25" t="n"/>
+      <c r="BQ112" s="27" t="n"/>
+      <c r="BR112" s="28" t="n"/>
+      <c r="BS112" s="28" t="n"/>
+      <c r="BT112" s="28" t="n"/>
+      <c r="BU112" s="25" t="n"/>
+      <c r="BV112" s="29" t="n"/>
+      <c r="BW112" s="24" t="n"/>
+      <c r="BX112" s="30" t="n"/>
+      <c r="BY112" s="27" t="n"/>
+      <c r="BZ112" s="24" t="n"/>
+      <c r="CA112" s="31" t="n"/>
+      <c r="CB112" s="24" t="n"/>
+      <c r="CC112" s="24" t="n"/>
+      <c r="CD112" s="24" t="n"/>
+      <c r="CE112" s="24" t="n"/>
+      <c r="CF112" s="24" t="n"/>
+      <c r="CG112" s="24" t="n"/>
+      <c r="CH112" s="24" t="n"/>
+      <c r="CI112" s="24" t="n"/>
+      <c r="CJ112" s="24" t="n"/>
+      <c r="CK112" s="24" t="n"/>
+      <c r="CL112" s="24" t="n"/>
+      <c r="CM112" s="24" t="n"/>
+      <c r="CN112" s="24" t="n"/>
+      <c r="CO112" s="24" t="n"/>
+      <c r="CP112" s="24" t="n"/>
+      <c r="CQ112" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="A113" s="24" t="inlineStr">
+        <is>
+          <t>f7536fc22bd84e98</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C113" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181836</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="H113" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I113" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J113" s="25" t="n"/>
+      <c r="K113" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L113" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M113" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N113" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O113" s="28" t="n">
+        <v>0.567487</v>
+      </c>
+      <c r="P113" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q113" s="28" t="n">
+        <v>0.077291</v>
+      </c>
+      <c r="R113" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S113" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U113" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V113" s="24" t="n"/>
+      <c r="W113" s="26" t="n"/>
+      <c r="X113" s="26" t="n"/>
+      <c r="Y113" s="25" t="n"/>
+      <c r="Z113" s="26" t="n"/>
+      <c r="AA113" s="28" t="n"/>
+      <c r="AB113" s="28" t="n"/>
+      <c r="AC113" s="30" t="n"/>
+      <c r="AD113" s="24" t="n"/>
+      <c r="AE113" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Corentin Moutet p=0.433 vs Marton Fucsovics. Executable ask 0.4900 (aec-atp-marfuc-cormou-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF113" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG113" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH113" s="24" t="n"/>
+      <c r="AI113" s="31" t="n"/>
+      <c r="AJ113" s="31" t="n"/>
+      <c r="AK113" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL113" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM113" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN113" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO113" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP113" s="24" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="AQ113" s="24" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="AR113" s="24" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="AS113" s="24" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="AT113" s="24" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="AU113" s="24" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="AV113" s="24" t="n"/>
+      <c r="AW113" s="24" t="n"/>
+      <c r="AX113" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY113" s="24" t="n"/>
+      <c r="AZ113" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA113" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB113" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC113" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD113" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE113" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF113" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG113" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH113" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:10.755068Z</t>
+        </is>
+      </c>
+      <c r="BI113" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ113" s="25" t="n"/>
+      <c r="BK113" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL113" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM113" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN113" s="28" t="n"/>
+      <c r="BO113" s="28" t="n"/>
+      <c r="BP113" s="25" t="n"/>
+      <c r="BQ113" s="27" t="n"/>
+      <c r="BR113" s="28" t="n"/>
+      <c r="BS113" s="28" t="n"/>
+      <c r="BT113" s="28" t="n"/>
+      <c r="BU113" s="25" t="n"/>
+      <c r="BV113" s="29" t="n"/>
+      <c r="BW113" s="24" t="n"/>
+      <c r="BX113" s="30" t="n"/>
+      <c r="BY113" s="27" t="n"/>
+      <c r="BZ113" s="24" t="n"/>
+      <c r="CA113" s="31" t="n"/>
+      <c r="CB113" s="24" t="n"/>
+      <c r="CC113" s="24" t="n"/>
+      <c r="CD113" s="24" t="n"/>
+      <c r="CE113" s="24" t="n"/>
+      <c r="CF113" s="24" t="n"/>
+      <c r="CG113" s="24" t="n"/>
+      <c r="CH113" s="24" t="n"/>
+      <c r="CI113" s="24" t="n"/>
+      <c r="CJ113" s="24" t="n"/>
+      <c r="CK113" s="24" t="n"/>
+      <c r="CL113" s="24" t="n"/>
+      <c r="CM113" s="24" t="n"/>
+      <c r="CN113" s="24" t="n"/>
+      <c r="CO113" s="24" t="n"/>
+      <c r="CP113" s="24" t="n"/>
+      <c r="CQ113" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="36" customHeight="1">
+      <c r="A114" s="24" t="inlineStr">
+        <is>
+          <t>c3922612492b4870</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:00Z</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181781</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="inlineStr">
+        <is>
+          <t>Sho Shimabukuro</t>
+        </is>
+      </c>
+      <c r="H114" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I114" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J114" s="25" t="n"/>
+      <c r="K114" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L114" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M114" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N114" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O114" s="28" t="n">
+        <v>0.529427</v>
+      </c>
+      <c r="P114" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q114" s="28" t="n">
+        <v>-0.041388</v>
+      </c>
+      <c r="R114" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U114" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V114" s="24" t="n"/>
+      <c r="W114" s="26" t="n"/>
+      <c r="X114" s="26" t="n"/>
+      <c r="Y114" s="25" t="n"/>
+      <c r="Z114" s="26" t="n"/>
+      <c r="AA114" s="28" t="n"/>
+      <c r="AB114" s="28" t="n"/>
+      <c r="AC114" s="30" t="n"/>
+      <c r="AD114" s="24" t="n"/>
+      <c r="AE114" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Marin Cilic p=0.529 vs Sho Shimabukuro. Executable ask 0.5700 (aec-atp-shoshi-marcil-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF114" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG114" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH114" s="24" t="n"/>
+      <c r="AI114" s="31" t="n"/>
+      <c r="AJ114" s="31" t="n"/>
+      <c r="AK114" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL114" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM114" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN114" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO114" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP114" s="24" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="AQ114" s="24" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="AR114" s="24" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="AS114" s="24" t="inlineStr">
+        <is>
+          <t>Sho Shimabukuro</t>
+        </is>
+      </c>
+      <c r="AT114" s="24" t="inlineStr">
+        <is>
+          <t>Sho Shimabukuro</t>
+        </is>
+      </c>
+      <c r="AU114" s="24" t="inlineStr">
+        <is>
+          <t>Sho Shimabukuro</t>
+        </is>
+      </c>
+      <c r="AV114" s="24" t="n"/>
+      <c r="AW114" s="24" t="n"/>
+      <c r="AX114" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY114" s="24" t="n"/>
+      <c r="AZ114" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA114" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB114" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC114" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD114" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE114" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF114" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG114" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH114" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:16.186106Z</t>
+        </is>
+      </c>
+      <c r="BI114" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ114" s="25" t="n"/>
+      <c r="BK114" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL114" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM114" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN114" s="28" t="n"/>
+      <c r="BO114" s="28" t="n"/>
+      <c r="BP114" s="25" t="n"/>
+      <c r="BQ114" s="27" t="n"/>
+      <c r="BR114" s="28" t="n"/>
+      <c r="BS114" s="28" t="n"/>
+      <c r="BT114" s="28" t="n"/>
+      <c r="BU114" s="25" t="n"/>
+      <c r="BV114" s="29" t="n"/>
+      <c r="BW114" s="24" t="n"/>
+      <c r="BX114" s="30" t="n"/>
+      <c r="BY114" s="27" t="n"/>
+      <c r="BZ114" s="24" t="n"/>
+      <c r="CA114" s="31" t="n"/>
+      <c r="CB114" s="24" t="n"/>
+      <c r="CC114" s="24" t="n"/>
+      <c r="CD114" s="24" t="n"/>
+      <c r="CE114" s="24" t="n"/>
+      <c r="CF114" s="24" t="n"/>
+      <c r="CG114" s="24" t="n"/>
+      <c r="CH114" s="24" t="n"/>
+      <c r="CI114" s="24" t="n"/>
+      <c r="CJ114" s="24" t="n"/>
+      <c r="CK114" s="24" t="n"/>
+      <c r="CL114" s="24" t="n"/>
+      <c r="CM114" s="24" t="n"/>
+      <c r="CN114" s="24" t="n"/>
+      <c r="CO114" s="24" t="n"/>
+      <c r="CP114" s="24" t="n"/>
+      <c r="CQ114" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="36" customHeight="1">
+      <c r="A115" s="24" t="inlineStr">
+        <is>
+          <t>b31b8f26e50748ca</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C115" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="D115" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181801</t>
+        </is>
+      </c>
+      <c r="E115" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F115" s="24" t="inlineStr">
+        <is>
+          <t>Kyrian Jacquet</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo</t>
+        </is>
+      </c>
+      <c r="H115" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I115" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J115" s="25" t="n"/>
+      <c r="K115" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L115" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M115" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N115" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O115" s="28" t="n">
+        <v>0.5845590000000001</v>
+      </c>
+      <c r="P115" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q115" s="28" t="n">
+        <v>0.045388</v>
+      </c>
+      <c r="R115" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S115" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T115" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U115" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V115" s="24" t="n"/>
+      <c r="W115" s="26" t="n"/>
+      <c r="X115" s="26" t="n"/>
+      <c r="Y115" s="25" t="n"/>
+      <c r="Z115" s="26" t="n"/>
+      <c r="AA115" s="28" t="n"/>
+      <c r="AB115" s="28" t="n"/>
+      <c r="AC115" s="30" t="n"/>
+      <c r="AD115" s="24" t="n"/>
+      <c r="AE115" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Kyrian Jacquet p=0.415 vs Gabriel Diallo. Executable ask 0.5400 (aec-atp-gabdia-kyrjac-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF115" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG115" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH115" s="24" t="n"/>
+      <c r="AI115" s="31" t="n"/>
+      <c r="AJ115" s="31" t="n"/>
+      <c r="AK115" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL115" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM115" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN115" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO115" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP115" s="24" t="inlineStr">
+        <is>
+          <t>Kyrian Jacquet</t>
+        </is>
+      </c>
+      <c r="AQ115" s="24" t="inlineStr">
+        <is>
+          <t>Kyrian Jacquet</t>
+        </is>
+      </c>
+      <c r="AR115" s="24" t="inlineStr">
+        <is>
+          <t>Kyrian Jacquet</t>
+        </is>
+      </c>
+      <c r="AS115" s="24" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo</t>
+        </is>
+      </c>
+      <c r="AT115" s="24" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo</t>
+        </is>
+      </c>
+      <c r="AU115" s="24" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo</t>
+        </is>
+      </c>
+      <c r="AV115" s="24" t="n"/>
+      <c r="AW115" s="24" t="n"/>
+      <c r="AX115" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY115" s="24" t="n"/>
+      <c r="AZ115" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA115" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB115" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC115" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD115" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE115" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF115" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG115" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH115" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:17.140267Z</t>
+        </is>
+      </c>
+      <c r="BI115" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ115" s="25" t="n"/>
+      <c r="BK115" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL115" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM115" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN115" s="28" t="n"/>
+      <c r="BO115" s="28" t="n"/>
+      <c r="BP115" s="25" t="n"/>
+      <c r="BQ115" s="27" t="n"/>
+      <c r="BR115" s="28" t="n"/>
+      <c r="BS115" s="28" t="n"/>
+      <c r="BT115" s="28" t="n"/>
+      <c r="BU115" s="25" t="n"/>
+      <c r="BV115" s="29" t="n"/>
+      <c r="BW115" s="24" t="n"/>
+      <c r="BX115" s="30" t="n"/>
+      <c r="BY115" s="27" t="n"/>
+      <c r="BZ115" s="24" t="n"/>
+      <c r="CA115" s="31" t="n"/>
+      <c r="CB115" s="24" t="n"/>
+      <c r="CC115" s="24" t="n"/>
+      <c r="CD115" s="24" t="n"/>
+      <c r="CE115" s="24" t="n"/>
+      <c r="CF115" s="24" t="n"/>
+      <c r="CG115" s="24" t="n"/>
+      <c r="CH115" s="24" t="n"/>
+      <c r="CI115" s="24" t="n"/>
+      <c r="CJ115" s="24" t="n"/>
+      <c r="CK115" s="24" t="n"/>
+      <c r="CL115" s="24" t="n"/>
+      <c r="CM115" s="24" t="n"/>
+      <c r="CN115" s="24" t="n"/>
+      <c r="CO115" s="24" t="n"/>
+      <c r="CP115" s="24" t="n"/>
+      <c r="CQ115" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="36" customHeight="1">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>e83b19278e0a4a7b</t>
+        </is>
+      </c>
+      <c r="B116" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C116" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:30Z</t>
+        </is>
+      </c>
+      <c r="D116" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181798</t>
+        </is>
+      </c>
+      <c r="E116" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F116" s="24" t="inlineStr">
+        <is>
+          <t>Yannick Hanfmann</t>
+        </is>
+      </c>
+      <c r="G116" s="24" t="inlineStr">
+        <is>
+          <t>Benjamin Bonzi</t>
+        </is>
+      </c>
+      <c r="H116" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I116" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J116" s="25" t="n"/>
+      <c r="K116" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L116" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M116" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N116" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O116" s="28" t="n">
+        <v>0.552246</v>
+      </c>
+      <c r="P116" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q116" s="28" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="R116" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S116" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U116" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V116" s="24" t="n"/>
+      <c r="W116" s="26" t="n"/>
+      <c r="X116" s="26" t="n"/>
+      <c r="Y116" s="25" t="n"/>
+      <c r="Z116" s="26" t="n"/>
+      <c r="AA116" s="28" t="n"/>
+      <c r="AB116" s="28" t="n"/>
+      <c r="AC116" s="30" t="n"/>
+      <c r="AD116" s="24" t="n"/>
+      <c r="AE116" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Yannick Hanfmann p=0.552 vs Benjamin Bonzi. Executable ask 0.5300 (aec-atp-benbon-yanhan-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF116" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG116" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH116" s="24" t="n"/>
+      <c r="AI116" s="31" t="n"/>
+      <c r="AJ116" s="31" t="n"/>
+      <c r="AK116" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL116" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM116" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN116" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO116" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP116" s="24" t="inlineStr">
+        <is>
+          <t>Yannick Hanfmann</t>
+        </is>
+      </c>
+      <c r="AQ116" s="24" t="inlineStr">
+        <is>
+          <t>Yannick Hanfmann</t>
+        </is>
+      </c>
+      <c r="AR116" s="24" t="inlineStr">
+        <is>
+          <t>Yannick Hanfmann</t>
+        </is>
+      </c>
+      <c r="AS116" s="24" t="inlineStr">
+        <is>
+          <t>Benjamin Bonzi</t>
+        </is>
+      </c>
+      <c r="AT116" s="24" t="inlineStr">
+        <is>
+          <t>Benjamin Bonzi</t>
+        </is>
+      </c>
+      <c r="AU116" s="24" t="inlineStr">
+        <is>
+          <t>Benjamin Bonzi</t>
+        </is>
+      </c>
+      <c r="AV116" s="24" t="n"/>
+      <c r="AW116" s="24" t="n"/>
+      <c r="AX116" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY116" s="24" t="n"/>
+      <c r="AZ116" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA116" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB116" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC116" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD116" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE116" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF116" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG116" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH116" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:19.678581Z</t>
+        </is>
+      </c>
+      <c r="BI116" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ116" s="25" t="n"/>
+      <c r="BK116" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL116" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM116" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN116" s="28" t="n"/>
+      <c r="BO116" s="28" t="n"/>
+      <c r="BP116" s="25" t="n"/>
+      <c r="BQ116" s="27" t="n"/>
+      <c r="BR116" s="28" t="n"/>
+      <c r="BS116" s="28" t="n"/>
+      <c r="BT116" s="28" t="n"/>
+      <c r="BU116" s="25" t="n"/>
+      <c r="BV116" s="29" t="n"/>
+      <c r="BW116" s="24" t="n"/>
+      <c r="BX116" s="30" t="n"/>
+      <c r="BY116" s="27" t="n"/>
+      <c r="BZ116" s="24" t="n"/>
+      <c r="CA116" s="31" t="n"/>
+      <c r="CB116" s="24" t="n"/>
+      <c r="CC116" s="24" t="n"/>
+      <c r="CD116" s="24" t="n"/>
+      <c r="CE116" s="24" t="n"/>
+      <c r="CF116" s="24" t="n"/>
+      <c r="CG116" s="24" t="n"/>
+      <c r="CH116" s="24" t="n"/>
+      <c r="CI116" s="24" t="n"/>
+      <c r="CJ116" s="24" t="n"/>
+      <c r="CK116" s="24" t="n"/>
+      <c r="CL116" s="24" t="n"/>
+      <c r="CM116" s="24" t="n"/>
+      <c r="CN116" s="24" t="n"/>
+      <c r="CO116" s="24" t="n"/>
+      <c r="CP116" s="24" t="n"/>
+      <c r="CQ116" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="36" customHeight="1">
+      <c r="A117" s="24" t="inlineStr">
+        <is>
+          <t>aace33ecb9034207</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="inlineStr">
+        <is>
+          <t>Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="G117" s="24" t="inlineStr">
+        <is>
+          <t>Alexis Galarneau</t>
+        </is>
+      </c>
+      <c r="H117" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I117" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J117" s="25" t="n"/>
+      <c r="K117" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L117" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M117" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N117" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O117" s="28" t="n">
+        <v>0.57909</v>
+      </c>
+      <c r="P117" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q117" s="28" t="n">
+        <v>0.088894</v>
+      </c>
+      <c r="R117" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="S117" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T117" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U117" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V117" s="24" t="n"/>
+      <c r="W117" s="26" t="n"/>
+      <c r="X117" s="26" t="n"/>
+      <c r="Y117" s="25" t="n"/>
+      <c r="Z117" s="26" t="n"/>
+      <c r="AA117" s="28" t="n"/>
+      <c r="AB117" s="28" t="n"/>
+      <c r="AC117" s="30" t="n"/>
+      <c r="AD117" s="24" t="n"/>
+      <c r="AE117" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Vit Kopriva p=0.579 vs Alexis Galarneau. Executable ask 0.4900 (aec-atp-alegal-vitkop-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF117" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG117" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH117" s="24" t="n"/>
+      <c r="AI117" s="31" t="n"/>
+      <c r="AJ117" s="31" t="n"/>
+      <c r="AK117" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL117" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM117" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN117" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO117" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP117" s="24" t="inlineStr">
+        <is>
+          <t>Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="AQ117" s="24" t="inlineStr">
+        <is>
+          <t>Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="AR117" s="24" t="inlineStr">
+        <is>
+          <t>Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="AS117" s="24" t="inlineStr">
+        <is>
+          <t>Alexis Galarneau</t>
+        </is>
+      </c>
+      <c r="AT117" s="24" t="inlineStr">
+        <is>
+          <t>Alexis Galarneau</t>
+        </is>
+      </c>
+      <c r="AU117" s="24" t="inlineStr">
+        <is>
+          <t>Alexis Galarneau</t>
+        </is>
+      </c>
+      <c r="AV117" s="24" t="n"/>
+      <c r="AW117" s="24" t="n"/>
+      <c r="AX117" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY117" s="24" t="n"/>
+      <c r="AZ117" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA117" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB117" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC117" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD117" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE117" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF117" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG117" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH117" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:20.160476Z</t>
+        </is>
+      </c>
+      <c r="BI117" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ117" s="25" t="n"/>
+      <c r="BK117" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL117" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM117" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN117" s="28" t="n"/>
+      <c r="BO117" s="28" t="n"/>
+      <c r="BP117" s="25" t="n"/>
+      <c r="BQ117" s="27" t="n"/>
+      <c r="BR117" s="28" t="n"/>
+      <c r="BS117" s="28" t="n"/>
+      <c r="BT117" s="28" t="n"/>
+      <c r="BU117" s="25" t="n"/>
+      <c r="BV117" s="29" t="n"/>
+      <c r="BW117" s="24" t="n"/>
+      <c r="BX117" s="30" t="n"/>
+      <c r="BY117" s="27" t="n"/>
+      <c r="BZ117" s="24" t="n"/>
+      <c r="CA117" s="31" t="n"/>
+      <c r="CB117" s="24" t="n"/>
+      <c r="CC117" s="24" t="n"/>
+      <c r="CD117" s="24" t="n"/>
+      <c r="CE117" s="24" t="n"/>
+      <c r="CF117" s="24" t="n"/>
+      <c r="CG117" s="24" t="n"/>
+      <c r="CH117" s="24" t="n"/>
+      <c r="CI117" s="24" t="n"/>
+      <c r="CJ117" s="24" t="n"/>
+      <c r="CK117" s="24" t="n"/>
+      <c r="CL117" s="24" t="n"/>
+      <c r="CM117" s="24" t="n"/>
+      <c r="CN117" s="24" t="n"/>
+      <c r="CO117" s="24" t="n"/>
+      <c r="CP117" s="24" t="n"/>
+      <c r="CQ117" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
